--- a/dane.xlsx
+++ b/dane.xlsx
@@ -3759,7 +3759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G491"/>
+  <dimension ref="A1:G501"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16047,6 +16047,256 @@
       </c>
       <c r="G491" t="n">
         <v>400</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="n">
+        <v>491</v>
+      </c>
+      <c r="B492" s="2" t="n">
+        <v>46068</v>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>Zwrot</t>
+        </is>
+      </c>
+      <c r="D492" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="E492" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F492" t="n">
+        <v>1</v>
+      </c>
+      <c r="G492" t="n">
+        <v>2397</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="n">
+        <v>492</v>
+      </c>
+      <c r="B493" s="2" t="n">
+        <v>46072</v>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>Wysłane</t>
+        </is>
+      </c>
+      <c r="D493" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="E493" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F493" t="n">
+        <v>4</v>
+      </c>
+      <c r="G493" t="n">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="n">
+        <v>493</v>
+      </c>
+      <c r="B494" s="2" t="n">
+        <v>46063</v>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>Dostarczone</t>
+        </is>
+      </c>
+      <c r="D494" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="E494" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F494" t="n">
+        <v>2</v>
+      </c>
+      <c r="G494" t="n">
+        <v>1953</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="n">
+        <v>494</v>
+      </c>
+      <c r="B495" s="2" t="n">
+        <v>46078</v>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>Nowe</t>
+        </is>
+      </c>
+      <c r="D495" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="E495" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F495" t="n">
+        <v>3</v>
+      </c>
+      <c r="G495" t="n">
+        <v>1805</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="n">
+        <v>495</v>
+      </c>
+      <c r="B496" s="2" t="n">
+        <v>46075</v>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>Wysłane</t>
+        </is>
+      </c>
+      <c r="D496" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="E496" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F496" t="n">
+        <v>3</v>
+      </c>
+      <c r="G496" t="n">
+        <v>2678</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="n">
+        <v>496</v>
+      </c>
+      <c r="B497" s="2" t="n">
+        <v>46071</v>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>Zwrot</t>
+        </is>
+      </c>
+      <c r="D497" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="E497" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F497" t="n">
+        <v>3</v>
+      </c>
+      <c r="G497" t="n">
+        <v>2586</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="n">
+        <v>497</v>
+      </c>
+      <c r="B498" s="2" t="n">
+        <v>46070</v>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>Nowe</t>
+        </is>
+      </c>
+      <c r="D498" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="E498" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F498" t="n">
+        <v>2</v>
+      </c>
+      <c r="G498" t="n">
+        <v>2745</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="n">
+        <v>498</v>
+      </c>
+      <c r="B499" s="2" t="n">
+        <v>46080</v>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>Nowe</t>
+        </is>
+      </c>
+      <c r="D499" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="E499" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F499" t="n">
+        <v>3</v>
+      </c>
+      <c r="G499" t="n">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="n">
+        <v>499</v>
+      </c>
+      <c r="B500" s="2" t="n">
+        <v>46077</v>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>Nowe</t>
+        </is>
+      </c>
+      <c r="D500" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E500" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F500" t="n">
+        <v>1</v>
+      </c>
+      <c r="G500" t="n">
+        <v>2061</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="n">
+        <v>500</v>
+      </c>
+      <c r="B501" s="2" t="n">
+        <v>46073</v>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>Zwrot</t>
+        </is>
+      </c>
+      <c r="D501" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="E501" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F501" t="n">
+        <v>2</v>
+      </c>
+      <c r="G501" t="n">
+        <v>1062</v>
       </c>
     </row>
   </sheetData>
@@ -16060,7 +16310,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3014"/>
+  <dimension ref="A1:E3072"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59006,6 +59256,992 @@
       </c>
       <c r="E3014" t="n">
         <v>490</v>
+      </c>
+    </row>
+    <row r="3015">
+      <c r="A3015" t="n">
+        <v>0</v>
+      </c>
+      <c r="B3015" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3015" t="n">
+        <v>52</v>
+      </c>
+      <c r="D3015" t="n">
+        <v>48</v>
+      </c>
+      <c r="E3015" t="n">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="3016">
+      <c r="A3016" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3016" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3016" t="n">
+        <v>70</v>
+      </c>
+      <c r="D3016" t="n">
+        <v>86</v>
+      </c>
+      <c r="E3016" t="n">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="3017">
+      <c r="A3017" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3017" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3017" t="n">
+        <v>62</v>
+      </c>
+      <c r="D3017" t="n">
+        <v>80</v>
+      </c>
+      <c r="E3017" t="n">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="3018">
+      <c r="A3018" t="n">
+        <v>3</v>
+      </c>
+      <c r="B3018" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3018" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3018" t="n">
+        <v>47</v>
+      </c>
+      <c r="E3018" t="n">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="3019">
+      <c r="A3019" t="n">
+        <v>4</v>
+      </c>
+      <c r="B3019" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3019" t="n">
+        <v>79</v>
+      </c>
+      <c r="D3019" t="n">
+        <v>15</v>
+      </c>
+      <c r="E3019" t="n">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="3020">
+      <c r="A3020" t="n">
+        <v>5</v>
+      </c>
+      <c r="B3020" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3020" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3020" t="n">
+        <v>63</v>
+      </c>
+      <c r="E3020" t="n">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="3021">
+      <c r="A3021" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3021" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3021" t="n">
+        <v>42</v>
+      </c>
+      <c r="D3021" t="n">
+        <v>43</v>
+      </c>
+      <c r="E3021" t="n">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="3022">
+      <c r="A3022" t="n">
+        <v>7</v>
+      </c>
+      <c r="B3022" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3022" t="n">
+        <v>86</v>
+      </c>
+      <c r="D3022" t="n">
+        <v>75</v>
+      </c>
+      <c r="E3022" t="n">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="3023">
+      <c r="A3023" t="n">
+        <v>8</v>
+      </c>
+      <c r="B3023" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3023" t="n">
+        <v>38</v>
+      </c>
+      <c r="D3023" t="n">
+        <v>89</v>
+      </c>
+      <c r="E3023" t="n">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="3024">
+      <c r="A3024" t="n">
+        <v>9</v>
+      </c>
+      <c r="B3024" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3024" t="n">
+        <v>11</v>
+      </c>
+      <c r="D3024" t="n">
+        <v>24</v>
+      </c>
+      <c r="E3024" t="n">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="3025">
+      <c r="A3025" t="n">
+        <v>10</v>
+      </c>
+      <c r="B3025" t="n">
+        <v>7</v>
+      </c>
+      <c r="C3025" t="n">
+        <v>65</v>
+      </c>
+      <c r="D3025" t="n">
+        <v>11</v>
+      </c>
+      <c r="E3025" t="n">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="3026">
+      <c r="A3026" t="n">
+        <v>11</v>
+      </c>
+      <c r="B3026" t="n">
+        <v>8</v>
+      </c>
+      <c r="C3026" t="n">
+        <v>68</v>
+      </c>
+      <c r="D3026" t="n">
+        <v>81</v>
+      </c>
+      <c r="E3026" t="n">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="3027">
+      <c r="A3027" t="n">
+        <v>12</v>
+      </c>
+      <c r="B3027" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3027" t="n">
+        <v>12</v>
+      </c>
+      <c r="D3027" t="n">
+        <v>40</v>
+      </c>
+      <c r="E3027" t="n">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="3028">
+      <c r="A3028" t="n">
+        <v>13</v>
+      </c>
+      <c r="B3028" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3028" t="n">
+        <v>91</v>
+      </c>
+      <c r="D3028" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3028" t="n">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="3029">
+      <c r="A3029" t="n">
+        <v>14</v>
+      </c>
+      <c r="B3029" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3029" t="n">
+        <v>64</v>
+      </c>
+      <c r="D3029" t="n">
+        <v>60</v>
+      </c>
+      <c r="E3029" t="n">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="3030">
+      <c r="A3030" t="n">
+        <v>15</v>
+      </c>
+      <c r="B3030" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3030" t="n">
+        <v>10</v>
+      </c>
+      <c r="D3030" t="n">
+        <v>93</v>
+      </c>
+      <c r="E3030" t="n">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="3031">
+      <c r="A3031" t="n">
+        <v>16</v>
+      </c>
+      <c r="B3031" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3031" t="n">
+        <v>66</v>
+      </c>
+      <c r="D3031" t="n">
+        <v>82</v>
+      </c>
+      <c r="E3031" t="n">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="3032">
+      <c r="A3032" t="n">
+        <v>17</v>
+      </c>
+      <c r="B3032" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3032" t="n">
+        <v>7</v>
+      </c>
+      <c r="D3032" t="n">
+        <v>8</v>
+      </c>
+      <c r="E3032" t="n">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="3033">
+      <c r="A3033" t="n">
+        <v>18</v>
+      </c>
+      <c r="B3033" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3033" t="n">
+        <v>57</v>
+      </c>
+      <c r="D3033" t="n">
+        <v>99</v>
+      </c>
+      <c r="E3033" t="n">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="3034">
+      <c r="A3034" t="n">
+        <v>19</v>
+      </c>
+      <c r="B3034" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3034" t="n">
+        <v>60</v>
+      </c>
+      <c r="D3034" t="n">
+        <v>39</v>
+      </c>
+      <c r="E3034" t="n">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="3035">
+      <c r="A3035" t="n">
+        <v>20</v>
+      </c>
+      <c r="B3035" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3035" t="n">
+        <v>7</v>
+      </c>
+      <c r="D3035" t="n">
+        <v>61</v>
+      </c>
+      <c r="E3035" t="n">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="3036">
+      <c r="A3036" t="n">
+        <v>21</v>
+      </c>
+      <c r="B3036" t="n">
+        <v>7</v>
+      </c>
+      <c r="C3036" t="n">
+        <v>22</v>
+      </c>
+      <c r="D3036" t="n">
+        <v>40</v>
+      </c>
+      <c r="E3036" t="n">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="3037">
+      <c r="A3037" t="n">
+        <v>22</v>
+      </c>
+      <c r="B3037" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3037" t="n">
+        <v>71</v>
+      </c>
+      <c r="D3037" t="n">
+        <v>41</v>
+      </c>
+      <c r="E3037" t="n">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="3038">
+      <c r="A3038" t="n">
+        <v>23</v>
+      </c>
+      <c r="B3038" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3038" t="n">
+        <v>77</v>
+      </c>
+      <c r="D3038" t="n">
+        <v>93</v>
+      </c>
+      <c r="E3038" t="n">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="3039">
+      <c r="A3039" t="n">
+        <v>24</v>
+      </c>
+      <c r="B3039" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3039" t="n">
+        <v>98</v>
+      </c>
+      <c r="D3039" t="n">
+        <v>27</v>
+      </c>
+      <c r="E3039" t="n">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="3040">
+      <c r="A3040" t="n">
+        <v>25</v>
+      </c>
+      <c r="B3040" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3040" t="n">
+        <v>87</v>
+      </c>
+      <c r="D3040" t="n">
+        <v>46</v>
+      </c>
+      <c r="E3040" t="n">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="3041">
+      <c r="A3041" t="n">
+        <v>26</v>
+      </c>
+      <c r="B3041" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3041" t="n">
+        <v>53</v>
+      </c>
+      <c r="D3041" t="n">
+        <v>67</v>
+      </c>
+      <c r="E3041" t="n">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="3042">
+      <c r="A3042" t="n">
+        <v>27</v>
+      </c>
+      <c r="B3042" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3042" t="n">
+        <v>95</v>
+      </c>
+      <c r="D3042" t="n">
+        <v>26</v>
+      </c>
+      <c r="E3042" t="n">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="3043">
+      <c r="A3043" t="n">
+        <v>28</v>
+      </c>
+      <c r="B3043" t="n">
+        <v>7</v>
+      </c>
+      <c r="C3043" t="n">
+        <v>52</v>
+      </c>
+      <c r="D3043" t="n">
+        <v>75</v>
+      </c>
+      <c r="E3043" t="n">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="3044">
+      <c r="A3044" t="n">
+        <v>29</v>
+      </c>
+      <c r="B3044" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3044" t="n">
+        <v>95</v>
+      </c>
+      <c r="D3044" t="n">
+        <v>71</v>
+      </c>
+      <c r="E3044" t="n">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="3045">
+      <c r="A3045" t="n">
+        <v>30</v>
+      </c>
+      <c r="B3045" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3045" t="n">
+        <v>40</v>
+      </c>
+      <c r="D3045" t="n">
+        <v>91</v>
+      </c>
+      <c r="E3045" t="n">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="3046">
+      <c r="A3046" t="n">
+        <v>31</v>
+      </c>
+      <c r="B3046" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3046" t="n">
+        <v>47</v>
+      </c>
+      <c r="D3046" t="n">
+        <v>12</v>
+      </c>
+      <c r="E3046" t="n">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="3047">
+      <c r="A3047" t="n">
+        <v>32</v>
+      </c>
+      <c r="B3047" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3047" t="n">
+        <v>12</v>
+      </c>
+      <c r="D3047" t="n">
+        <v>61</v>
+      </c>
+      <c r="E3047" t="n">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="3048">
+      <c r="A3048" t="n">
+        <v>33</v>
+      </c>
+      <c r="B3048" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3048" t="n">
+        <v>78</v>
+      </c>
+      <c r="D3048" t="n">
+        <v>83</v>
+      </c>
+      <c r="E3048" t="n">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="3049">
+      <c r="A3049" t="n">
+        <v>34</v>
+      </c>
+      <c r="B3049" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3049" t="n">
+        <v>36</v>
+      </c>
+      <c r="D3049" t="n">
+        <v>27</v>
+      </c>
+      <c r="E3049" t="n">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="3050">
+      <c r="A3050" t="n">
+        <v>35</v>
+      </c>
+      <c r="B3050" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3050" t="n">
+        <v>31</v>
+      </c>
+      <c r="D3050" t="n">
+        <v>4</v>
+      </c>
+      <c r="E3050" t="n">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="3051">
+      <c r="A3051" t="n">
+        <v>36</v>
+      </c>
+      <c r="B3051" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3051" t="n">
+        <v>71</v>
+      </c>
+      <c r="D3051" t="n">
+        <v>96</v>
+      </c>
+      <c r="E3051" t="n">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="3052">
+      <c r="A3052" t="n">
+        <v>37</v>
+      </c>
+      <c r="B3052" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3052" t="n">
+        <v>59</v>
+      </c>
+      <c r="D3052" t="n">
+        <v>79</v>
+      </c>
+      <c r="E3052" t="n">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="3053">
+      <c r="A3053" t="n">
+        <v>38</v>
+      </c>
+      <c r="B3053" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3053" t="n">
+        <v>26</v>
+      </c>
+      <c r="D3053" t="n">
+        <v>26</v>
+      </c>
+      <c r="E3053" t="n">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="3054">
+      <c r="A3054" t="n">
+        <v>39</v>
+      </c>
+      <c r="B3054" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3054" t="n">
+        <v>71</v>
+      </c>
+      <c r="D3054" t="n">
+        <v>69</v>
+      </c>
+      <c r="E3054" t="n">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="3055">
+      <c r="A3055" t="n">
+        <v>40</v>
+      </c>
+      <c r="B3055" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3055" t="n">
+        <v>42</v>
+      </c>
+      <c r="D3055" t="n">
+        <v>39</v>
+      </c>
+      <c r="E3055" t="n">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="3056">
+      <c r="A3056" t="n">
+        <v>41</v>
+      </c>
+      <c r="B3056" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3056" t="n">
+        <v>25</v>
+      </c>
+      <c r="D3056" t="n">
+        <v>53</v>
+      </c>
+      <c r="E3056" t="n">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="3057">
+      <c r="A3057" t="n">
+        <v>42</v>
+      </c>
+      <c r="B3057" t="n">
+        <v>7</v>
+      </c>
+      <c r="C3057" t="n">
+        <v>100</v>
+      </c>
+      <c r="D3057" t="n">
+        <v>10</v>
+      </c>
+      <c r="E3057" t="n">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="3058">
+      <c r="A3058" t="n">
+        <v>43</v>
+      </c>
+      <c r="B3058" t="n">
+        <v>8</v>
+      </c>
+      <c r="C3058" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3058" t="n">
+        <v>90</v>
+      </c>
+      <c r="E3058" t="n">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="3059">
+      <c r="A3059" t="n">
+        <v>44</v>
+      </c>
+      <c r="B3059" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3059" t="n">
+        <v>75</v>
+      </c>
+      <c r="D3059" t="n">
+        <v>66</v>
+      </c>
+      <c r="E3059" t="n">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="3060">
+      <c r="A3060" t="n">
+        <v>45</v>
+      </c>
+      <c r="B3060" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3060" t="n">
+        <v>97</v>
+      </c>
+      <c r="D3060" t="n">
+        <v>42</v>
+      </c>
+      <c r="E3060" t="n">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="3061">
+      <c r="A3061" t="n">
+        <v>46</v>
+      </c>
+      <c r="B3061" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3061" t="n">
+        <v>96</v>
+      </c>
+      <c r="D3061" t="n">
+        <v>25</v>
+      </c>
+      <c r="E3061" t="n">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="3062">
+      <c r="A3062" t="n">
+        <v>47</v>
+      </c>
+      <c r="B3062" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3062" t="n">
+        <v>50</v>
+      </c>
+      <c r="D3062" t="n">
+        <v>84</v>
+      </c>
+      <c r="E3062" t="n">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="3063">
+      <c r="A3063" t="n">
+        <v>48</v>
+      </c>
+      <c r="B3063" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3063" t="n">
+        <v>46</v>
+      </c>
+      <c r="D3063" t="n">
+        <v>40</v>
+      </c>
+      <c r="E3063" t="n">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="3064">
+      <c r="A3064" t="n">
+        <v>49</v>
+      </c>
+      <c r="B3064" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3064" t="n">
+        <v>90</v>
+      </c>
+      <c r="D3064" t="n">
+        <v>82</v>
+      </c>
+      <c r="E3064" t="n">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="3065">
+      <c r="A3065" t="n">
+        <v>50</v>
+      </c>
+      <c r="B3065" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3065" t="n">
+        <v>84</v>
+      </c>
+      <c r="D3065" t="n">
+        <v>98</v>
+      </c>
+      <c r="E3065" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="3066">
+      <c r="A3066" t="n">
+        <v>51</v>
+      </c>
+      <c r="B3066" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3066" t="n">
+        <v>27</v>
+      </c>
+      <c r="D3066" t="n">
+        <v>38</v>
+      </c>
+      <c r="E3066" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="3067">
+      <c r="A3067" t="n">
+        <v>52</v>
+      </c>
+      <c r="B3067" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3067" t="n">
+        <v>70</v>
+      </c>
+      <c r="D3067" t="n">
+        <v>85</v>
+      </c>
+      <c r="E3067" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="3068">
+      <c r="A3068" t="n">
+        <v>53</v>
+      </c>
+      <c r="B3068" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3068" t="n">
+        <v>66</v>
+      </c>
+      <c r="D3068" t="n">
+        <v>38</v>
+      </c>
+      <c r="E3068" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="3069">
+      <c r="A3069" t="n">
+        <v>54</v>
+      </c>
+      <c r="B3069" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3069" t="n">
+        <v>82</v>
+      </c>
+      <c r="D3069" t="n">
+        <v>57</v>
+      </c>
+      <c r="E3069" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="3070">
+      <c r="A3070" t="n">
+        <v>55</v>
+      </c>
+      <c r="B3070" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3070" t="n">
+        <v>52</v>
+      </c>
+      <c r="D3070" t="n">
+        <v>89</v>
+      </c>
+      <c r="E3070" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="3071">
+      <c r="A3071" t="n">
+        <v>56</v>
+      </c>
+      <c r="B3071" t="n">
+        <v>7</v>
+      </c>
+      <c r="C3071" t="n">
+        <v>76</v>
+      </c>
+      <c r="D3071" t="n">
+        <v>91</v>
+      </c>
+      <c r="E3071" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="3072">
+      <c r="A3072" t="n">
+        <v>57</v>
+      </c>
+      <c r="B3072" t="n">
+        <v>8</v>
+      </c>
+      <c r="C3072" t="n">
+        <v>85</v>
+      </c>
+      <c r="D3072" t="n">
+        <v>93</v>
+      </c>
+      <c r="E3072" t="n">
+        <v>500</v>
       </c>
     </row>
   </sheetData>
@@ -59019,7 +60255,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F213"/>
+  <dimension ref="A1:F216"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64964,30 +66200,114 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Glow Opole</t>
+          <t>Vita Pro</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>9125752553</t>
+          <t>0039863389</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Elbląg</t>
+          <t>Radom</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
+          <t>Sklep internetowy z suplementami</t>
+        </is>
+      </c>
+      <c r="F213" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>218</v>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Care Pure </t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>9163561334</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Zabrze</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
           <t>Medycyna estetyczna / klinika urody</t>
         </is>
       </c>
-      <c r="F213" t="n">
-        <v>2</v>
+      <c r="F214" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>219</v>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Well Power Zabrze</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>8678424220</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Koło</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>Medycyna estetyczna / klinika urody</t>
+        </is>
+      </c>
+      <c r="F215" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>220</v>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Energy Power Radom</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>4609605632</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Opole</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>Siłownia / klub sportowy</t>
+        </is>
+      </c>
+      <c r="F216" t="n">
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/dane.xlsx
+++ b/dane.xlsx
@@ -3759,7 +3759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G501"/>
+  <dimension ref="A1:G511"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16297,6 +16297,256 @@
       </c>
       <c r="G501" t="n">
         <v>1062</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="n">
+        <v>501</v>
+      </c>
+      <c r="B502" s="2" t="n">
+        <v>46073</v>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>Zwrot</t>
+        </is>
+      </c>
+      <c r="D502" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E502" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F502" t="n">
+        <v>3</v>
+      </c>
+      <c r="G502" t="n">
+        <v>2520</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="n">
+        <v>502</v>
+      </c>
+      <c r="B503" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>Wysłane</t>
+        </is>
+      </c>
+      <c r="D503" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E503" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F503" t="n">
+        <v>3</v>
+      </c>
+      <c r="G503" t="n">
+        <v>2726</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="n">
+        <v>503</v>
+      </c>
+      <c r="B504" s="2" t="n">
+        <v>46090</v>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>Zwrot</t>
+        </is>
+      </c>
+      <c r="D504" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="E504" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F504" t="n">
+        <v>3</v>
+      </c>
+      <c r="G504" t="n">
+        <v>2932</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="n">
+        <v>504</v>
+      </c>
+      <c r="B505" s="2" t="n">
+        <v>46066</v>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>Nowe</t>
+        </is>
+      </c>
+      <c r="D505" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="E505" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F505" t="n">
+        <v>4</v>
+      </c>
+      <c r="G505" t="n">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="n">
+        <v>505</v>
+      </c>
+      <c r="B506" s="2" t="n">
+        <v>46077</v>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>Zwrot</t>
+        </is>
+      </c>
+      <c r="D506" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="E506" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F506" t="n">
+        <v>1</v>
+      </c>
+      <c r="G506" t="n">
+        <v>2073</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="n">
+        <v>506</v>
+      </c>
+      <c r="B507" s="2" t="n">
+        <v>46069</v>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>Wysłane</t>
+        </is>
+      </c>
+      <c r="D507" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="E507" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F507" t="n">
+        <v>2</v>
+      </c>
+      <c r="G507" t="n">
+        <v>956</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="n">
+        <v>507</v>
+      </c>
+      <c r="B508" s="2" t="n">
+        <v>46067</v>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>Nowe</t>
+        </is>
+      </c>
+      <c r="D508" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="E508" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F508" t="n">
+        <v>3</v>
+      </c>
+      <c r="G508" t="n">
+        <v>2984</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="n">
+        <v>508</v>
+      </c>
+      <c r="B509" s="2" t="n">
+        <v>46066</v>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>Nowe</t>
+        </is>
+      </c>
+      <c r="D509" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="E509" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F509" t="n">
+        <v>1</v>
+      </c>
+      <c r="G509" t="n">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="n">
+        <v>509</v>
+      </c>
+      <c r="B510" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>Dostarczone</t>
+        </is>
+      </c>
+      <c r="D510" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E510" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F510" t="n">
+        <v>2</v>
+      </c>
+      <c r="G510" t="n">
+        <v>2326</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="n">
+        <v>510</v>
+      </c>
+      <c r="B511" s="2" t="n">
+        <v>46071</v>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>Nowe</t>
+        </is>
+      </c>
+      <c r="D511" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="E511" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F511" t="n">
+        <v>4</v>
+      </c>
+      <c r="G511" t="n">
+        <v>1818</v>
       </c>
     </row>
   </sheetData>
@@ -16310,7 +16560,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3072"/>
+  <dimension ref="A1:E3127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -60242,6 +60492,941 @@
       </c>
       <c r="E3072" t="n">
         <v>500</v>
+      </c>
+    </row>
+    <row r="3073">
+      <c r="A3073" t="n">
+        <v>0</v>
+      </c>
+      <c r="B3073" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3073" t="n">
+        <v>89</v>
+      </c>
+      <c r="D3073" t="n">
+        <v>27</v>
+      </c>
+      <c r="E3073" t="n">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="3074">
+      <c r="A3074" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3074" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3074" t="n">
+        <v>28</v>
+      </c>
+      <c r="D3074" t="n">
+        <v>79</v>
+      </c>
+      <c r="E3074" t="n">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="3075">
+      <c r="A3075" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3075" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3075" t="n">
+        <v>16</v>
+      </c>
+      <c r="D3075" t="n">
+        <v>53</v>
+      </c>
+      <c r="E3075" t="n">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="3076">
+      <c r="A3076" t="n">
+        <v>3</v>
+      </c>
+      <c r="B3076" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3076" t="n">
+        <v>41</v>
+      </c>
+      <c r="D3076" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3076" t="n">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="3077">
+      <c r="A3077" t="n">
+        <v>4</v>
+      </c>
+      <c r="B3077" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3077" t="n">
+        <v>91</v>
+      </c>
+      <c r="D3077" t="n">
+        <v>44</v>
+      </c>
+      <c r="E3077" t="n">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="3078">
+      <c r="A3078" t="n">
+        <v>5</v>
+      </c>
+      <c r="B3078" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3078" t="n">
+        <v>57</v>
+      </c>
+      <c r="D3078" t="n">
+        <v>10</v>
+      </c>
+      <c r="E3078" t="n">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="3079">
+      <c r="A3079" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3079" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3079" t="n">
+        <v>85</v>
+      </c>
+      <c r="D3079" t="n">
+        <v>38</v>
+      </c>
+      <c r="E3079" t="n">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="3080">
+      <c r="A3080" t="n">
+        <v>7</v>
+      </c>
+      <c r="B3080" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3080" t="n">
+        <v>85</v>
+      </c>
+      <c r="D3080" t="n">
+        <v>90</v>
+      </c>
+      <c r="E3080" t="n">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="3081">
+      <c r="A3081" t="n">
+        <v>8</v>
+      </c>
+      <c r="B3081" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3081" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3081" t="n">
+        <v>28</v>
+      </c>
+      <c r="E3081" t="n">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="3082">
+      <c r="A3082" t="n">
+        <v>9</v>
+      </c>
+      <c r="B3082" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3082" t="n">
+        <v>26</v>
+      </c>
+      <c r="D3082" t="n">
+        <v>85</v>
+      </c>
+      <c r="E3082" t="n">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="3083">
+      <c r="A3083" t="n">
+        <v>10</v>
+      </c>
+      <c r="B3083" t="n">
+        <v>7</v>
+      </c>
+      <c r="C3083" t="n">
+        <v>11</v>
+      </c>
+      <c r="D3083" t="n">
+        <v>75</v>
+      </c>
+      <c r="E3083" t="n">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="3084">
+      <c r="A3084" t="n">
+        <v>11</v>
+      </c>
+      <c r="B3084" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3084" t="n">
+        <v>84</v>
+      </c>
+      <c r="D3084" t="n">
+        <v>22</v>
+      </c>
+      <c r="E3084" t="n">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="3085">
+      <c r="A3085" t="n">
+        <v>12</v>
+      </c>
+      <c r="B3085" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3085" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3085" t="n">
+        <v>16</v>
+      </c>
+      <c r="E3085" t="n">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="3086">
+      <c r="A3086" t="n">
+        <v>13</v>
+      </c>
+      <c r="B3086" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3086" t="n">
+        <v>80</v>
+      </c>
+      <c r="D3086" t="n">
+        <v>21</v>
+      </c>
+      <c r="E3086" t="n">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="3087">
+      <c r="A3087" t="n">
+        <v>14</v>
+      </c>
+      <c r="B3087" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3087" t="n">
+        <v>50</v>
+      </c>
+      <c r="D3087" t="n">
+        <v>93</v>
+      </c>
+      <c r="E3087" t="n">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="3088">
+      <c r="A3088" t="n">
+        <v>15</v>
+      </c>
+      <c r="B3088" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3088" t="n">
+        <v>48</v>
+      </c>
+      <c r="D3088" t="n">
+        <v>100</v>
+      </c>
+      <c r="E3088" t="n">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="3089">
+      <c r="A3089" t="n">
+        <v>16</v>
+      </c>
+      <c r="B3089" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3089" t="n">
+        <v>54</v>
+      </c>
+      <c r="D3089" t="n">
+        <v>63</v>
+      </c>
+      <c r="E3089" t="n">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="3090">
+      <c r="A3090" t="n">
+        <v>17</v>
+      </c>
+      <c r="B3090" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3090" t="n">
+        <v>61</v>
+      </c>
+      <c r="D3090" t="n">
+        <v>94</v>
+      </c>
+      <c r="E3090" t="n">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="3091">
+      <c r="A3091" t="n">
+        <v>18</v>
+      </c>
+      <c r="B3091" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3091" t="n">
+        <v>67</v>
+      </c>
+      <c r="D3091" t="n">
+        <v>64</v>
+      </c>
+      <c r="E3091" t="n">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="3092">
+      <c r="A3092" t="n">
+        <v>19</v>
+      </c>
+      <c r="B3092" t="n">
+        <v>7</v>
+      </c>
+      <c r="C3092" t="n">
+        <v>61</v>
+      </c>
+      <c r="D3092" t="n">
+        <v>85</v>
+      </c>
+      <c r="E3092" t="n">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="3093">
+      <c r="A3093" t="n">
+        <v>20</v>
+      </c>
+      <c r="B3093" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3093" t="n">
+        <v>52</v>
+      </c>
+      <c r="D3093" t="n">
+        <v>36</v>
+      </c>
+      <c r="E3093" t="n">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="3094">
+      <c r="A3094" t="n">
+        <v>21</v>
+      </c>
+      <c r="B3094" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3094" t="n">
+        <v>47</v>
+      </c>
+      <c r="D3094" t="n">
+        <v>97</v>
+      </c>
+      <c r="E3094" t="n">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="3095">
+      <c r="A3095" t="n">
+        <v>22</v>
+      </c>
+      <c r="B3095" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3095" t="n">
+        <v>37</v>
+      </c>
+      <c r="D3095" t="n">
+        <v>69</v>
+      </c>
+      <c r="E3095" t="n">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="3096">
+      <c r="A3096" t="n">
+        <v>23</v>
+      </c>
+      <c r="B3096" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3096" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3096" t="n">
+        <v>35</v>
+      </c>
+      <c r="E3096" t="n">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="3097">
+      <c r="A3097" t="n">
+        <v>24</v>
+      </c>
+      <c r="B3097" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3097" t="n">
+        <v>66</v>
+      </c>
+      <c r="D3097" t="n">
+        <v>16</v>
+      </c>
+      <c r="E3097" t="n">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="3098">
+      <c r="A3098" t="n">
+        <v>25</v>
+      </c>
+      <c r="B3098" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3098" t="n">
+        <v>44</v>
+      </c>
+      <c r="D3098" t="n">
+        <v>61</v>
+      </c>
+      <c r="E3098" t="n">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="3099">
+      <c r="A3099" t="n">
+        <v>26</v>
+      </c>
+      <c r="B3099" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3099" t="n">
+        <v>34</v>
+      </c>
+      <c r="D3099" t="n">
+        <v>31</v>
+      </c>
+      <c r="E3099" t="n">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="3100">
+      <c r="A3100" t="n">
+        <v>27</v>
+      </c>
+      <c r="B3100" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3100" t="n">
+        <v>76</v>
+      </c>
+      <c r="D3100" t="n">
+        <v>57</v>
+      </c>
+      <c r="E3100" t="n">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="3101">
+      <c r="A3101" t="n">
+        <v>28</v>
+      </c>
+      <c r="B3101" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3101" t="n">
+        <v>83</v>
+      </c>
+      <c r="D3101" t="n">
+        <v>97</v>
+      </c>
+      <c r="E3101" t="n">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="3102">
+      <c r="A3102" t="n">
+        <v>29</v>
+      </c>
+      <c r="B3102" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3102" t="n">
+        <v>67</v>
+      </c>
+      <c r="D3102" t="n">
+        <v>36</v>
+      </c>
+      <c r="E3102" t="n">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="3103">
+      <c r="A3103" t="n">
+        <v>30</v>
+      </c>
+      <c r="B3103" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3103" t="n">
+        <v>9</v>
+      </c>
+      <c r="D3103" t="n">
+        <v>26</v>
+      </c>
+      <c r="E3103" t="n">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="3104">
+      <c r="A3104" t="n">
+        <v>31</v>
+      </c>
+      <c r="B3104" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3104" t="n">
+        <v>80</v>
+      </c>
+      <c r="D3104" t="n">
+        <v>88</v>
+      </c>
+      <c r="E3104" t="n">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="3105">
+      <c r="A3105" t="n">
+        <v>32</v>
+      </c>
+      <c r="B3105" t="n">
+        <v>7</v>
+      </c>
+      <c r="C3105" t="n">
+        <v>74</v>
+      </c>
+      <c r="D3105" t="n">
+        <v>51</v>
+      </c>
+      <c r="E3105" t="n">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="3106">
+      <c r="A3106" t="n">
+        <v>33</v>
+      </c>
+      <c r="B3106" t="n">
+        <v>8</v>
+      </c>
+      <c r="C3106" t="n">
+        <v>47</v>
+      </c>
+      <c r="D3106" t="n">
+        <v>15</v>
+      </c>
+      <c r="E3106" t="n">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="3107">
+      <c r="A3107" t="n">
+        <v>34</v>
+      </c>
+      <c r="B3107" t="n">
+        <v>9</v>
+      </c>
+      <c r="C3107" t="n">
+        <v>73</v>
+      </c>
+      <c r="D3107" t="n">
+        <v>26</v>
+      </c>
+      <c r="E3107" t="n">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="3108">
+      <c r="A3108" t="n">
+        <v>35</v>
+      </c>
+      <c r="B3108" t="n">
+        <v>10</v>
+      </c>
+      <c r="C3108" t="n">
+        <v>69</v>
+      </c>
+      <c r="D3108" t="n">
+        <v>98</v>
+      </c>
+      <c r="E3108" t="n">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="3109">
+      <c r="A3109" t="n">
+        <v>36</v>
+      </c>
+      <c r="B3109" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3109" t="n">
+        <v>8</v>
+      </c>
+      <c r="D3109" t="n">
+        <v>7</v>
+      </c>
+      <c r="E3109" t="n">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="3110">
+      <c r="A3110" t="n">
+        <v>37</v>
+      </c>
+      <c r="B3110" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3110" t="n">
+        <v>6</v>
+      </c>
+      <c r="D3110" t="n">
+        <v>33</v>
+      </c>
+      <c r="E3110" t="n">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="3111">
+      <c r="A3111" t="n">
+        <v>38</v>
+      </c>
+      <c r="B3111" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3111" t="n">
+        <v>66</v>
+      </c>
+      <c r="D3111" t="n">
+        <v>24</v>
+      </c>
+      <c r="E3111" t="n">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="3112">
+      <c r="A3112" t="n">
+        <v>39</v>
+      </c>
+      <c r="B3112" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3112" t="n">
+        <v>100</v>
+      </c>
+      <c r="D3112" t="n">
+        <v>47</v>
+      </c>
+      <c r="E3112" t="n">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="3113">
+      <c r="A3113" t="n">
+        <v>40</v>
+      </c>
+      <c r="B3113" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3113" t="n">
+        <v>9</v>
+      </c>
+      <c r="D3113" t="n">
+        <v>58</v>
+      </c>
+      <c r="E3113" t="n">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="3114">
+      <c r="A3114" t="n">
+        <v>41</v>
+      </c>
+      <c r="B3114" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3114" t="n">
+        <v>26</v>
+      </c>
+      <c r="D3114" t="n">
+        <v>33</v>
+      </c>
+      <c r="E3114" t="n">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="3115">
+      <c r="A3115" t="n">
+        <v>42</v>
+      </c>
+      <c r="B3115" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3115" t="n">
+        <v>35</v>
+      </c>
+      <c r="D3115" t="n">
+        <v>28</v>
+      </c>
+      <c r="E3115" t="n">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="3116">
+      <c r="A3116" t="n">
+        <v>43</v>
+      </c>
+      <c r="B3116" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3116" t="n">
+        <v>55</v>
+      </c>
+      <c r="D3116" t="n">
+        <v>79</v>
+      </c>
+      <c r="E3116" t="n">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="3117">
+      <c r="A3117" t="n">
+        <v>44</v>
+      </c>
+      <c r="B3117" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3117" t="n">
+        <v>8</v>
+      </c>
+      <c r="D3117" t="n">
+        <v>71</v>
+      </c>
+      <c r="E3117" t="n">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="3118">
+      <c r="A3118" t="n">
+        <v>45</v>
+      </c>
+      <c r="B3118" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3118" t="n">
+        <v>37</v>
+      </c>
+      <c r="D3118" t="n">
+        <v>36</v>
+      </c>
+      <c r="E3118" t="n">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="3119">
+      <c r="A3119" t="n">
+        <v>46</v>
+      </c>
+      <c r="B3119" t="n">
+        <v>7</v>
+      </c>
+      <c r="C3119" t="n">
+        <v>68</v>
+      </c>
+      <c r="D3119" t="n">
+        <v>41</v>
+      </c>
+      <c r="E3119" t="n">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="3120">
+      <c r="A3120" t="n">
+        <v>47</v>
+      </c>
+      <c r="B3120" t="n">
+        <v>8</v>
+      </c>
+      <c r="C3120" t="n">
+        <v>15</v>
+      </c>
+      <c r="D3120" t="n">
+        <v>97</v>
+      </c>
+      <c r="E3120" t="n">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="3121">
+      <c r="A3121" t="n">
+        <v>48</v>
+      </c>
+      <c r="B3121" t="n">
+        <v>9</v>
+      </c>
+      <c r="C3121" t="n">
+        <v>77</v>
+      </c>
+      <c r="D3121" t="n">
+        <v>52</v>
+      </c>
+      <c r="E3121" t="n">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="3122">
+      <c r="A3122" t="n">
+        <v>49</v>
+      </c>
+      <c r="B3122" t="n">
+        <v>10</v>
+      </c>
+      <c r="C3122" t="n">
+        <v>36</v>
+      </c>
+      <c r="D3122" t="n">
+        <v>14</v>
+      </c>
+      <c r="E3122" t="n">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="3123">
+      <c r="A3123" t="n">
+        <v>50</v>
+      </c>
+      <c r="B3123" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3123" t="n">
+        <v>74</v>
+      </c>
+      <c r="D3123" t="n">
+        <v>92</v>
+      </c>
+      <c r="E3123" t="n">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="3124">
+      <c r="A3124" t="n">
+        <v>51</v>
+      </c>
+      <c r="B3124" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3124" t="n">
+        <v>76</v>
+      </c>
+      <c r="D3124" t="n">
+        <v>92</v>
+      </c>
+      <c r="E3124" t="n">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="3125">
+      <c r="A3125" t="n">
+        <v>52</v>
+      </c>
+      <c r="B3125" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3125" t="n">
+        <v>12</v>
+      </c>
+      <c r="D3125" t="n">
+        <v>28</v>
+      </c>
+      <c r="E3125" t="n">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="3126">
+      <c r="A3126" t="n">
+        <v>53</v>
+      </c>
+      <c r="B3126" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3126" t="n">
+        <v>9</v>
+      </c>
+      <c r="D3126" t="n">
+        <v>77</v>
+      </c>
+      <c r="E3126" t="n">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="3127">
+      <c r="A3127" t="n">
+        <v>54</v>
+      </c>
+      <c r="B3127" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3127" t="n">
+        <v>13</v>
+      </c>
+      <c r="D3127" t="n">
+        <v>75</v>
+      </c>
+      <c r="E3127" t="n">
+        <v>510</v>
       </c>
     </row>
   </sheetData>
@@ -60255,7 +61440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F216"/>
+  <dimension ref="A1:F219"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66284,21 +67469,21 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Energy Power Radom</t>
+          <t>Kosmetyki Power</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>4609605632</t>
+          <t>7351525503</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Opole</t>
+          <t>Chojnice</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -66307,7 +67492,91 @@
         </is>
       </c>
       <c r="F216" t="n">
-        <v>18</v>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>222</v>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Life Pro</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>8550379790</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Słupsk</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>Medycyna estetyczna / klinika urody</t>
+        </is>
+      </c>
+      <c r="F217" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>223</v>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Kosmetyki Pro Team</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>1219812981</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Częstochowa</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>Drogeria specjalistyczna</t>
+        </is>
+      </c>
+      <c r="F218" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
+        <v>224</v>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Life Natura Ruda Śląska</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>9682322964</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Radom</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>Siłownia / klub sportowy</t>
+        </is>
+      </c>
+      <c r="F219" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/dane.xlsx
+++ b/dane.xlsx
@@ -3759,7 +3759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G511"/>
+  <dimension ref="A1:G521"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16547,6 +16547,256 @@
       </c>
       <c r="G511" t="n">
         <v>1818</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="n">
+        <v>511</v>
+      </c>
+      <c r="B512" s="2" t="n">
+        <v>46069</v>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>Nowe</t>
+        </is>
+      </c>
+      <c r="D512" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="E512" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F512" t="n">
+        <v>1</v>
+      </c>
+      <c r="G512" t="n">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="n">
+        <v>512</v>
+      </c>
+      <c r="B513" s="2" t="n">
+        <v>46083</v>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>Zwrot</t>
+        </is>
+      </c>
+      <c r="D513" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E513" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F513" t="n">
+        <v>3</v>
+      </c>
+      <c r="G513" t="n">
+        <v>2185</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="n">
+        <v>513</v>
+      </c>
+      <c r="B514" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>Zwrot</t>
+        </is>
+      </c>
+      <c r="D514" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E514" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F514" t="n">
+        <v>2</v>
+      </c>
+      <c r="G514" t="n">
+        <v>1605</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="n">
+        <v>514</v>
+      </c>
+      <c r="B515" s="2" t="n">
+        <v>46089</v>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>Zwrot</t>
+        </is>
+      </c>
+      <c r="D515" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="E515" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F515" t="n">
+        <v>3</v>
+      </c>
+      <c r="G515" t="n">
+        <v>3013</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="n">
+        <v>515</v>
+      </c>
+      <c r="B516" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>Nowe</t>
+        </is>
+      </c>
+      <c r="D516" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E516" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F516" t="n">
+        <v>4</v>
+      </c>
+      <c r="G516" t="n">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="n">
+        <v>516</v>
+      </c>
+      <c r="B517" s="2" t="n">
+        <v>46080</v>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>Wysłane</t>
+        </is>
+      </c>
+      <c r="D517" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="E517" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F517" t="n">
+        <v>4</v>
+      </c>
+      <c r="G517" t="n">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="n">
+        <v>517</v>
+      </c>
+      <c r="B518" s="2" t="n">
+        <v>46066</v>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>Dostarczone</t>
+        </is>
+      </c>
+      <c r="D518" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E518" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F518" t="n">
+        <v>2</v>
+      </c>
+      <c r="G518" t="n">
+        <v>2519</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="n">
+        <v>518</v>
+      </c>
+      <c r="B519" s="2" t="n">
+        <v>46068</v>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>Dostarczone</t>
+        </is>
+      </c>
+      <c r="D519" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="E519" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F519" t="n">
+        <v>1</v>
+      </c>
+      <c r="G519" t="n">
+        <v>1421</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="n">
+        <v>519</v>
+      </c>
+      <c r="B520" s="2" t="n">
+        <v>46078</v>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>Wysłane</t>
+        </is>
+      </c>
+      <c r="D520" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="E520" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F520" t="n">
+        <v>3</v>
+      </c>
+      <c r="G520" t="n">
+        <v>2275</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="n">
+        <v>520</v>
+      </c>
+      <c r="B521" s="2" t="n">
+        <v>46090</v>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>Nowe</t>
+        </is>
+      </c>
+      <c r="D521" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="E521" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F521" t="n">
+        <v>2</v>
+      </c>
+      <c r="G521" t="n">
+        <v>1696</v>
       </c>
     </row>
   </sheetData>
@@ -16560,7 +16810,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3127"/>
+  <dimension ref="A1:E3202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61427,6 +61677,1281 @@
       </c>
       <c r="E3127" t="n">
         <v>510</v>
+      </c>
+    </row>
+    <row r="3128">
+      <c r="A3128" t="n">
+        <v>0</v>
+      </c>
+      <c r="B3128" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3128" t="n">
+        <v>79</v>
+      </c>
+      <c r="D3128" t="n">
+        <v>31</v>
+      </c>
+      <c r="E3128" t="n">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="3129">
+      <c r="A3129" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3129" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3129" t="n">
+        <v>11</v>
+      </c>
+      <c r="D3129" t="n">
+        <v>69</v>
+      </c>
+      <c r="E3129" t="n">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="3130">
+      <c r="A3130" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3130" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3130" t="n">
+        <v>86</v>
+      </c>
+      <c r="D3130" t="n">
+        <v>23</v>
+      </c>
+      <c r="E3130" t="n">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="3131">
+      <c r="A3131" t="n">
+        <v>3</v>
+      </c>
+      <c r="B3131" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3131" t="n">
+        <v>54</v>
+      </c>
+      <c r="D3131" t="n">
+        <v>45</v>
+      </c>
+      <c r="E3131" t="n">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="3132">
+      <c r="A3132" t="n">
+        <v>4</v>
+      </c>
+      <c r="B3132" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3132" t="n">
+        <v>15</v>
+      </c>
+      <c r="D3132" t="n">
+        <v>46</v>
+      </c>
+      <c r="E3132" t="n">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="3133">
+      <c r="A3133" t="n">
+        <v>5</v>
+      </c>
+      <c r="B3133" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3133" t="n">
+        <v>73</v>
+      </c>
+      <c r="D3133" t="n">
+        <v>19</v>
+      </c>
+      <c r="E3133" t="n">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="3134">
+      <c r="A3134" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3134" t="n">
+        <v>7</v>
+      </c>
+      <c r="C3134" t="n">
+        <v>9</v>
+      </c>
+      <c r="D3134" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3134" t="n">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="3135">
+      <c r="A3135" t="n">
+        <v>7</v>
+      </c>
+      <c r="B3135" t="n">
+        <v>8</v>
+      </c>
+      <c r="C3135" t="n">
+        <v>48</v>
+      </c>
+      <c r="D3135" t="n">
+        <v>44</v>
+      </c>
+      <c r="E3135" t="n">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="3136">
+      <c r="A3136" t="n">
+        <v>8</v>
+      </c>
+      <c r="B3136" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3136" t="n">
+        <v>8</v>
+      </c>
+      <c r="D3136" t="n">
+        <v>72</v>
+      </c>
+      <c r="E3136" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="3137">
+      <c r="A3137" t="n">
+        <v>9</v>
+      </c>
+      <c r="B3137" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3137" t="n">
+        <v>91</v>
+      </c>
+      <c r="D3137" t="n">
+        <v>72</v>
+      </c>
+      <c r="E3137" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="3138">
+      <c r="A3138" t="n">
+        <v>10</v>
+      </c>
+      <c r="B3138" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3138" t="n">
+        <v>28</v>
+      </c>
+      <c r="D3138" t="n">
+        <v>32</v>
+      </c>
+      <c r="E3138" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="3139">
+      <c r="A3139" t="n">
+        <v>11</v>
+      </c>
+      <c r="B3139" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3139" t="n">
+        <v>80</v>
+      </c>
+      <c r="D3139" t="n">
+        <v>98</v>
+      </c>
+      <c r="E3139" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="3140">
+      <c r="A3140" t="n">
+        <v>12</v>
+      </c>
+      <c r="B3140" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3140" t="n">
+        <v>38</v>
+      </c>
+      <c r="D3140" t="n">
+        <v>18</v>
+      </c>
+      <c r="E3140" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="3141">
+      <c r="A3141" t="n">
+        <v>13</v>
+      </c>
+      <c r="B3141" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3141" t="n">
+        <v>69</v>
+      </c>
+      <c r="D3141" t="n">
+        <v>47</v>
+      </c>
+      <c r="E3141" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="3142">
+      <c r="A3142" t="n">
+        <v>14</v>
+      </c>
+      <c r="B3142" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3142" t="n">
+        <v>13</v>
+      </c>
+      <c r="D3142" t="n">
+        <v>61</v>
+      </c>
+      <c r="E3142" t="n">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="3143">
+      <c r="A3143" t="n">
+        <v>15</v>
+      </c>
+      <c r="B3143" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3143" t="n">
+        <v>61</v>
+      </c>
+      <c r="D3143" t="n">
+        <v>62</v>
+      </c>
+      <c r="E3143" t="n">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="3144">
+      <c r="A3144" t="n">
+        <v>16</v>
+      </c>
+      <c r="B3144" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3144" t="n">
+        <v>49</v>
+      </c>
+      <c r="D3144" t="n">
+        <v>98</v>
+      </c>
+      <c r="E3144" t="n">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="3145">
+      <c r="A3145" t="n">
+        <v>17</v>
+      </c>
+      <c r="B3145" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3145" t="n">
+        <v>11</v>
+      </c>
+      <c r="D3145" t="n">
+        <v>80</v>
+      </c>
+      <c r="E3145" t="n">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="3146">
+      <c r="A3146" t="n">
+        <v>18</v>
+      </c>
+      <c r="B3146" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3146" t="n">
+        <v>52</v>
+      </c>
+      <c r="D3146" t="n">
+        <v>44</v>
+      </c>
+      <c r="E3146" t="n">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="3147">
+      <c r="A3147" t="n">
+        <v>19</v>
+      </c>
+      <c r="B3147" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3147" t="n">
+        <v>25</v>
+      </c>
+      <c r="D3147" t="n">
+        <v>77</v>
+      </c>
+      <c r="E3147" t="n">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="3148">
+      <c r="A3148" t="n">
+        <v>20</v>
+      </c>
+      <c r="B3148" t="n">
+        <v>7</v>
+      </c>
+      <c r="C3148" t="n">
+        <v>81</v>
+      </c>
+      <c r="D3148" t="n">
+        <v>63</v>
+      </c>
+      <c r="E3148" t="n">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="3149">
+      <c r="A3149" t="n">
+        <v>21</v>
+      </c>
+      <c r="B3149" t="n">
+        <v>8</v>
+      </c>
+      <c r="C3149" t="n">
+        <v>99</v>
+      </c>
+      <c r="D3149" t="n">
+        <v>84</v>
+      </c>
+      <c r="E3149" t="n">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="3150">
+      <c r="A3150" t="n">
+        <v>22</v>
+      </c>
+      <c r="B3150" t="n">
+        <v>9</v>
+      </c>
+      <c r="C3150" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3150" t="n">
+        <v>91</v>
+      </c>
+      <c r="E3150" t="n">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="3151">
+      <c r="A3151" t="n">
+        <v>23</v>
+      </c>
+      <c r="B3151" t="n">
+        <v>10</v>
+      </c>
+      <c r="C3151" t="n">
+        <v>85</v>
+      </c>
+      <c r="D3151" t="n">
+        <v>9</v>
+      </c>
+      <c r="E3151" t="n">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="3152">
+      <c r="A3152" t="n">
+        <v>24</v>
+      </c>
+      <c r="B3152" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3152" t="n">
+        <v>67</v>
+      </c>
+      <c r="D3152" t="n">
+        <v>37</v>
+      </c>
+      <c r="E3152" t="n">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="3153">
+      <c r="A3153" t="n">
+        <v>25</v>
+      </c>
+      <c r="B3153" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3153" t="n">
+        <v>89</v>
+      </c>
+      <c r="D3153" t="n">
+        <v>21</v>
+      </c>
+      <c r="E3153" t="n">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="3154">
+      <c r="A3154" t="n">
+        <v>26</v>
+      </c>
+      <c r="B3154" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3154" t="n">
+        <v>26</v>
+      </c>
+      <c r="D3154" t="n">
+        <v>95</v>
+      </c>
+      <c r="E3154" t="n">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="3155">
+      <c r="A3155" t="n">
+        <v>27</v>
+      </c>
+      <c r="B3155" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3155" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3155" t="n">
+        <v>80</v>
+      </c>
+      <c r="E3155" t="n">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="3156">
+      <c r="A3156" t="n">
+        <v>28</v>
+      </c>
+      <c r="B3156" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3156" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3156" t="n">
+        <v>16</v>
+      </c>
+      <c r="E3156" t="n">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="3157">
+      <c r="A3157" t="n">
+        <v>29</v>
+      </c>
+      <c r="B3157" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3157" t="n">
+        <v>71</v>
+      </c>
+      <c r="D3157" t="n">
+        <v>26</v>
+      </c>
+      <c r="E3157" t="n">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="3158">
+      <c r="A3158" t="n">
+        <v>30</v>
+      </c>
+      <c r="B3158" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3158" t="n">
+        <v>70</v>
+      </c>
+      <c r="D3158" t="n">
+        <v>91</v>
+      </c>
+      <c r="E3158" t="n">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="3159">
+      <c r="A3159" t="n">
+        <v>31</v>
+      </c>
+      <c r="B3159" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3159" t="n">
+        <v>55</v>
+      </c>
+      <c r="D3159" t="n">
+        <v>83</v>
+      </c>
+      <c r="E3159" t="n">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="3160">
+      <c r="A3160" t="n">
+        <v>32</v>
+      </c>
+      <c r="B3160" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3160" t="n">
+        <v>87</v>
+      </c>
+      <c r="D3160" t="n">
+        <v>54</v>
+      </c>
+      <c r="E3160" t="n">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="3161">
+      <c r="A3161" t="n">
+        <v>33</v>
+      </c>
+      <c r="B3161" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3161" t="n">
+        <v>54</v>
+      </c>
+      <c r="D3161" t="n">
+        <v>20</v>
+      </c>
+      <c r="E3161" t="n">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="3162">
+      <c r="A3162" t="n">
+        <v>34</v>
+      </c>
+      <c r="B3162" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3162" t="n">
+        <v>83</v>
+      </c>
+      <c r="D3162" t="n">
+        <v>9</v>
+      </c>
+      <c r="E3162" t="n">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="3163">
+      <c r="A3163" t="n">
+        <v>35</v>
+      </c>
+      <c r="B3163" t="n">
+        <v>7</v>
+      </c>
+      <c r="C3163" t="n">
+        <v>98</v>
+      </c>
+      <c r="D3163" t="n">
+        <v>53</v>
+      </c>
+      <c r="E3163" t="n">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="3164">
+      <c r="A3164" t="n">
+        <v>36</v>
+      </c>
+      <c r="B3164" t="n">
+        <v>8</v>
+      </c>
+      <c r="C3164" t="n">
+        <v>49</v>
+      </c>
+      <c r="D3164" t="n">
+        <v>79</v>
+      </c>
+      <c r="E3164" t="n">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="3165">
+      <c r="A3165" t="n">
+        <v>37</v>
+      </c>
+      <c r="B3165" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3165" t="n">
+        <v>98</v>
+      </c>
+      <c r="D3165" t="n">
+        <v>74</v>
+      </c>
+      <c r="E3165" t="n">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="3166">
+      <c r="A3166" t="n">
+        <v>38</v>
+      </c>
+      <c r="B3166" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3166" t="n">
+        <v>64</v>
+      </c>
+      <c r="D3166" t="n">
+        <v>63</v>
+      </c>
+      <c r="E3166" t="n">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="3167">
+      <c r="A3167" t="n">
+        <v>39</v>
+      </c>
+      <c r="B3167" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3167" t="n">
+        <v>78</v>
+      </c>
+      <c r="D3167" t="n">
+        <v>89</v>
+      </c>
+      <c r="E3167" t="n">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="3168">
+      <c r="A3168" t="n">
+        <v>40</v>
+      </c>
+      <c r="B3168" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3168" t="n">
+        <v>29</v>
+      </c>
+      <c r="D3168" t="n">
+        <v>20</v>
+      </c>
+      <c r="E3168" t="n">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="3169">
+      <c r="A3169" t="n">
+        <v>41</v>
+      </c>
+      <c r="B3169" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3169" t="n">
+        <v>51</v>
+      </c>
+      <c r="D3169" t="n">
+        <v>76</v>
+      </c>
+      <c r="E3169" t="n">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="3170">
+      <c r="A3170" t="n">
+        <v>42</v>
+      </c>
+      <c r="B3170" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3170" t="n">
+        <v>81</v>
+      </c>
+      <c r="D3170" t="n">
+        <v>44</v>
+      </c>
+      <c r="E3170" t="n">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="3171">
+      <c r="A3171" t="n">
+        <v>43</v>
+      </c>
+      <c r="B3171" t="n">
+        <v>7</v>
+      </c>
+      <c r="C3171" t="n">
+        <v>6</v>
+      </c>
+      <c r="D3171" t="n">
+        <v>86</v>
+      </c>
+      <c r="E3171" t="n">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="3172">
+      <c r="A3172" t="n">
+        <v>44</v>
+      </c>
+      <c r="B3172" t="n">
+        <v>8</v>
+      </c>
+      <c r="C3172" t="n">
+        <v>31</v>
+      </c>
+      <c r="D3172" t="n">
+        <v>62</v>
+      </c>
+      <c r="E3172" t="n">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="3173">
+      <c r="A3173" t="n">
+        <v>45</v>
+      </c>
+      <c r="B3173" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3173" t="n">
+        <v>84</v>
+      </c>
+      <c r="D3173" t="n">
+        <v>94</v>
+      </c>
+      <c r="E3173" t="n">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="3174">
+      <c r="A3174" t="n">
+        <v>46</v>
+      </c>
+      <c r="B3174" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3174" t="n">
+        <v>62</v>
+      </c>
+      <c r="D3174" t="n">
+        <v>96</v>
+      </c>
+      <c r="E3174" t="n">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="3175">
+      <c r="A3175" t="n">
+        <v>47</v>
+      </c>
+      <c r="B3175" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3175" t="n">
+        <v>100</v>
+      </c>
+      <c r="D3175" t="n">
+        <v>29</v>
+      </c>
+      <c r="E3175" t="n">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="3176">
+      <c r="A3176" t="n">
+        <v>48</v>
+      </c>
+      <c r="B3176" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3176" t="n">
+        <v>9</v>
+      </c>
+      <c r="D3176" t="n">
+        <v>95</v>
+      </c>
+      <c r="E3176" t="n">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="3177">
+      <c r="A3177" t="n">
+        <v>49</v>
+      </c>
+      <c r="B3177" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3177" t="n">
+        <v>45</v>
+      </c>
+      <c r="D3177" t="n">
+        <v>13</v>
+      </c>
+      <c r="E3177" t="n">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="3178">
+      <c r="A3178" t="n">
+        <v>50</v>
+      </c>
+      <c r="B3178" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3178" t="n">
+        <v>64</v>
+      </c>
+      <c r="D3178" t="n">
+        <v>71</v>
+      </c>
+      <c r="E3178" t="n">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="3179">
+      <c r="A3179" t="n">
+        <v>51</v>
+      </c>
+      <c r="B3179" t="n">
+        <v>7</v>
+      </c>
+      <c r="C3179" t="n">
+        <v>59</v>
+      </c>
+      <c r="D3179" t="n">
+        <v>6</v>
+      </c>
+      <c r="E3179" t="n">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="3180">
+      <c r="A3180" t="n">
+        <v>52</v>
+      </c>
+      <c r="B3180" t="n">
+        <v>8</v>
+      </c>
+      <c r="C3180" t="n">
+        <v>41</v>
+      </c>
+      <c r="D3180" t="n">
+        <v>40</v>
+      </c>
+      <c r="E3180" t="n">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="3181">
+      <c r="A3181" t="n">
+        <v>53</v>
+      </c>
+      <c r="B3181" t="n">
+        <v>9</v>
+      </c>
+      <c r="C3181" t="n">
+        <v>94</v>
+      </c>
+      <c r="D3181" t="n">
+        <v>65</v>
+      </c>
+      <c r="E3181" t="n">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="3182">
+      <c r="A3182" t="n">
+        <v>54</v>
+      </c>
+      <c r="B3182" t="n">
+        <v>10</v>
+      </c>
+      <c r="C3182" t="n">
+        <v>12</v>
+      </c>
+      <c r="D3182" t="n">
+        <v>17</v>
+      </c>
+      <c r="E3182" t="n">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="3183">
+      <c r="A3183" t="n">
+        <v>55</v>
+      </c>
+      <c r="B3183" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3183" t="n">
+        <v>70</v>
+      </c>
+      <c r="D3183" t="n">
+        <v>14</v>
+      </c>
+      <c r="E3183" t="n">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="3184">
+      <c r="A3184" t="n">
+        <v>56</v>
+      </c>
+      <c r="B3184" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3184" t="n">
+        <v>50</v>
+      </c>
+      <c r="D3184" t="n">
+        <v>47</v>
+      </c>
+      <c r="E3184" t="n">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="3185">
+      <c r="A3185" t="n">
+        <v>57</v>
+      </c>
+      <c r="B3185" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3185" t="n">
+        <v>34</v>
+      </c>
+      <c r="D3185" t="n">
+        <v>90</v>
+      </c>
+      <c r="E3185" t="n">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="3186">
+      <c r="A3186" t="n">
+        <v>58</v>
+      </c>
+      <c r="B3186" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3186" t="n">
+        <v>85</v>
+      </c>
+      <c r="D3186" t="n">
+        <v>43</v>
+      </c>
+      <c r="E3186" t="n">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="3187">
+      <c r="A3187" t="n">
+        <v>59</v>
+      </c>
+      <c r="B3187" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3187" t="n">
+        <v>100</v>
+      </c>
+      <c r="D3187" t="n">
+        <v>92</v>
+      </c>
+      <c r="E3187" t="n">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="3188">
+      <c r="A3188" t="n">
+        <v>60</v>
+      </c>
+      <c r="B3188" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3188" t="n">
+        <v>36</v>
+      </c>
+      <c r="D3188" t="n">
+        <v>17</v>
+      </c>
+      <c r="E3188" t="n">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="3189">
+      <c r="A3189" t="n">
+        <v>61</v>
+      </c>
+      <c r="B3189" t="n">
+        <v>7</v>
+      </c>
+      <c r="C3189" t="n">
+        <v>62</v>
+      </c>
+      <c r="D3189" t="n">
+        <v>8</v>
+      </c>
+      <c r="E3189" t="n">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="3190">
+      <c r="A3190" t="n">
+        <v>62</v>
+      </c>
+      <c r="B3190" t="n">
+        <v>8</v>
+      </c>
+      <c r="C3190" t="n">
+        <v>63</v>
+      </c>
+      <c r="D3190" t="n">
+        <v>92</v>
+      </c>
+      <c r="E3190" t="n">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="3191">
+      <c r="A3191" t="n">
+        <v>63</v>
+      </c>
+      <c r="B3191" t="n">
+        <v>9</v>
+      </c>
+      <c r="C3191" t="n">
+        <v>64</v>
+      </c>
+      <c r="D3191" t="n">
+        <v>56</v>
+      </c>
+      <c r="E3191" t="n">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="3192">
+      <c r="A3192" t="n">
+        <v>64</v>
+      </c>
+      <c r="B3192" t="n">
+        <v>10</v>
+      </c>
+      <c r="C3192" t="n">
+        <v>32</v>
+      </c>
+      <c r="D3192" t="n">
+        <v>4</v>
+      </c>
+      <c r="E3192" t="n">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="3193">
+      <c r="A3193" t="n">
+        <v>65</v>
+      </c>
+      <c r="B3193" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3193" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3193" t="n">
+        <v>67</v>
+      </c>
+      <c r="E3193" t="n">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="3194">
+      <c r="A3194" t="n">
+        <v>66</v>
+      </c>
+      <c r="B3194" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3194" t="n">
+        <v>31</v>
+      </c>
+      <c r="D3194" t="n">
+        <v>87</v>
+      </c>
+      <c r="E3194" t="n">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="3195">
+      <c r="A3195" t="n">
+        <v>67</v>
+      </c>
+      <c r="B3195" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3195" t="n">
+        <v>47</v>
+      </c>
+      <c r="D3195" t="n">
+        <v>100</v>
+      </c>
+      <c r="E3195" t="n">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="3196">
+      <c r="A3196" t="n">
+        <v>68</v>
+      </c>
+      <c r="B3196" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3196" t="n">
+        <v>43</v>
+      </c>
+      <c r="D3196" t="n">
+        <v>90</v>
+      </c>
+      <c r="E3196" t="n">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="3197">
+      <c r="A3197" t="n">
+        <v>69</v>
+      </c>
+      <c r="B3197" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3197" t="n">
+        <v>80</v>
+      </c>
+      <c r="D3197" t="n">
+        <v>40</v>
+      </c>
+      <c r="E3197" t="n">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="3198">
+      <c r="A3198" t="n">
+        <v>70</v>
+      </c>
+      <c r="B3198" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3198" t="n">
+        <v>12</v>
+      </c>
+      <c r="D3198" t="n">
+        <v>71</v>
+      </c>
+      <c r="E3198" t="n">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="3199">
+      <c r="A3199" t="n">
+        <v>71</v>
+      </c>
+      <c r="B3199" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3199" t="n">
+        <v>86</v>
+      </c>
+      <c r="D3199" t="n">
+        <v>43</v>
+      </c>
+      <c r="E3199" t="n">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="3200">
+      <c r="A3200" t="n">
+        <v>72</v>
+      </c>
+      <c r="B3200" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3200" t="n">
+        <v>58</v>
+      </c>
+      <c r="D3200" t="n">
+        <v>69</v>
+      </c>
+      <c r="E3200" t="n">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="3201">
+      <c r="A3201" t="n">
+        <v>73</v>
+      </c>
+      <c r="B3201" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3201" t="n">
+        <v>91</v>
+      </c>
+      <c r="D3201" t="n">
+        <v>49</v>
+      </c>
+      <c r="E3201" t="n">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="3202">
+      <c r="A3202" t="n">
+        <v>74</v>
+      </c>
+      <c r="B3202" t="n">
+        <v>7</v>
+      </c>
+      <c r="C3202" t="n">
+        <v>18</v>
+      </c>
+      <c r="D3202" t="n">
+        <v>28</v>
+      </c>
+      <c r="E3202" t="n">
+        <v>520</v>
       </c>
     </row>
   </sheetData>
@@ -61440,7 +62965,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F219"/>
+  <dimension ref="A1:F222"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67553,30 +69078,114 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Life Natura Ruda Śląska</t>
+          <t>Strong Vital Zabrze</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>9682322964</t>
+          <t>7023020714</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>Radom</t>
+          <t>Lubin</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Siłownia / klub sportowy</t>
+          <t>Gabinet dietetyczny</t>
         </is>
       </c>
       <c r="F219" t="n">
-        <v>4</v>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>226</v>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Muscle Kalisz</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>4181823517</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Biała Podlaska</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>Supermarket / drogeria wielkopowierzchniowa</t>
+        </is>
+      </c>
+      <c r="F220" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>227</v>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Fitness Bielsko-Biała</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>7179838855</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Płock</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>Medycyna estetyczna / klinika urody</t>
+        </is>
+      </c>
+      <c r="F221" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
+        <v>228</v>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Eko Wałbrzych</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>2995586494</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>Pszczyna</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>Drogeria specjalistyczna</t>
+        </is>
+      </c>
+      <c r="F222" t="n">
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/dane.xlsx
+++ b/dane.xlsx
@@ -3759,7 +3759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G521"/>
+  <dimension ref="A1:G531"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16797,6 +16797,256 @@
       </c>
       <c r="G521" t="n">
         <v>1696</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="n">
+        <v>521</v>
+      </c>
+      <c r="B522" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>Nowe</t>
+        </is>
+      </c>
+      <c r="D522" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="E522" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F522" t="n">
+        <v>1</v>
+      </c>
+      <c r="G522" t="n">
+        <v>1788</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="n">
+        <v>522</v>
+      </c>
+      <c r="B523" s="2" t="n">
+        <v>46090</v>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>Nowe</t>
+        </is>
+      </c>
+      <c r="D523" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="E523" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F523" t="n">
+        <v>2</v>
+      </c>
+      <c r="G523" t="n">
+        <v>1273</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="n">
+        <v>523</v>
+      </c>
+      <c r="B524" s="2" t="n">
+        <v>46072</v>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>Wysłane</t>
+        </is>
+      </c>
+      <c r="D524" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E524" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F524" t="n">
+        <v>4</v>
+      </c>
+      <c r="G524" t="n">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="n">
+        <v>524</v>
+      </c>
+      <c r="B525" s="2" t="n">
+        <v>46089</v>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>Zwrot</t>
+        </is>
+      </c>
+      <c r="D525" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="E525" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F525" t="n">
+        <v>4</v>
+      </c>
+      <c r="G525" t="n">
+        <v>1799</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="n">
+        <v>525</v>
+      </c>
+      <c r="B526" s="2" t="n">
+        <v>46079</v>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>Dostarczone</t>
+        </is>
+      </c>
+      <c r="D526" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="E526" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F526" t="n">
+        <v>3</v>
+      </c>
+      <c r="G526" t="n">
+        <v>3080</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="n">
+        <v>526</v>
+      </c>
+      <c r="B527" s="2" t="n">
+        <v>46068</v>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>Dostarczone</t>
+        </is>
+      </c>
+      <c r="D527" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="E527" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F527" t="n">
+        <v>4</v>
+      </c>
+      <c r="G527" t="n">
+        <v>1033</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="n">
+        <v>527</v>
+      </c>
+      <c r="B528" s="2" t="n">
+        <v>46071</v>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>Zwrot</t>
+        </is>
+      </c>
+      <c r="D528" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E528" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F528" t="n">
+        <v>3</v>
+      </c>
+      <c r="G528" t="n">
+        <v>2419</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="n">
+        <v>528</v>
+      </c>
+      <c r="B529" s="2" t="n">
+        <v>46070</v>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>Zwrot</t>
+        </is>
+      </c>
+      <c r="D529" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E529" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F529" t="n">
+        <v>2</v>
+      </c>
+      <c r="G529" t="n">
+        <v>1452</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="n">
+        <v>529</v>
+      </c>
+      <c r="B530" s="2" t="n">
+        <v>46067</v>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>Dostarczone</t>
+        </is>
+      </c>
+      <c r="D530" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E530" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F530" t="n">
+        <v>2</v>
+      </c>
+      <c r="G530" t="n">
+        <v>3026</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="n">
+        <v>530</v>
+      </c>
+      <c r="B531" s="2" t="n">
+        <v>46081</v>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>Dostarczone</t>
+        </is>
+      </c>
+      <c r="D531" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="E531" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F531" t="n">
+        <v>4</v>
+      </c>
+      <c r="G531" t="n">
+        <v>199</v>
       </c>
     </row>
   </sheetData>
@@ -16810,7 +17060,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3202"/>
+  <dimension ref="A1:E3255"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62952,6 +63202,907 @@
       </c>
       <c r="E3202" t="n">
         <v>520</v>
+      </c>
+    </row>
+    <row r="3203">
+      <c r="A3203" t="n">
+        <v>0</v>
+      </c>
+      <c r="B3203" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3203" t="n">
+        <v>55</v>
+      </c>
+      <c r="D3203" t="n">
+        <v>56</v>
+      </c>
+      <c r="E3203" t="n">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="3204">
+      <c r="A3204" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3204" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3204" t="n">
+        <v>43</v>
+      </c>
+      <c r="D3204" t="n">
+        <v>68</v>
+      </c>
+      <c r="E3204" t="n">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="3205">
+      <c r="A3205" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3205" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3205" t="n">
+        <v>75</v>
+      </c>
+      <c r="D3205" t="n">
+        <v>71</v>
+      </c>
+      <c r="E3205" t="n">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="3206">
+      <c r="A3206" t="n">
+        <v>3</v>
+      </c>
+      <c r="B3206" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3206" t="n">
+        <v>44</v>
+      </c>
+      <c r="D3206" t="n">
+        <v>90</v>
+      </c>
+      <c r="E3206" t="n">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="3207">
+      <c r="A3207" t="n">
+        <v>4</v>
+      </c>
+      <c r="B3207" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3207" t="n">
+        <v>10</v>
+      </c>
+      <c r="D3207" t="n">
+        <v>39</v>
+      </c>
+      <c r="E3207" t="n">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="3208">
+      <c r="A3208" t="n">
+        <v>5</v>
+      </c>
+      <c r="B3208" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3208" t="n">
+        <v>75</v>
+      </c>
+      <c r="D3208" t="n">
+        <v>35</v>
+      </c>
+      <c r="E3208" t="n">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="3209">
+      <c r="A3209" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3209" t="n">
+        <v>7</v>
+      </c>
+      <c r="C3209" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3209" t="n">
+        <v>61</v>
+      </c>
+      <c r="E3209" t="n">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="3210">
+      <c r="A3210" t="n">
+        <v>7</v>
+      </c>
+      <c r="B3210" t="n">
+        <v>8</v>
+      </c>
+      <c r="C3210" t="n">
+        <v>35</v>
+      </c>
+      <c r="D3210" t="n">
+        <v>10</v>
+      </c>
+      <c r="E3210" t="n">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="3211">
+      <c r="A3211" t="n">
+        <v>8</v>
+      </c>
+      <c r="B3211" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3211" t="n">
+        <v>11</v>
+      </c>
+      <c r="D3211" t="n">
+        <v>20</v>
+      </c>
+      <c r="E3211" t="n">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="3212">
+      <c r="A3212" t="n">
+        <v>9</v>
+      </c>
+      <c r="B3212" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3212" t="n">
+        <v>16</v>
+      </c>
+      <c r="D3212" t="n">
+        <v>62</v>
+      </c>
+      <c r="E3212" t="n">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="3213">
+      <c r="A3213" t="n">
+        <v>10</v>
+      </c>
+      <c r="B3213" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3213" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3213" t="n">
+        <v>12</v>
+      </c>
+      <c r="E3213" t="n">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="3214">
+      <c r="A3214" t="n">
+        <v>11</v>
+      </c>
+      <c r="B3214" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3214" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3214" t="n">
+        <v>42</v>
+      </c>
+      <c r="E3214" t="n">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="3215">
+      <c r="A3215" t="n">
+        <v>12</v>
+      </c>
+      <c r="B3215" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3215" t="n">
+        <v>50</v>
+      </c>
+      <c r="D3215" t="n">
+        <v>98</v>
+      </c>
+      <c r="E3215" t="n">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="3216">
+      <c r="A3216" t="n">
+        <v>13</v>
+      </c>
+      <c r="B3216" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3216" t="n">
+        <v>6</v>
+      </c>
+      <c r="D3216" t="n">
+        <v>35</v>
+      </c>
+      <c r="E3216" t="n">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="3217">
+      <c r="A3217" t="n">
+        <v>14</v>
+      </c>
+      <c r="B3217" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3217" t="n">
+        <v>32</v>
+      </c>
+      <c r="D3217" t="n">
+        <v>66</v>
+      </c>
+      <c r="E3217" t="n">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="3218">
+      <c r="A3218" t="n">
+        <v>15</v>
+      </c>
+      <c r="B3218" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3218" t="n">
+        <v>27</v>
+      </c>
+      <c r="D3218" t="n">
+        <v>57</v>
+      </c>
+      <c r="E3218" t="n">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="3219">
+      <c r="A3219" t="n">
+        <v>16</v>
+      </c>
+      <c r="B3219" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3219" t="n">
+        <v>51</v>
+      </c>
+      <c r="D3219" t="n">
+        <v>41</v>
+      </c>
+      <c r="E3219" t="n">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="3220">
+      <c r="A3220" t="n">
+        <v>17</v>
+      </c>
+      <c r="B3220" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3220" t="n">
+        <v>34</v>
+      </c>
+      <c r="D3220" t="n">
+        <v>73</v>
+      </c>
+      <c r="E3220" t="n">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="3221">
+      <c r="A3221" t="n">
+        <v>18</v>
+      </c>
+      <c r="B3221" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3221" t="n">
+        <v>14</v>
+      </c>
+      <c r="D3221" t="n">
+        <v>94</v>
+      </c>
+      <c r="E3221" t="n">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="3222">
+      <c r="A3222" t="n">
+        <v>19</v>
+      </c>
+      <c r="B3222" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3222" t="n">
+        <v>87</v>
+      </c>
+      <c r="D3222" t="n">
+        <v>16</v>
+      </c>
+      <c r="E3222" t="n">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="3223">
+      <c r="A3223" t="n">
+        <v>20</v>
+      </c>
+      <c r="B3223" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3223" t="n">
+        <v>65</v>
+      </c>
+      <c r="D3223" t="n">
+        <v>34</v>
+      </c>
+      <c r="E3223" t="n">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="3224">
+      <c r="A3224" t="n">
+        <v>21</v>
+      </c>
+      <c r="B3224" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3224" t="n">
+        <v>55</v>
+      </c>
+      <c r="D3224" t="n">
+        <v>93</v>
+      </c>
+      <c r="E3224" t="n">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="3225">
+      <c r="A3225" t="n">
+        <v>22</v>
+      </c>
+      <c r="B3225" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3225" t="n">
+        <v>57</v>
+      </c>
+      <c r="D3225" t="n">
+        <v>65</v>
+      </c>
+      <c r="E3225" t="n">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="3226">
+      <c r="A3226" t="n">
+        <v>23</v>
+      </c>
+      <c r="B3226" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3226" t="n">
+        <v>42</v>
+      </c>
+      <c r="D3226" t="n">
+        <v>35</v>
+      </c>
+      <c r="E3226" t="n">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="3227">
+      <c r="A3227" t="n">
+        <v>24</v>
+      </c>
+      <c r="B3227" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3227" t="n">
+        <v>34</v>
+      </c>
+      <c r="D3227" t="n">
+        <v>17</v>
+      </c>
+      <c r="E3227" t="n">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="3228">
+      <c r="A3228" t="n">
+        <v>25</v>
+      </c>
+      <c r="B3228" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3228" t="n">
+        <v>55</v>
+      </c>
+      <c r="D3228" t="n">
+        <v>29</v>
+      </c>
+      <c r="E3228" t="n">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="3229">
+      <c r="A3229" t="n">
+        <v>26</v>
+      </c>
+      <c r="B3229" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3229" t="n">
+        <v>56</v>
+      </c>
+      <c r="D3229" t="n">
+        <v>15</v>
+      </c>
+      <c r="E3229" t="n">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="3230">
+      <c r="A3230" t="n">
+        <v>27</v>
+      </c>
+      <c r="B3230" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3230" t="n">
+        <v>23</v>
+      </c>
+      <c r="D3230" t="n">
+        <v>49</v>
+      </c>
+      <c r="E3230" t="n">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="3231">
+      <c r="A3231" t="n">
+        <v>28</v>
+      </c>
+      <c r="B3231" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3231" t="n">
+        <v>60</v>
+      </c>
+      <c r="D3231" t="n">
+        <v>50</v>
+      </c>
+      <c r="E3231" t="n">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="3232">
+      <c r="A3232" t="n">
+        <v>29</v>
+      </c>
+      <c r="B3232" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3232" t="n">
+        <v>93</v>
+      </c>
+      <c r="D3232" t="n">
+        <v>53</v>
+      </c>
+      <c r="E3232" t="n">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="3233">
+      <c r="A3233" t="n">
+        <v>30</v>
+      </c>
+      <c r="B3233" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3233" t="n">
+        <v>87</v>
+      </c>
+      <c r="D3233" t="n">
+        <v>46</v>
+      </c>
+      <c r="E3233" t="n">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="3234">
+      <c r="A3234" t="n">
+        <v>31</v>
+      </c>
+      <c r="B3234" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3234" t="n">
+        <v>16</v>
+      </c>
+      <c r="D3234" t="n">
+        <v>55</v>
+      </c>
+      <c r="E3234" t="n">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="3235">
+      <c r="A3235" t="n">
+        <v>32</v>
+      </c>
+      <c r="B3235" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3235" t="n">
+        <v>82</v>
+      </c>
+      <c r="D3235" t="n">
+        <v>30</v>
+      </c>
+      <c r="E3235" t="n">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="3236">
+      <c r="A3236" t="n">
+        <v>33</v>
+      </c>
+      <c r="B3236" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3236" t="n">
+        <v>39</v>
+      </c>
+      <c r="D3236" t="n">
+        <v>94</v>
+      </c>
+      <c r="E3236" t="n">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="3237">
+      <c r="A3237" t="n">
+        <v>34</v>
+      </c>
+      <c r="B3237" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3237" t="n">
+        <v>94</v>
+      </c>
+      <c r="D3237" t="n">
+        <v>81</v>
+      </c>
+      <c r="E3237" t="n">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="3238">
+      <c r="A3238" t="n">
+        <v>35</v>
+      </c>
+      <c r="B3238" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3238" t="n">
+        <v>34</v>
+      </c>
+      <c r="D3238" t="n">
+        <v>49</v>
+      </c>
+      <c r="E3238" t="n">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="3239">
+      <c r="A3239" t="n">
+        <v>36</v>
+      </c>
+      <c r="B3239" t="n">
+        <v>7</v>
+      </c>
+      <c r="C3239" t="n">
+        <v>27</v>
+      </c>
+      <c r="D3239" t="n">
+        <v>11</v>
+      </c>
+      <c r="E3239" t="n">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="3240">
+      <c r="A3240" t="n">
+        <v>37</v>
+      </c>
+      <c r="B3240" t="n">
+        <v>8</v>
+      </c>
+      <c r="C3240" t="n">
+        <v>67</v>
+      </c>
+      <c r="D3240" t="n">
+        <v>37</v>
+      </c>
+      <c r="E3240" t="n">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="3241">
+      <c r="A3241" t="n">
+        <v>38</v>
+      </c>
+      <c r="B3241" t="n">
+        <v>9</v>
+      </c>
+      <c r="C3241" t="n">
+        <v>80</v>
+      </c>
+      <c r="D3241" t="n">
+        <v>25</v>
+      </c>
+      <c r="E3241" t="n">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="3242">
+      <c r="A3242" t="n">
+        <v>39</v>
+      </c>
+      <c r="B3242" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3242" t="n">
+        <v>42</v>
+      </c>
+      <c r="D3242" t="n">
+        <v>14</v>
+      </c>
+      <c r="E3242" t="n">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="3243">
+      <c r="A3243" t="n">
+        <v>40</v>
+      </c>
+      <c r="B3243" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3243" t="n">
+        <v>66</v>
+      </c>
+      <c r="D3243" t="n">
+        <v>11</v>
+      </c>
+      <c r="E3243" t="n">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="3244">
+      <c r="A3244" t="n">
+        <v>41</v>
+      </c>
+      <c r="B3244" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3244" t="n">
+        <v>12</v>
+      </c>
+      <c r="D3244" t="n">
+        <v>65</v>
+      </c>
+      <c r="E3244" t="n">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="3245">
+      <c r="A3245" t="n">
+        <v>42</v>
+      </c>
+      <c r="B3245" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3245" t="n">
+        <v>14</v>
+      </c>
+      <c r="D3245" t="n">
+        <v>96</v>
+      </c>
+      <c r="E3245" t="n">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="3246">
+      <c r="A3246" t="n">
+        <v>43</v>
+      </c>
+      <c r="B3246" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3246" t="n">
+        <v>27</v>
+      </c>
+      <c r="D3246" t="n">
+        <v>19</v>
+      </c>
+      <c r="E3246" t="n">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="3247">
+      <c r="A3247" t="n">
+        <v>44</v>
+      </c>
+      <c r="B3247" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3247" t="n">
+        <v>82</v>
+      </c>
+      <c r="D3247" t="n">
+        <v>17</v>
+      </c>
+      <c r="E3247" t="n">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="3248">
+      <c r="A3248" t="n">
+        <v>45</v>
+      </c>
+      <c r="B3248" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3248" t="n">
+        <v>59</v>
+      </c>
+      <c r="D3248" t="n">
+        <v>63</v>
+      </c>
+      <c r="E3248" t="n">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="3249">
+      <c r="A3249" t="n">
+        <v>46</v>
+      </c>
+      <c r="B3249" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3249" t="n">
+        <v>36</v>
+      </c>
+      <c r="D3249" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3249" t="n">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="3250">
+      <c r="A3250" t="n">
+        <v>47</v>
+      </c>
+      <c r="B3250" t="n">
+        <v>7</v>
+      </c>
+      <c r="C3250" t="n">
+        <v>9</v>
+      </c>
+      <c r="D3250" t="n">
+        <v>97</v>
+      </c>
+      <c r="E3250" t="n">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="3251">
+      <c r="A3251" t="n">
+        <v>48</v>
+      </c>
+      <c r="B3251" t="n">
+        <v>8</v>
+      </c>
+      <c r="C3251" t="n">
+        <v>86</v>
+      </c>
+      <c r="D3251" t="n">
+        <v>19</v>
+      </c>
+      <c r="E3251" t="n">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="3252">
+      <c r="A3252" t="n">
+        <v>49</v>
+      </c>
+      <c r="B3252" t="n">
+        <v>9</v>
+      </c>
+      <c r="C3252" t="n">
+        <v>12</v>
+      </c>
+      <c r="D3252" t="n">
+        <v>68</v>
+      </c>
+      <c r="E3252" t="n">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="3253">
+      <c r="A3253" t="n">
+        <v>50</v>
+      </c>
+      <c r="B3253" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3253" t="n">
+        <v>87</v>
+      </c>
+      <c r="D3253" t="n">
+        <v>25</v>
+      </c>
+      <c r="E3253" t="n">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="3254">
+      <c r="A3254" t="n">
+        <v>51</v>
+      </c>
+      <c r="B3254" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3254" t="n">
+        <v>57</v>
+      </c>
+      <c r="D3254" t="n">
+        <v>43</v>
+      </c>
+      <c r="E3254" t="n">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="3255">
+      <c r="A3255" t="n">
+        <v>52</v>
+      </c>
+      <c r="B3255" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3255" t="n">
+        <v>77</v>
+      </c>
+      <c r="D3255" t="n">
+        <v>66</v>
+      </c>
+      <c r="E3255" t="n">
+        <v>530</v>
       </c>
     </row>
   </sheetData>
@@ -62965,7 +64116,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F222"/>
+  <dimension ref="A1:F225"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69162,30 +70313,114 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Eko Wałbrzych</t>
+          <t>Vital Expert</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>2995586494</t>
+          <t>3018233883</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>Pszczyna</t>
+          <t>Gdańsk</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Drogeria specjalistyczna</t>
+          <t>Medycyna estetyczna / klinika urody</t>
         </is>
       </c>
       <c r="F222" t="n">
-        <v>17</v>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>230</v>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Fitness Eco</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>1557688364</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>Leszno</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>Zielarnia</t>
+        </is>
+      </c>
+      <c r="F223" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
+        <v>231</v>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Muscle Fit &amp; Synowie</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>5916905560</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>Biłgoraj</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>Siłownia / klub sportowy</t>
+        </is>
+      </c>
+      <c r="F224" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>232</v>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Apteki Pure Partner</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>7211729605</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>Żory</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>Siłownia / klub sportowy</t>
+        </is>
+      </c>
+      <c r="F225" t="n">
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/dane.xlsx
+++ b/dane.xlsx
@@ -3759,7 +3759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G531"/>
+  <dimension ref="A1:G541"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17047,6 +17047,256 @@
       </c>
       <c r="G531" t="n">
         <v>199</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="n">
+        <v>531</v>
+      </c>
+      <c r="B532" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>Dostarczone</t>
+        </is>
+      </c>
+      <c r="D532" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E532" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F532" t="n">
+        <v>4</v>
+      </c>
+      <c r="G532" t="n">
+        <v>1467</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="n">
+        <v>532</v>
+      </c>
+      <c r="B533" s="2" t="n">
+        <v>46088</v>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>Dostarczone</t>
+        </is>
+      </c>
+      <c r="D533" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="E533" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F533" t="n">
+        <v>3</v>
+      </c>
+      <c r="G533" t="n">
+        <v>2651</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="n">
+        <v>533</v>
+      </c>
+      <c r="B534" s="2" t="n">
+        <v>46067</v>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>Wysłane</t>
+        </is>
+      </c>
+      <c r="D534" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="E534" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F534" t="n">
+        <v>2</v>
+      </c>
+      <c r="G534" t="n">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="n">
+        <v>534</v>
+      </c>
+      <c r="B535" s="2" t="n">
+        <v>46075</v>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>Nowe</t>
+        </is>
+      </c>
+      <c r="D535" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="E535" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F535" t="n">
+        <v>2</v>
+      </c>
+      <c r="G535" t="n">
+        <v>2953</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="n">
+        <v>535</v>
+      </c>
+      <c r="B536" s="2" t="n">
+        <v>46076</v>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>Zwrot</t>
+        </is>
+      </c>
+      <c r="D536" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="E536" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F536" t="n">
+        <v>3</v>
+      </c>
+      <c r="G536" t="n">
+        <v>2762</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="n">
+        <v>536</v>
+      </c>
+      <c r="B537" s="2" t="n">
+        <v>46067</v>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>Zwrot</t>
+        </is>
+      </c>
+      <c r="D537" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="E537" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F537" t="n">
+        <v>4</v>
+      </c>
+      <c r="G537" t="n">
+        <v>3203</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="n">
+        <v>537</v>
+      </c>
+      <c r="B538" s="2" t="n">
+        <v>46067</v>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>Nowe</t>
+        </is>
+      </c>
+      <c r="D538" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="E538" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F538" t="n">
+        <v>2</v>
+      </c>
+      <c r="G538" t="n">
+        <v>1693</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="n">
+        <v>538</v>
+      </c>
+      <c r="B539" s="2" t="n">
+        <v>46067</v>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>Dostarczone</t>
+        </is>
+      </c>
+      <c r="D539" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="E539" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F539" t="n">
+        <v>1</v>
+      </c>
+      <c r="G539" t="n">
+        <v>1624</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="n">
+        <v>539</v>
+      </c>
+      <c r="B540" s="2" t="n">
+        <v>46064</v>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>Zwrot</t>
+        </is>
+      </c>
+      <c r="D540" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="E540" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F540" t="n">
+        <v>3</v>
+      </c>
+      <c r="G540" t="n">
+        <v>1556</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="n">
+        <v>540</v>
+      </c>
+      <c r="B541" s="2" t="n">
+        <v>46072</v>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>Nowe</t>
+        </is>
+      </c>
+      <c r="D541" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="E541" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F541" t="n">
+        <v>3</v>
+      </c>
+      <c r="G541" t="n">
+        <v>2107</v>
       </c>
     </row>
   </sheetData>
@@ -17060,7 +17310,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3255"/>
+  <dimension ref="A1:E3327"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64103,6 +64353,1230 @@
       </c>
       <c r="E3255" t="n">
         <v>530</v>
+      </c>
+    </row>
+    <row r="3256">
+      <c r="A3256" t="n">
+        <v>0</v>
+      </c>
+      <c r="B3256" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3256" t="n">
+        <v>54</v>
+      </c>
+      <c r="D3256" t="n">
+        <v>14</v>
+      </c>
+      <c r="E3256" t="n">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="3257">
+      <c r="A3257" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3257" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3257" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3257" t="n">
+        <v>6</v>
+      </c>
+      <c r="E3257" t="n">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="3258">
+      <c r="A3258" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3258" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3258" t="n">
+        <v>82</v>
+      </c>
+      <c r="D3258" t="n">
+        <v>51</v>
+      </c>
+      <c r="E3258" t="n">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="3259">
+      <c r="A3259" t="n">
+        <v>3</v>
+      </c>
+      <c r="B3259" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3259" t="n">
+        <v>54</v>
+      </c>
+      <c r="D3259" t="n">
+        <v>85</v>
+      </c>
+      <c r="E3259" t="n">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="3260">
+      <c r="A3260" t="n">
+        <v>4</v>
+      </c>
+      <c r="B3260" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3260" t="n">
+        <v>23</v>
+      </c>
+      <c r="D3260" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3260" t="n">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="3261">
+      <c r="A3261" t="n">
+        <v>5</v>
+      </c>
+      <c r="B3261" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3261" t="n">
+        <v>41</v>
+      </c>
+      <c r="D3261" t="n">
+        <v>7</v>
+      </c>
+      <c r="E3261" t="n">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="3262">
+      <c r="A3262" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3262" t="n">
+        <v>7</v>
+      </c>
+      <c r="C3262" t="n">
+        <v>96</v>
+      </c>
+      <c r="D3262" t="n">
+        <v>29</v>
+      </c>
+      <c r="E3262" t="n">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="3263">
+      <c r="A3263" t="n">
+        <v>7</v>
+      </c>
+      <c r="B3263" t="n">
+        <v>8</v>
+      </c>
+      <c r="C3263" t="n">
+        <v>96</v>
+      </c>
+      <c r="D3263" t="n">
+        <v>8</v>
+      </c>
+      <c r="E3263" t="n">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="3264">
+      <c r="A3264" t="n">
+        <v>8</v>
+      </c>
+      <c r="B3264" t="n">
+        <v>9</v>
+      </c>
+      <c r="C3264" t="n">
+        <v>26</v>
+      </c>
+      <c r="D3264" t="n">
+        <v>90</v>
+      </c>
+      <c r="E3264" t="n">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="3265">
+      <c r="A3265" t="n">
+        <v>9</v>
+      </c>
+      <c r="B3265" t="n">
+        <v>10</v>
+      </c>
+      <c r="C3265" t="n">
+        <v>42</v>
+      </c>
+      <c r="D3265" t="n">
+        <v>79</v>
+      </c>
+      <c r="E3265" t="n">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="3266">
+      <c r="A3266" t="n">
+        <v>10</v>
+      </c>
+      <c r="B3266" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3266" t="n">
+        <v>76</v>
+      </c>
+      <c r="D3266" t="n">
+        <v>5</v>
+      </c>
+      <c r="E3266" t="n">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="3267">
+      <c r="A3267" t="n">
+        <v>11</v>
+      </c>
+      <c r="B3267" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3267" t="n">
+        <v>34</v>
+      </c>
+      <c r="D3267" t="n">
+        <v>100</v>
+      </c>
+      <c r="E3267" t="n">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="3268">
+      <c r="A3268" t="n">
+        <v>12</v>
+      </c>
+      <c r="B3268" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3268" t="n">
+        <v>41</v>
+      </c>
+      <c r="D3268" t="n">
+        <v>69</v>
+      </c>
+      <c r="E3268" t="n">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="3269">
+      <c r="A3269" t="n">
+        <v>13</v>
+      </c>
+      <c r="B3269" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3269" t="n">
+        <v>78</v>
+      </c>
+      <c r="D3269" t="n">
+        <v>67</v>
+      </c>
+      <c r="E3269" t="n">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="3270">
+      <c r="A3270" t="n">
+        <v>14</v>
+      </c>
+      <c r="B3270" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3270" t="n">
+        <v>95</v>
+      </c>
+      <c r="D3270" t="n">
+        <v>63</v>
+      </c>
+      <c r="E3270" t="n">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="3271">
+      <c r="A3271" t="n">
+        <v>15</v>
+      </c>
+      <c r="B3271" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3271" t="n">
+        <v>26</v>
+      </c>
+      <c r="D3271" t="n">
+        <v>50</v>
+      </c>
+      <c r="E3271" t="n">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="3272">
+      <c r="A3272" t="n">
+        <v>16</v>
+      </c>
+      <c r="B3272" t="n">
+        <v>7</v>
+      </c>
+      <c r="C3272" t="n">
+        <v>45</v>
+      </c>
+      <c r="D3272" t="n">
+        <v>26</v>
+      </c>
+      <c r="E3272" t="n">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="3273">
+      <c r="A3273" t="n">
+        <v>17</v>
+      </c>
+      <c r="B3273" t="n">
+        <v>8</v>
+      </c>
+      <c r="C3273" t="n">
+        <v>54</v>
+      </c>
+      <c r="D3273" t="n">
+        <v>21</v>
+      </c>
+      <c r="E3273" t="n">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="3274">
+      <c r="A3274" t="n">
+        <v>18</v>
+      </c>
+      <c r="B3274" t="n">
+        <v>9</v>
+      </c>
+      <c r="C3274" t="n">
+        <v>36</v>
+      </c>
+      <c r="D3274" t="n">
+        <v>28</v>
+      </c>
+      <c r="E3274" t="n">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="3275">
+      <c r="A3275" t="n">
+        <v>19</v>
+      </c>
+      <c r="B3275" t="n">
+        <v>10</v>
+      </c>
+      <c r="C3275" t="n">
+        <v>48</v>
+      </c>
+      <c r="D3275" t="n">
+        <v>35</v>
+      </c>
+      <c r="E3275" t="n">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="3276">
+      <c r="A3276" t="n">
+        <v>20</v>
+      </c>
+      <c r="B3276" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3276" t="n">
+        <v>89</v>
+      </c>
+      <c r="D3276" t="n">
+        <v>25</v>
+      </c>
+      <c r="E3276" t="n">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="3277">
+      <c r="A3277" t="n">
+        <v>21</v>
+      </c>
+      <c r="B3277" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3277" t="n">
+        <v>44</v>
+      </c>
+      <c r="D3277" t="n">
+        <v>66</v>
+      </c>
+      <c r="E3277" t="n">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="3278">
+      <c r="A3278" t="n">
+        <v>22</v>
+      </c>
+      <c r="B3278" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3278" t="n">
+        <v>69</v>
+      </c>
+      <c r="D3278" t="n">
+        <v>67</v>
+      </c>
+      <c r="E3278" t="n">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="3279">
+      <c r="A3279" t="n">
+        <v>23</v>
+      </c>
+      <c r="B3279" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3279" t="n">
+        <v>83</v>
+      </c>
+      <c r="D3279" t="n">
+        <v>88</v>
+      </c>
+      <c r="E3279" t="n">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="3280">
+      <c r="A3280" t="n">
+        <v>24</v>
+      </c>
+      <c r="B3280" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3280" t="n">
+        <v>97</v>
+      </c>
+      <c r="D3280" t="n">
+        <v>21</v>
+      </c>
+      <c r="E3280" t="n">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="3281">
+      <c r="A3281" t="n">
+        <v>25</v>
+      </c>
+      <c r="B3281" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3281" t="n">
+        <v>67</v>
+      </c>
+      <c r="D3281" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3281" t="n">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="3282">
+      <c r="A3282" t="n">
+        <v>26</v>
+      </c>
+      <c r="B3282" t="n">
+        <v>7</v>
+      </c>
+      <c r="C3282" t="n">
+        <v>74</v>
+      </c>
+      <c r="D3282" t="n">
+        <v>38</v>
+      </c>
+      <c r="E3282" t="n">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="3283">
+      <c r="A3283" t="n">
+        <v>27</v>
+      </c>
+      <c r="B3283" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3283" t="n">
+        <v>61</v>
+      </c>
+      <c r="D3283" t="n">
+        <v>96</v>
+      </c>
+      <c r="E3283" t="n">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="3284">
+      <c r="A3284" t="n">
+        <v>28</v>
+      </c>
+      <c r="B3284" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3284" t="n">
+        <v>6</v>
+      </c>
+      <c r="D3284" t="n">
+        <v>39</v>
+      </c>
+      <c r="E3284" t="n">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="3285">
+      <c r="A3285" t="n">
+        <v>29</v>
+      </c>
+      <c r="B3285" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3285" t="n">
+        <v>37</v>
+      </c>
+      <c r="D3285" t="n">
+        <v>64</v>
+      </c>
+      <c r="E3285" t="n">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="3286">
+      <c r="A3286" t="n">
+        <v>30</v>
+      </c>
+      <c r="B3286" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3286" t="n">
+        <v>41</v>
+      </c>
+      <c r="D3286" t="n">
+        <v>93</v>
+      </c>
+      <c r="E3286" t="n">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="3287">
+      <c r="A3287" t="n">
+        <v>31</v>
+      </c>
+      <c r="B3287" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3287" t="n">
+        <v>83</v>
+      </c>
+      <c r="D3287" t="n">
+        <v>49</v>
+      </c>
+      <c r="E3287" t="n">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="3288">
+      <c r="A3288" t="n">
+        <v>32</v>
+      </c>
+      <c r="B3288" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3288" t="n">
+        <v>95</v>
+      </c>
+      <c r="D3288" t="n">
+        <v>45</v>
+      </c>
+      <c r="E3288" t="n">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="3289">
+      <c r="A3289" t="n">
+        <v>33</v>
+      </c>
+      <c r="B3289" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3289" t="n">
+        <v>30</v>
+      </c>
+      <c r="D3289" t="n">
+        <v>54</v>
+      </c>
+      <c r="E3289" t="n">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="3290">
+      <c r="A3290" t="n">
+        <v>34</v>
+      </c>
+      <c r="B3290" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3290" t="n">
+        <v>64</v>
+      </c>
+      <c r="D3290" t="n">
+        <v>15</v>
+      </c>
+      <c r="E3290" t="n">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="3291">
+      <c r="A3291" t="n">
+        <v>35</v>
+      </c>
+      <c r="B3291" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3291" t="n">
+        <v>14</v>
+      </c>
+      <c r="D3291" t="n">
+        <v>41</v>
+      </c>
+      <c r="E3291" t="n">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="3292">
+      <c r="A3292" t="n">
+        <v>36</v>
+      </c>
+      <c r="B3292" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3292" t="n">
+        <v>25</v>
+      </c>
+      <c r="D3292" t="n">
+        <v>69</v>
+      </c>
+      <c r="E3292" t="n">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="3293">
+      <c r="A3293" t="n">
+        <v>37</v>
+      </c>
+      <c r="B3293" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3293" t="n">
+        <v>9</v>
+      </c>
+      <c r="D3293" t="n">
+        <v>77</v>
+      </c>
+      <c r="E3293" t="n">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="3294">
+      <c r="A3294" t="n">
+        <v>38</v>
+      </c>
+      <c r="B3294" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3294" t="n">
+        <v>31</v>
+      </c>
+      <c r="D3294" t="n">
+        <v>50</v>
+      </c>
+      <c r="E3294" t="n">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="3295">
+      <c r="A3295" t="n">
+        <v>39</v>
+      </c>
+      <c r="B3295" t="n">
+        <v>7</v>
+      </c>
+      <c r="C3295" t="n">
+        <v>9</v>
+      </c>
+      <c r="D3295" t="n">
+        <v>33</v>
+      </c>
+      <c r="E3295" t="n">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="3296">
+      <c r="A3296" t="n">
+        <v>40</v>
+      </c>
+      <c r="B3296" t="n">
+        <v>8</v>
+      </c>
+      <c r="C3296" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3296" t="n">
+        <v>77</v>
+      </c>
+      <c r="E3296" t="n">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="3297">
+      <c r="A3297" t="n">
+        <v>41</v>
+      </c>
+      <c r="B3297" t="n">
+        <v>9</v>
+      </c>
+      <c r="C3297" t="n">
+        <v>9</v>
+      </c>
+      <c r="D3297" t="n">
+        <v>92</v>
+      </c>
+      <c r="E3297" t="n">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="3298">
+      <c r="A3298" t="n">
+        <v>42</v>
+      </c>
+      <c r="B3298" t="n">
+        <v>10</v>
+      </c>
+      <c r="C3298" t="n">
+        <v>94</v>
+      </c>
+      <c r="D3298" t="n">
+        <v>73</v>
+      </c>
+      <c r="E3298" t="n">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="3299">
+      <c r="A3299" t="n">
+        <v>43</v>
+      </c>
+      <c r="B3299" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3299" t="n">
+        <v>20</v>
+      </c>
+      <c r="D3299" t="n">
+        <v>94</v>
+      </c>
+      <c r="E3299" t="n">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="3300">
+      <c r="A3300" t="n">
+        <v>44</v>
+      </c>
+      <c r="B3300" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3300" t="n">
+        <v>61</v>
+      </c>
+      <c r="D3300" t="n">
+        <v>30</v>
+      </c>
+      <c r="E3300" t="n">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="3301">
+      <c r="A3301" t="n">
+        <v>45</v>
+      </c>
+      <c r="B3301" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3301" t="n">
+        <v>27</v>
+      </c>
+      <c r="D3301" t="n">
+        <v>31</v>
+      </c>
+      <c r="E3301" t="n">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="3302">
+      <c r="A3302" t="n">
+        <v>46</v>
+      </c>
+      <c r="B3302" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3302" t="n">
+        <v>14</v>
+      </c>
+      <c r="D3302" t="n">
+        <v>90</v>
+      </c>
+      <c r="E3302" t="n">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="3303">
+      <c r="A3303" t="n">
+        <v>47</v>
+      </c>
+      <c r="B3303" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3303" t="n">
+        <v>49</v>
+      </c>
+      <c r="D3303" t="n">
+        <v>35</v>
+      </c>
+      <c r="E3303" t="n">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="3304">
+      <c r="A3304" t="n">
+        <v>48</v>
+      </c>
+      <c r="B3304" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3304" t="n">
+        <v>100</v>
+      </c>
+      <c r="D3304" t="n">
+        <v>67</v>
+      </c>
+      <c r="E3304" t="n">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="3305">
+      <c r="A3305" t="n">
+        <v>49</v>
+      </c>
+      <c r="B3305" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3305" t="n">
+        <v>27</v>
+      </c>
+      <c r="D3305" t="n">
+        <v>26</v>
+      </c>
+      <c r="E3305" t="n">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="3306">
+      <c r="A3306" t="n">
+        <v>50</v>
+      </c>
+      <c r="B3306" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3306" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3306" t="n">
+        <v>71</v>
+      </c>
+      <c r="E3306" t="n">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="3307">
+      <c r="A3307" t="n">
+        <v>51</v>
+      </c>
+      <c r="B3307" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3307" t="n">
+        <v>87</v>
+      </c>
+      <c r="D3307" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3307" t="n">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="3308">
+      <c r="A3308" t="n">
+        <v>52</v>
+      </c>
+      <c r="B3308" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3308" t="n">
+        <v>75</v>
+      </c>
+      <c r="D3308" t="n">
+        <v>88</v>
+      </c>
+      <c r="E3308" t="n">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="3309">
+      <c r="A3309" t="n">
+        <v>53</v>
+      </c>
+      <c r="B3309" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3309" t="n">
+        <v>84</v>
+      </c>
+      <c r="D3309" t="n">
+        <v>44</v>
+      </c>
+      <c r="E3309" t="n">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="3310">
+      <c r="A3310" t="n">
+        <v>54</v>
+      </c>
+      <c r="B3310" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3310" t="n">
+        <v>44</v>
+      </c>
+      <c r="D3310" t="n">
+        <v>65</v>
+      </c>
+      <c r="E3310" t="n">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="3311">
+      <c r="A3311" t="n">
+        <v>55</v>
+      </c>
+      <c r="B3311" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3311" t="n">
+        <v>58</v>
+      </c>
+      <c r="D3311" t="n">
+        <v>58</v>
+      </c>
+      <c r="E3311" t="n">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="3312">
+      <c r="A3312" t="n">
+        <v>56</v>
+      </c>
+      <c r="B3312" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3312" t="n">
+        <v>82</v>
+      </c>
+      <c r="D3312" t="n">
+        <v>67</v>
+      </c>
+      <c r="E3312" t="n">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="3313">
+      <c r="A3313" t="n">
+        <v>57</v>
+      </c>
+      <c r="B3313" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3313" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3313" t="n">
+        <v>25</v>
+      </c>
+      <c r="E3313" t="n">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="3314">
+      <c r="A3314" t="n">
+        <v>58</v>
+      </c>
+      <c r="B3314" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3314" t="n">
+        <v>37</v>
+      </c>
+      <c r="D3314" t="n">
+        <v>99</v>
+      </c>
+      <c r="E3314" t="n">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="3315">
+      <c r="A3315" t="n">
+        <v>59</v>
+      </c>
+      <c r="B3315" t="n">
+        <v>7</v>
+      </c>
+      <c r="C3315" t="n">
+        <v>56</v>
+      </c>
+      <c r="D3315" t="n">
+        <v>41</v>
+      </c>
+      <c r="E3315" t="n">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="3316">
+      <c r="A3316" t="n">
+        <v>60</v>
+      </c>
+      <c r="B3316" t="n">
+        <v>8</v>
+      </c>
+      <c r="C3316" t="n">
+        <v>88</v>
+      </c>
+      <c r="D3316" t="n">
+        <v>55</v>
+      </c>
+      <c r="E3316" t="n">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="3317">
+      <c r="A3317" t="n">
+        <v>61</v>
+      </c>
+      <c r="B3317" t="n">
+        <v>9</v>
+      </c>
+      <c r="C3317" t="n">
+        <v>70</v>
+      </c>
+      <c r="D3317" t="n">
+        <v>47</v>
+      </c>
+      <c r="E3317" t="n">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="3318">
+      <c r="A3318" t="n">
+        <v>62</v>
+      </c>
+      <c r="B3318" t="n">
+        <v>10</v>
+      </c>
+      <c r="C3318" t="n">
+        <v>41</v>
+      </c>
+      <c r="D3318" t="n">
+        <v>80</v>
+      </c>
+      <c r="E3318" t="n">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="3319">
+      <c r="A3319" t="n">
+        <v>63</v>
+      </c>
+      <c r="B3319" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3319" t="n">
+        <v>83</v>
+      </c>
+      <c r="D3319" t="n">
+        <v>81</v>
+      </c>
+      <c r="E3319" t="n">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="3320">
+      <c r="A3320" t="n">
+        <v>64</v>
+      </c>
+      <c r="B3320" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3320" t="n">
+        <v>86</v>
+      </c>
+      <c r="D3320" t="n">
+        <v>45</v>
+      </c>
+      <c r="E3320" t="n">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="3321">
+      <c r="A3321" t="n">
+        <v>65</v>
+      </c>
+      <c r="B3321" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3321" t="n">
+        <v>49</v>
+      </c>
+      <c r="D3321" t="n">
+        <v>13</v>
+      </c>
+      <c r="E3321" t="n">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="3322">
+      <c r="A3322" t="n">
+        <v>66</v>
+      </c>
+      <c r="B3322" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3322" t="n">
+        <v>90</v>
+      </c>
+      <c r="D3322" t="n">
+        <v>15</v>
+      </c>
+      <c r="E3322" t="n">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="3323">
+      <c r="A3323" t="n">
+        <v>67</v>
+      </c>
+      <c r="B3323" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3323" t="n">
+        <v>57</v>
+      </c>
+      <c r="D3323" t="n">
+        <v>95</v>
+      </c>
+      <c r="E3323" t="n">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="3324">
+      <c r="A3324" t="n">
+        <v>68</v>
+      </c>
+      <c r="B3324" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3324" t="n">
+        <v>95</v>
+      </c>
+      <c r="D3324" t="n">
+        <v>23</v>
+      </c>
+      <c r="E3324" t="n">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="3325">
+      <c r="A3325" t="n">
+        <v>69</v>
+      </c>
+      <c r="B3325" t="n">
+        <v>7</v>
+      </c>
+      <c r="C3325" t="n">
+        <v>72</v>
+      </c>
+      <c r="D3325" t="n">
+        <v>72</v>
+      </c>
+      <c r="E3325" t="n">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="3326">
+      <c r="A3326" t="n">
+        <v>70</v>
+      </c>
+      <c r="B3326" t="n">
+        <v>8</v>
+      </c>
+      <c r="C3326" t="n">
+        <v>22</v>
+      </c>
+      <c r="D3326" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3326" t="n">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="3327">
+      <c r="A3327" t="n">
+        <v>71</v>
+      </c>
+      <c r="B3327" t="n">
+        <v>9</v>
+      </c>
+      <c r="C3327" t="n">
+        <v>78</v>
+      </c>
+      <c r="D3327" t="n">
+        <v>53</v>
+      </c>
+      <c r="E3327" t="n">
+        <v>540</v>
       </c>
     </row>
   </sheetData>
@@ -64116,7 +65590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F225"/>
+  <dimension ref="A1:F228"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70397,30 +71871,114 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Apteki Pure Partner</t>
+          <t>Sport Eco</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>7211729605</t>
+          <t>6827402898</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>Żory</t>
+          <t>Stalowa Wola</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
+          <t>Gabinet dietetyczny</t>
+        </is>
+      </c>
+      <c r="F225" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
+        <v>234</v>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Fit Pro Sosnowiec</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>8076735321</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>Malbork</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>Apteka</t>
+        </is>
+      </c>
+      <c r="F226" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
+        <v>235</v>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Beauty Active</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>1819900663</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>Olsztyn</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>Supermarket / drogeria wielkopowierzchniowa</t>
+        </is>
+      </c>
+      <c r="F227" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
+        <v>236</v>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Dbam o Zdrowie Toruń</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>8547957586</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>Białystok</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
           <t>Siłownia / klub sportowy</t>
         </is>
       </c>
-      <c r="F225" t="n">
-        <v>21</v>
+      <c r="F228" t="n">
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/dane.xlsx
+++ b/dane.xlsx
@@ -3759,7 +3759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G541"/>
+  <dimension ref="A1:G551"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17297,6 +17297,256 @@
       </c>
       <c r="G541" t="n">
         <v>2107</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="n">
+        <v>541</v>
+      </c>
+      <c r="B542" s="2" t="n">
+        <v>46088</v>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>Nowe</t>
+        </is>
+      </c>
+      <c r="D542" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="E542" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F542" t="n">
+        <v>2</v>
+      </c>
+      <c r="G542" t="n">
+        <v>1671</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="n">
+        <v>542</v>
+      </c>
+      <c r="B543" s="2" t="n">
+        <v>46089</v>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>Zwrot</t>
+        </is>
+      </c>
+      <c r="D543" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="E543" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F543" t="n">
+        <v>2</v>
+      </c>
+      <c r="G543" t="n">
+        <v>2780</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="n">
+        <v>543</v>
+      </c>
+      <c r="B544" s="2" t="n">
+        <v>46076</v>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>Zwrot</t>
+        </is>
+      </c>
+      <c r="D544" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="E544" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F544" t="n">
+        <v>3</v>
+      </c>
+      <c r="G544" t="n">
+        <v>3160</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="n">
+        <v>544</v>
+      </c>
+      <c r="B545" s="2" t="n">
+        <v>46074</v>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>Wysłane</t>
+        </is>
+      </c>
+      <c r="D545" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="E545" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F545" t="n">
+        <v>3</v>
+      </c>
+      <c r="G545" t="n">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="n">
+        <v>545</v>
+      </c>
+      <c r="B546" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>Dostarczone</t>
+        </is>
+      </c>
+      <c r="D546" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="E546" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F546" t="n">
+        <v>2</v>
+      </c>
+      <c r="G546" t="n">
+        <v>1292</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="n">
+        <v>546</v>
+      </c>
+      <c r="B547" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>Dostarczone</t>
+        </is>
+      </c>
+      <c r="D547" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E547" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F547" t="n">
+        <v>1</v>
+      </c>
+      <c r="G547" t="n">
+        <v>3079</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="n">
+        <v>547</v>
+      </c>
+      <c r="B548" s="2" t="n">
+        <v>46062</v>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>Wysłane</t>
+        </is>
+      </c>
+      <c r="D548" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="E548" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F548" t="n">
+        <v>4</v>
+      </c>
+      <c r="G548" t="n">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="n">
+        <v>548</v>
+      </c>
+      <c r="B549" s="2" t="n">
+        <v>46081</v>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>Zwrot</t>
+        </is>
+      </c>
+      <c r="D549" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E549" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F549" t="n">
+        <v>3</v>
+      </c>
+      <c r="G549" t="n">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="n">
+        <v>549</v>
+      </c>
+      <c r="B550" s="2" t="n">
+        <v>46071</v>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>Wysłane</t>
+        </is>
+      </c>
+      <c r="D550" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E550" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F550" t="n">
+        <v>4</v>
+      </c>
+      <c r="G550" t="n">
+        <v>3283</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="n">
+        <v>550</v>
+      </c>
+      <c r="B551" s="2" t="n">
+        <v>46074</v>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>Dostarczone</t>
+        </is>
+      </c>
+      <c r="D551" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E551" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F551" t="n">
+        <v>4</v>
+      </c>
+      <c r="G551" t="n">
+        <v>1408</v>
       </c>
     </row>
   </sheetData>
@@ -17310,7 +17560,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3327"/>
+  <dimension ref="A1:E3375"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65577,6 +65827,822 @@
       </c>
       <c r="E3327" t="n">
         <v>540</v>
+      </c>
+    </row>
+    <row r="3328">
+      <c r="A3328" t="n">
+        <v>0</v>
+      </c>
+      <c r="B3328" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3328" t="n">
+        <v>15</v>
+      </c>
+      <c r="D3328" t="n">
+        <v>23</v>
+      </c>
+      <c r="E3328" t="n">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="3329">
+      <c r="A3329" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3329" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3329" t="n">
+        <v>13</v>
+      </c>
+      <c r="D3329" t="n">
+        <v>5</v>
+      </c>
+      <c r="E3329" t="n">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="3330">
+      <c r="A3330" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3330" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3330" t="n">
+        <v>38</v>
+      </c>
+      <c r="D3330" t="n">
+        <v>28</v>
+      </c>
+      <c r="E3330" t="n">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="3331">
+      <c r="A3331" t="n">
+        <v>3</v>
+      </c>
+      <c r="B3331" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3331" t="n">
+        <v>61</v>
+      </c>
+      <c r="D3331" t="n">
+        <v>70</v>
+      </c>
+      <c r="E3331" t="n">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="3332">
+      <c r="A3332" t="n">
+        <v>4</v>
+      </c>
+      <c r="B3332" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3332" t="n">
+        <v>17</v>
+      </c>
+      <c r="D3332" t="n">
+        <v>86</v>
+      </c>
+      <c r="E3332" t="n">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="3333">
+      <c r="A3333" t="n">
+        <v>5</v>
+      </c>
+      <c r="B3333" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3333" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3333" t="n">
+        <v>70</v>
+      </c>
+      <c r="E3333" t="n">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="3334">
+      <c r="A3334" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3334" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3334" t="n">
+        <v>47</v>
+      </c>
+      <c r="D3334" t="n">
+        <v>53</v>
+      </c>
+      <c r="E3334" t="n">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="3335">
+      <c r="A3335" t="n">
+        <v>7</v>
+      </c>
+      <c r="B3335" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3335" t="n">
+        <v>43</v>
+      </c>
+      <c r="D3335" t="n">
+        <v>44</v>
+      </c>
+      <c r="E3335" t="n">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="3336">
+      <c r="A3336" t="n">
+        <v>8</v>
+      </c>
+      <c r="B3336" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3336" t="n">
+        <v>84</v>
+      </c>
+      <c r="D3336" t="n">
+        <v>4</v>
+      </c>
+      <c r="E3336" t="n">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="3337">
+      <c r="A3337" t="n">
+        <v>9</v>
+      </c>
+      <c r="B3337" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3337" t="n">
+        <v>34</v>
+      </c>
+      <c r="D3337" t="n">
+        <v>48</v>
+      </c>
+      <c r="E3337" t="n">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="3338">
+      <c r="A3338" t="n">
+        <v>10</v>
+      </c>
+      <c r="B3338" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3338" t="n">
+        <v>43</v>
+      </c>
+      <c r="D3338" t="n">
+        <v>56</v>
+      </c>
+      <c r="E3338" t="n">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="3339">
+      <c r="A3339" t="n">
+        <v>11</v>
+      </c>
+      <c r="B3339" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3339" t="n">
+        <v>67</v>
+      </c>
+      <c r="D3339" t="n">
+        <v>8</v>
+      </c>
+      <c r="E3339" t="n">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="3340">
+      <c r="A3340" t="n">
+        <v>12</v>
+      </c>
+      <c r="B3340" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3340" t="n">
+        <v>81</v>
+      </c>
+      <c r="D3340" t="n">
+        <v>23</v>
+      </c>
+      <c r="E3340" t="n">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="3341">
+      <c r="A3341" t="n">
+        <v>13</v>
+      </c>
+      <c r="B3341" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3341" t="n">
+        <v>7</v>
+      </c>
+      <c r="D3341" t="n">
+        <v>100</v>
+      </c>
+      <c r="E3341" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="3342">
+      <c r="A3342" t="n">
+        <v>14</v>
+      </c>
+      <c r="B3342" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3342" t="n">
+        <v>60</v>
+      </c>
+      <c r="D3342" t="n">
+        <v>12</v>
+      </c>
+      <c r="E3342" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="3343">
+      <c r="A3343" t="n">
+        <v>15</v>
+      </c>
+      <c r="B3343" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3343" t="n">
+        <v>19</v>
+      </c>
+      <c r="D3343" t="n">
+        <v>17</v>
+      </c>
+      <c r="E3343" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="3344">
+      <c r="A3344" t="n">
+        <v>16</v>
+      </c>
+      <c r="B3344" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3344" t="n">
+        <v>17</v>
+      </c>
+      <c r="D3344" t="n">
+        <v>82</v>
+      </c>
+      <c r="E3344" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="3345">
+      <c r="A3345" t="n">
+        <v>17</v>
+      </c>
+      <c r="B3345" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3345" t="n">
+        <v>47</v>
+      </c>
+      <c r="D3345" t="n">
+        <v>94</v>
+      </c>
+      <c r="E3345" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="3346">
+      <c r="A3346" t="n">
+        <v>18</v>
+      </c>
+      <c r="B3346" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3346" t="n">
+        <v>85</v>
+      </c>
+      <c r="D3346" t="n">
+        <v>80</v>
+      </c>
+      <c r="E3346" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="3347">
+      <c r="A3347" t="n">
+        <v>19</v>
+      </c>
+      <c r="B3347" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3347" t="n">
+        <v>20</v>
+      </c>
+      <c r="D3347" t="n">
+        <v>14</v>
+      </c>
+      <c r="E3347" t="n">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="3348">
+      <c r="A3348" t="n">
+        <v>20</v>
+      </c>
+      <c r="B3348" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3348" t="n">
+        <v>52</v>
+      </c>
+      <c r="D3348" t="n">
+        <v>56</v>
+      </c>
+      <c r="E3348" t="n">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="3349">
+      <c r="A3349" t="n">
+        <v>21</v>
+      </c>
+      <c r="B3349" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3349" t="n">
+        <v>75</v>
+      </c>
+      <c r="D3349" t="n">
+        <v>48</v>
+      </c>
+      <c r="E3349" t="n">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="3350">
+      <c r="A3350" t="n">
+        <v>22</v>
+      </c>
+      <c r="B3350" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3350" t="n">
+        <v>47</v>
+      </c>
+      <c r="D3350" t="n">
+        <v>53</v>
+      </c>
+      <c r="E3350" t="n">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="3351">
+      <c r="A3351" t="n">
+        <v>23</v>
+      </c>
+      <c r="B3351" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3351" t="n">
+        <v>73</v>
+      </c>
+      <c r="D3351" t="n">
+        <v>25</v>
+      </c>
+      <c r="E3351" t="n">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="3352">
+      <c r="A3352" t="n">
+        <v>24</v>
+      </c>
+      <c r="B3352" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3352" t="n">
+        <v>6</v>
+      </c>
+      <c r="D3352" t="n">
+        <v>64</v>
+      </c>
+      <c r="E3352" t="n">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="3353">
+      <c r="A3353" t="n">
+        <v>25</v>
+      </c>
+      <c r="B3353" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3353" t="n">
+        <v>13</v>
+      </c>
+      <c r="D3353" t="n">
+        <v>23</v>
+      </c>
+      <c r="E3353" t="n">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="3354">
+      <c r="A3354" t="n">
+        <v>26</v>
+      </c>
+      <c r="B3354" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3354" t="n">
+        <v>77</v>
+      </c>
+      <c r="D3354" t="n">
+        <v>60</v>
+      </c>
+      <c r="E3354" t="n">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="3355">
+      <c r="A3355" t="n">
+        <v>27</v>
+      </c>
+      <c r="B3355" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3355" t="n">
+        <v>94</v>
+      </c>
+      <c r="D3355" t="n">
+        <v>27</v>
+      </c>
+      <c r="E3355" t="n">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="3356">
+      <c r="A3356" t="n">
+        <v>28</v>
+      </c>
+      <c r="B3356" t="n">
+        <v>7</v>
+      </c>
+      <c r="C3356" t="n">
+        <v>100</v>
+      </c>
+      <c r="D3356" t="n">
+        <v>69</v>
+      </c>
+      <c r="E3356" t="n">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="3357">
+      <c r="A3357" t="n">
+        <v>29</v>
+      </c>
+      <c r="B3357" t="n">
+        <v>8</v>
+      </c>
+      <c r="C3357" t="n">
+        <v>97</v>
+      </c>
+      <c r="D3357" t="n">
+        <v>54</v>
+      </c>
+      <c r="E3357" t="n">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="3358">
+      <c r="A3358" t="n">
+        <v>30</v>
+      </c>
+      <c r="B3358" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3358" t="n">
+        <v>15</v>
+      </c>
+      <c r="D3358" t="n">
+        <v>14</v>
+      </c>
+      <c r="E3358" t="n">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="3359">
+      <c r="A3359" t="n">
+        <v>31</v>
+      </c>
+      <c r="B3359" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3359" t="n">
+        <v>21</v>
+      </c>
+      <c r="D3359" t="n">
+        <v>6</v>
+      </c>
+      <c r="E3359" t="n">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="3360">
+      <c r="A3360" t="n">
+        <v>32</v>
+      </c>
+      <c r="B3360" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3360" t="n">
+        <v>72</v>
+      </c>
+      <c r="D3360" t="n">
+        <v>53</v>
+      </c>
+      <c r="E3360" t="n">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="3361">
+      <c r="A3361" t="n">
+        <v>33</v>
+      </c>
+      <c r="B3361" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3361" t="n">
+        <v>38</v>
+      </c>
+      <c r="D3361" t="n">
+        <v>34</v>
+      </c>
+      <c r="E3361" t="n">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="3362">
+      <c r="A3362" t="n">
+        <v>34</v>
+      </c>
+      <c r="B3362" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3362" t="n">
+        <v>26</v>
+      </c>
+      <c r="D3362" t="n">
+        <v>41</v>
+      </c>
+      <c r="E3362" t="n">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="3363">
+      <c r="A3363" t="n">
+        <v>35</v>
+      </c>
+      <c r="B3363" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3363" t="n">
+        <v>85</v>
+      </c>
+      <c r="D3363" t="n">
+        <v>84</v>
+      </c>
+      <c r="E3363" t="n">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="3364">
+      <c r="A3364" t="n">
+        <v>36</v>
+      </c>
+      <c r="B3364" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3364" t="n">
+        <v>57</v>
+      </c>
+      <c r="D3364" t="n">
+        <v>31</v>
+      </c>
+      <c r="E3364" t="n">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="3365">
+      <c r="A3365" t="n">
+        <v>37</v>
+      </c>
+      <c r="B3365" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3365" t="n">
+        <v>18</v>
+      </c>
+      <c r="D3365" t="n">
+        <v>16</v>
+      </c>
+      <c r="E3365" t="n">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="3366">
+      <c r="A3366" t="n">
+        <v>38</v>
+      </c>
+      <c r="B3366" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3366" t="n">
+        <v>79</v>
+      </c>
+      <c r="D3366" t="n">
+        <v>46</v>
+      </c>
+      <c r="E3366" t="n">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="3367">
+      <c r="A3367" t="n">
+        <v>39</v>
+      </c>
+      <c r="B3367" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3367" t="n">
+        <v>18</v>
+      </c>
+      <c r="D3367" t="n">
+        <v>98</v>
+      </c>
+      <c r="E3367" t="n">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="3368">
+      <c r="A3368" t="n">
+        <v>40</v>
+      </c>
+      <c r="B3368" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3368" t="n">
+        <v>40</v>
+      </c>
+      <c r="D3368" t="n">
+        <v>6</v>
+      </c>
+      <c r="E3368" t="n">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="3369">
+      <c r="A3369" t="n">
+        <v>41</v>
+      </c>
+      <c r="B3369" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3369" t="n">
+        <v>52</v>
+      </c>
+      <c r="D3369" t="n">
+        <v>26</v>
+      </c>
+      <c r="E3369" t="n">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="3370">
+      <c r="A3370" t="n">
+        <v>42</v>
+      </c>
+      <c r="B3370" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3370" t="n">
+        <v>71</v>
+      </c>
+      <c r="D3370" t="n">
+        <v>29</v>
+      </c>
+      <c r="E3370" t="n">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="3371">
+      <c r="A3371" t="n">
+        <v>43</v>
+      </c>
+      <c r="B3371" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3371" t="n">
+        <v>31</v>
+      </c>
+      <c r="D3371" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3371" t="n">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="3372">
+      <c r="A3372" t="n">
+        <v>44</v>
+      </c>
+      <c r="B3372" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3372" t="n">
+        <v>8</v>
+      </c>
+      <c r="D3372" t="n">
+        <v>35</v>
+      </c>
+      <c r="E3372" t="n">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="3373">
+      <c r="A3373" t="n">
+        <v>45</v>
+      </c>
+      <c r="B3373" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3373" t="n">
+        <v>8</v>
+      </c>
+      <c r="D3373" t="n">
+        <v>97</v>
+      </c>
+      <c r="E3373" t="n">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="3374">
+      <c r="A3374" t="n">
+        <v>46</v>
+      </c>
+      <c r="B3374" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3374" t="n">
+        <v>21</v>
+      </c>
+      <c r="D3374" t="n">
+        <v>47</v>
+      </c>
+      <c r="E3374" t="n">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="3375">
+      <c r="A3375" t="n">
+        <v>47</v>
+      </c>
+      <c r="B3375" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3375" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3375" t="n">
+        <v>4</v>
+      </c>
+      <c r="E3375" t="n">
+        <v>550</v>
       </c>
     </row>
   </sheetData>
@@ -65590,7 +66656,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F228"/>
+  <dimension ref="A1:F231"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -71955,30 +73021,114 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Dbam o Zdrowie Toruń</t>
+          <t>Active Force</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>8547957586</t>
+          <t>7292747755</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>Białystok</t>
+          <t>Dąbrowa Górnicza</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
+          <t>Apteka</t>
+        </is>
+      </c>
+      <c r="F228" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>238</v>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Care Energy Partner</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>4247843015</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Częstochowa</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>Supermarket / drogeria wielkopowierzchniowa</t>
+        </is>
+      </c>
+      <c r="F229" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>239</v>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Herbapol Life &amp; Synowie</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>7206057044</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Jaworzno</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>Zielarnia</t>
+        </is>
+      </c>
+      <c r="F230" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="n">
+        <v>240</v>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dbam o Zdrowie Expert </t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>2182766158</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>Nowy Targ</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
           <t>Siłownia / klub sportowy</t>
         </is>
       </c>
-      <c r="F228" t="n">
-        <v>15</v>
+      <c r="F231" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/dane.xlsx
+++ b/dane.xlsx
@@ -3759,7 +3759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G551"/>
+  <dimension ref="A1:G561"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17547,6 +17547,256 @@
       </c>
       <c r="G551" t="n">
         <v>1408</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="n">
+        <v>551</v>
+      </c>
+      <c r="B552" s="2" t="n">
+        <v>46064</v>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>Wysłane</t>
+        </is>
+      </c>
+      <c r="D552" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E552" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F552" t="n">
+        <v>3</v>
+      </c>
+      <c r="G552" t="n">
+        <v>1101</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="n">
+        <v>552</v>
+      </c>
+      <c r="B553" s="2" t="n">
+        <v>46089</v>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>Zwrot</t>
+        </is>
+      </c>
+      <c r="D553" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="E553" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F553" t="n">
+        <v>3</v>
+      </c>
+      <c r="G553" t="n">
+        <v>2346</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="n">
+        <v>553</v>
+      </c>
+      <c r="B554" s="2" t="n">
+        <v>46076</v>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>Nowe</t>
+        </is>
+      </c>
+      <c r="D554" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="E554" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F554" t="n">
+        <v>4</v>
+      </c>
+      <c r="G554" t="n">
+        <v>2514</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="n">
+        <v>554</v>
+      </c>
+      <c r="B555" s="2" t="n">
+        <v>46069</v>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>Zwrot</t>
+        </is>
+      </c>
+      <c r="D555" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="E555" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F555" t="n">
+        <v>3</v>
+      </c>
+      <c r="G555" t="n">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="n">
+        <v>555</v>
+      </c>
+      <c r="B556" s="2" t="n">
+        <v>46078</v>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>Nowe</t>
+        </is>
+      </c>
+      <c r="D556" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E556" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F556" t="n">
+        <v>2</v>
+      </c>
+      <c r="G556" t="n">
+        <v>3321</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="n">
+        <v>556</v>
+      </c>
+      <c r="B557" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>Zwrot</t>
+        </is>
+      </c>
+      <c r="D557" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="E557" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F557" t="n">
+        <v>3</v>
+      </c>
+      <c r="G557" t="n">
+        <v>2860</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="n">
+        <v>557</v>
+      </c>
+      <c r="B558" s="2" t="n">
+        <v>46064</v>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>Dostarczone</t>
+        </is>
+      </c>
+      <c r="D558" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="E558" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F558" t="n">
+        <v>1</v>
+      </c>
+      <c r="G558" t="n">
+        <v>1628</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="n">
+        <v>558</v>
+      </c>
+      <c r="B559" s="2" t="n">
+        <v>46089</v>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>Wysłane</t>
+        </is>
+      </c>
+      <c r="D559" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E559" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F559" t="n">
+        <v>1</v>
+      </c>
+      <c r="G559" t="n">
+        <v>2467</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="n">
+        <v>559</v>
+      </c>
+      <c r="B560" s="2" t="n">
+        <v>46083</v>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>Dostarczone</t>
+        </is>
+      </c>
+      <c r="D560" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E560" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F560" t="n">
+        <v>1</v>
+      </c>
+      <c r="G560" t="n">
+        <v>2148</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="n">
+        <v>560</v>
+      </c>
+      <c r="B561" s="2" t="n">
+        <v>46076</v>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>Zwrot</t>
+        </is>
+      </c>
+      <c r="D561" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="E561" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F561" t="n">
+        <v>2</v>
+      </c>
+      <c r="G561" t="n">
+        <v>920</v>
       </c>
     </row>
   </sheetData>
@@ -17560,7 +17810,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3375"/>
+  <dimension ref="A1:E3426"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66643,6 +66893,873 @@
       </c>
       <c r="E3375" t="n">
         <v>550</v>
+      </c>
+    </row>
+    <row r="3376">
+      <c r="A3376" t="n">
+        <v>0</v>
+      </c>
+      <c r="B3376" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3376" t="n">
+        <v>82</v>
+      </c>
+      <c r="D3376" t="n">
+        <v>20</v>
+      </c>
+      <c r="E3376" t="n">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="3377">
+      <c r="A3377" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3377" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3377" t="n">
+        <v>77</v>
+      </c>
+      <c r="D3377" t="n">
+        <v>58</v>
+      </c>
+      <c r="E3377" t="n">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="3378">
+      <c r="A3378" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3378" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3378" t="n">
+        <v>55</v>
+      </c>
+      <c r="D3378" t="n">
+        <v>39</v>
+      </c>
+      <c r="E3378" t="n">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="3379">
+      <c r="A3379" t="n">
+        <v>3</v>
+      </c>
+      <c r="B3379" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3379" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3379" t="n">
+        <v>7</v>
+      </c>
+      <c r="E3379" t="n">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="3380">
+      <c r="A3380" t="n">
+        <v>4</v>
+      </c>
+      <c r="B3380" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3380" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3380" t="n">
+        <v>47</v>
+      </c>
+      <c r="E3380" t="n">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="3381">
+      <c r="A3381" t="n">
+        <v>5</v>
+      </c>
+      <c r="B3381" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3381" t="n">
+        <v>20</v>
+      </c>
+      <c r="D3381" t="n">
+        <v>97</v>
+      </c>
+      <c r="E3381" t="n">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="3382">
+      <c r="A3382" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3382" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3382" t="n">
+        <v>57</v>
+      </c>
+      <c r="D3382" t="n">
+        <v>85</v>
+      </c>
+      <c r="E3382" t="n">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="3383">
+      <c r="A3383" t="n">
+        <v>7</v>
+      </c>
+      <c r="B3383" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3383" t="n">
+        <v>66</v>
+      </c>
+      <c r="D3383" t="n">
+        <v>39</v>
+      </c>
+      <c r="E3383" t="n">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="3384">
+      <c r="A3384" t="n">
+        <v>8</v>
+      </c>
+      <c r="B3384" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3384" t="n">
+        <v>21</v>
+      </c>
+      <c r="D3384" t="n">
+        <v>38</v>
+      </c>
+      <c r="E3384" t="n">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="3385">
+      <c r="A3385" t="n">
+        <v>9</v>
+      </c>
+      <c r="B3385" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3385" t="n">
+        <v>23</v>
+      </c>
+      <c r="D3385" t="n">
+        <v>45</v>
+      </c>
+      <c r="E3385" t="n">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="3386">
+      <c r="A3386" t="n">
+        <v>10</v>
+      </c>
+      <c r="B3386" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3386" t="n">
+        <v>60</v>
+      </c>
+      <c r="D3386" t="n">
+        <v>28</v>
+      </c>
+      <c r="E3386" t="n">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="3387">
+      <c r="A3387" t="n">
+        <v>11</v>
+      </c>
+      <c r="B3387" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3387" t="n">
+        <v>93</v>
+      </c>
+      <c r="D3387" t="n">
+        <v>12</v>
+      </c>
+      <c r="E3387" t="n">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="3388">
+      <c r="A3388" t="n">
+        <v>12</v>
+      </c>
+      <c r="B3388" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3388" t="n">
+        <v>5</v>
+      </c>
+      <c r="D3388" t="n">
+        <v>18</v>
+      </c>
+      <c r="E3388" t="n">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="3389">
+      <c r="A3389" t="n">
+        <v>13</v>
+      </c>
+      <c r="B3389" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3389" t="n">
+        <v>37</v>
+      </c>
+      <c r="D3389" t="n">
+        <v>16</v>
+      </c>
+      <c r="E3389" t="n">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="3390">
+      <c r="A3390" t="n">
+        <v>14</v>
+      </c>
+      <c r="B3390" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3390" t="n">
+        <v>17</v>
+      </c>
+      <c r="D3390" t="n">
+        <v>95</v>
+      </c>
+      <c r="E3390" t="n">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="3391">
+      <c r="A3391" t="n">
+        <v>15</v>
+      </c>
+      <c r="B3391" t="n">
+        <v>7</v>
+      </c>
+      <c r="C3391" t="n">
+        <v>98</v>
+      </c>
+      <c r="D3391" t="n">
+        <v>92</v>
+      </c>
+      <c r="E3391" t="n">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="3392">
+      <c r="A3392" t="n">
+        <v>16</v>
+      </c>
+      <c r="B3392" t="n">
+        <v>8</v>
+      </c>
+      <c r="C3392" t="n">
+        <v>14</v>
+      </c>
+      <c r="D3392" t="n">
+        <v>86</v>
+      </c>
+      <c r="E3392" t="n">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="3393">
+      <c r="A3393" t="n">
+        <v>17</v>
+      </c>
+      <c r="B3393" t="n">
+        <v>9</v>
+      </c>
+      <c r="C3393" t="n">
+        <v>91</v>
+      </c>
+      <c r="D3393" t="n">
+        <v>27</v>
+      </c>
+      <c r="E3393" t="n">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="3394">
+      <c r="A3394" t="n">
+        <v>18</v>
+      </c>
+      <c r="B3394" t="n">
+        <v>10</v>
+      </c>
+      <c r="C3394" t="n">
+        <v>98</v>
+      </c>
+      <c r="D3394" t="n">
+        <v>47</v>
+      </c>
+      <c r="E3394" t="n">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="3395">
+      <c r="A3395" t="n">
+        <v>19</v>
+      </c>
+      <c r="B3395" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3395" t="n">
+        <v>49</v>
+      </c>
+      <c r="D3395" t="n">
+        <v>19</v>
+      </c>
+      <c r="E3395" t="n">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="3396">
+      <c r="A3396" t="n">
+        <v>20</v>
+      </c>
+      <c r="B3396" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3396" t="n">
+        <v>65</v>
+      </c>
+      <c r="D3396" t="n">
+        <v>59</v>
+      </c>
+      <c r="E3396" t="n">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="3397">
+      <c r="A3397" t="n">
+        <v>21</v>
+      </c>
+      <c r="B3397" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3397" t="n">
+        <v>11</v>
+      </c>
+      <c r="D3397" t="n">
+        <v>66</v>
+      </c>
+      <c r="E3397" t="n">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="3398">
+      <c r="A3398" t="n">
+        <v>22</v>
+      </c>
+      <c r="B3398" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3398" t="n">
+        <v>61</v>
+      </c>
+      <c r="D3398" t="n">
+        <v>50</v>
+      </c>
+      <c r="E3398" t="n">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="3399">
+      <c r="A3399" t="n">
+        <v>23</v>
+      </c>
+      <c r="B3399" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3399" t="n">
+        <v>67</v>
+      </c>
+      <c r="D3399" t="n">
+        <v>100</v>
+      </c>
+      <c r="E3399" t="n">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="3400">
+      <c r="A3400" t="n">
+        <v>24</v>
+      </c>
+      <c r="B3400" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3400" t="n">
+        <v>96</v>
+      </c>
+      <c r="D3400" t="n">
+        <v>24</v>
+      </c>
+      <c r="E3400" t="n">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="3401">
+      <c r="A3401" t="n">
+        <v>25</v>
+      </c>
+      <c r="B3401" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3401" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3401" t="n">
+        <v>97</v>
+      </c>
+      <c r="E3401" t="n">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="3402">
+      <c r="A3402" t="n">
+        <v>26</v>
+      </c>
+      <c r="B3402" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3402" t="n">
+        <v>23</v>
+      </c>
+      <c r="D3402" t="n">
+        <v>38</v>
+      </c>
+      <c r="E3402" t="n">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="3403">
+      <c r="A3403" t="n">
+        <v>27</v>
+      </c>
+      <c r="B3403" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3403" t="n">
+        <v>93</v>
+      </c>
+      <c r="D3403" t="n">
+        <v>23</v>
+      </c>
+      <c r="E3403" t="n">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="3404">
+      <c r="A3404" t="n">
+        <v>28</v>
+      </c>
+      <c r="B3404" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3404" t="n">
+        <v>59</v>
+      </c>
+      <c r="D3404" t="n">
+        <v>31</v>
+      </c>
+      <c r="E3404" t="n">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="3405">
+      <c r="A3405" t="n">
+        <v>29</v>
+      </c>
+      <c r="B3405" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3405" t="n">
+        <v>16</v>
+      </c>
+      <c r="D3405" t="n">
+        <v>20</v>
+      </c>
+      <c r="E3405" t="n">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="3406">
+      <c r="A3406" t="n">
+        <v>30</v>
+      </c>
+      <c r="B3406" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3406" t="n">
+        <v>46</v>
+      </c>
+      <c r="D3406" t="n">
+        <v>99</v>
+      </c>
+      <c r="E3406" t="n">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="3407">
+      <c r="A3407" t="n">
+        <v>31</v>
+      </c>
+      <c r="B3407" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3407" t="n">
+        <v>42</v>
+      </c>
+      <c r="D3407" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3407" t="n">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="3408">
+      <c r="A3408" t="n">
+        <v>32</v>
+      </c>
+      <c r="B3408" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3408" t="n">
+        <v>25</v>
+      </c>
+      <c r="D3408" t="n">
+        <v>34</v>
+      </c>
+      <c r="E3408" t="n">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="3409">
+      <c r="A3409" t="n">
+        <v>33</v>
+      </c>
+      <c r="B3409" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3409" t="n">
+        <v>11</v>
+      </c>
+      <c r="D3409" t="n">
+        <v>14</v>
+      </c>
+      <c r="E3409" t="n">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="3410">
+      <c r="A3410" t="n">
+        <v>34</v>
+      </c>
+      <c r="B3410" t="n">
+        <v>7</v>
+      </c>
+      <c r="C3410" t="n">
+        <v>11</v>
+      </c>
+      <c r="D3410" t="n">
+        <v>85</v>
+      </c>
+      <c r="E3410" t="n">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="3411">
+      <c r="A3411" t="n">
+        <v>35</v>
+      </c>
+      <c r="B3411" t="n">
+        <v>8</v>
+      </c>
+      <c r="C3411" t="n">
+        <v>18</v>
+      </c>
+      <c r="D3411" t="n">
+        <v>36</v>
+      </c>
+      <c r="E3411" t="n">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="3412">
+      <c r="A3412" t="n">
+        <v>36</v>
+      </c>
+      <c r="B3412" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3412" t="n">
+        <v>86</v>
+      </c>
+      <c r="D3412" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3412" t="n">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="3413">
+      <c r="A3413" t="n">
+        <v>37</v>
+      </c>
+      <c r="B3413" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3413" t="n">
+        <v>54</v>
+      </c>
+      <c r="D3413" t="n">
+        <v>16</v>
+      </c>
+      <c r="E3413" t="n">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="3414">
+      <c r="A3414" t="n">
+        <v>38</v>
+      </c>
+      <c r="B3414" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3414" t="n">
+        <v>66</v>
+      </c>
+      <c r="D3414" t="n">
+        <v>37</v>
+      </c>
+      <c r="E3414" t="n">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="3415">
+      <c r="A3415" t="n">
+        <v>39</v>
+      </c>
+      <c r="B3415" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3415" t="n">
+        <v>7</v>
+      </c>
+      <c r="D3415" t="n">
+        <v>61</v>
+      </c>
+      <c r="E3415" t="n">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="3416">
+      <c r="A3416" t="n">
+        <v>40</v>
+      </c>
+      <c r="B3416" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3416" t="n">
+        <v>91</v>
+      </c>
+      <c r="D3416" t="n">
+        <v>33</v>
+      </c>
+      <c r="E3416" t="n">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="3417">
+      <c r="A3417" t="n">
+        <v>41</v>
+      </c>
+      <c r="B3417" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3417" t="n">
+        <v>26</v>
+      </c>
+      <c r="D3417" t="n">
+        <v>95</v>
+      </c>
+      <c r="E3417" t="n">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="3418">
+      <c r="A3418" t="n">
+        <v>42</v>
+      </c>
+      <c r="B3418" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3418" t="n">
+        <v>80</v>
+      </c>
+      <c r="D3418" t="n">
+        <v>73</v>
+      </c>
+      <c r="E3418" t="n">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="3419">
+      <c r="A3419" t="n">
+        <v>43</v>
+      </c>
+      <c r="B3419" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3419" t="n">
+        <v>96</v>
+      </c>
+      <c r="D3419" t="n">
+        <v>87</v>
+      </c>
+      <c r="E3419" t="n">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="3420">
+      <c r="A3420" t="n">
+        <v>44</v>
+      </c>
+      <c r="B3420" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3420" t="n">
+        <v>18</v>
+      </c>
+      <c r="D3420" t="n">
+        <v>61</v>
+      </c>
+      <c r="E3420" t="n">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="3421">
+      <c r="A3421" t="n">
+        <v>45</v>
+      </c>
+      <c r="B3421" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3421" t="n">
+        <v>51</v>
+      </c>
+      <c r="D3421" t="n">
+        <v>31</v>
+      </c>
+      <c r="E3421" t="n">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="3422">
+      <c r="A3422" t="n">
+        <v>46</v>
+      </c>
+      <c r="B3422" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3422" t="n">
+        <v>93</v>
+      </c>
+      <c r="D3422" t="n">
+        <v>7</v>
+      </c>
+      <c r="E3422" t="n">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="3423">
+      <c r="A3423" t="n">
+        <v>47</v>
+      </c>
+      <c r="B3423" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3423" t="n">
+        <v>78</v>
+      </c>
+      <c r="D3423" t="n">
+        <v>62</v>
+      </c>
+      <c r="E3423" t="n">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="3424">
+      <c r="A3424" t="n">
+        <v>48</v>
+      </c>
+      <c r="B3424" t="n">
+        <v>7</v>
+      </c>
+      <c r="C3424" t="n">
+        <v>86</v>
+      </c>
+      <c r="D3424" t="n">
+        <v>26</v>
+      </c>
+      <c r="E3424" t="n">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="3425">
+      <c r="A3425" t="n">
+        <v>49</v>
+      </c>
+      <c r="B3425" t="n">
+        <v>8</v>
+      </c>
+      <c r="C3425" t="n">
+        <v>20</v>
+      </c>
+      <c r="D3425" t="n">
+        <v>89</v>
+      </c>
+      <c r="E3425" t="n">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="3426">
+      <c r="A3426" t="n">
+        <v>50</v>
+      </c>
+      <c r="B3426" t="n">
+        <v>9</v>
+      </c>
+      <c r="C3426" t="n">
+        <v>20</v>
+      </c>
+      <c r="D3426" t="n">
+        <v>63</v>
+      </c>
+      <c r="E3426" t="n">
+        <v>560</v>
       </c>
     </row>
   </sheetData>
@@ -66656,7 +67773,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F231"/>
+  <dimension ref="A1:F234"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73105,30 +74222,114 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dbam o Zdrowie Expert </t>
+          <t>Power Kraków</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>2182766158</t>
+          <t>7303043147</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Nowy Targ</t>
+          <t>Zakopane</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Siłownia / klub sportowy</t>
+          <t>Drogeria specjalistyczna</t>
         </is>
       </c>
       <c r="F231" t="n">
-        <v>1</v>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
+        <v>242</v>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Pro Muscle Bielsko-Biała</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>8630248238</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>Gorzów Wielkopolski</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>Sklep internetowy z suplementami</t>
+        </is>
+      </c>
+      <c r="F232" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
+        <v>243</v>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Power Zielona Góra</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>5361536383</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Tarnobrzeg</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>Zielarnia</t>
+        </is>
+      </c>
+      <c r="F233" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="n">
+        <v>244</v>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Vita Max</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>7440930474</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Cieszyn</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>Sklep internetowy z suplementami</t>
+        </is>
+      </c>
+      <c r="F234" t="n">
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/dane.xlsx
+++ b/dane.xlsx
@@ -3759,7 +3759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G561"/>
+  <dimension ref="A1:G571"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17797,6 +17797,256 @@
       </c>
       <c r="G561" t="n">
         <v>920</v>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="n">
+        <v>561</v>
+      </c>
+      <c r="B562" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>Dostarczone</t>
+        </is>
+      </c>
+      <c r="D562" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E562" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F562" t="n">
+        <v>3</v>
+      </c>
+      <c r="G562" t="n">
+        <v>1973</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="n">
+        <v>562</v>
+      </c>
+      <c r="B563" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>Wysłane</t>
+        </is>
+      </c>
+      <c r="D563" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="E563" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F563" t="n">
+        <v>4</v>
+      </c>
+      <c r="G563" t="n">
+        <v>2254</v>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="n">
+        <v>563</v>
+      </c>
+      <c r="B564" s="2" t="n">
+        <v>46070</v>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>Wysłane</t>
+        </is>
+      </c>
+      <c r="D564" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E564" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F564" t="n">
+        <v>4</v>
+      </c>
+      <c r="G564" t="n">
+        <v>2553</v>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="n">
+        <v>564</v>
+      </c>
+      <c r="B565" s="2" t="n">
+        <v>46076</v>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>Dostarczone</t>
+        </is>
+      </c>
+      <c r="D565" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="E565" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F565" t="n">
+        <v>1</v>
+      </c>
+      <c r="G565" t="n">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="n">
+        <v>565</v>
+      </c>
+      <c r="B566" s="2" t="n">
+        <v>46089</v>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>Dostarczone</t>
+        </is>
+      </c>
+      <c r="D566" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="E566" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F566" t="n">
+        <v>3</v>
+      </c>
+      <c r="G566" t="n">
+        <v>3061</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="n">
+        <v>566</v>
+      </c>
+      <c r="B567" s="2" t="n">
+        <v>46080</v>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>Zwrot</t>
+        </is>
+      </c>
+      <c r="D567" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="E567" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F567" t="n">
+        <v>4</v>
+      </c>
+      <c r="G567" t="n">
+        <v>1728</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="n">
+        <v>567</v>
+      </c>
+      <c r="B568" s="2" t="n">
+        <v>46090</v>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>Dostarczone</t>
+        </is>
+      </c>
+      <c r="D568" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="E568" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F568" t="n">
+        <v>2</v>
+      </c>
+      <c r="G568" t="n">
+        <v>2890</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="n">
+        <v>568</v>
+      </c>
+      <c r="B569" s="2" t="n">
+        <v>46063</v>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>Zwrot</t>
+        </is>
+      </c>
+      <c r="D569" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E569" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F569" t="n">
+        <v>1</v>
+      </c>
+      <c r="G569" t="n">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="n">
+        <v>569</v>
+      </c>
+      <c r="B570" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>Dostarczone</t>
+        </is>
+      </c>
+      <c r="D570" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E570" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F570" t="n">
+        <v>2</v>
+      </c>
+      <c r="G570" t="n">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="n">
+        <v>570</v>
+      </c>
+      <c r="B571" s="2" t="n">
+        <v>46063</v>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>Zwrot</t>
+        </is>
+      </c>
+      <c r="D571" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="E571" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F571" t="n">
+        <v>3</v>
+      </c>
+      <c r="G571" t="n">
+        <v>2427</v>
       </c>
     </row>
   </sheetData>
@@ -17810,7 +18060,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3426"/>
+  <dimension ref="A1:E3496"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67760,6 +68010,1196 @@
       </c>
       <c r="E3426" t="n">
         <v>560</v>
+      </c>
+    </row>
+    <row r="3427">
+      <c r="A3427" t="n">
+        <v>0</v>
+      </c>
+      <c r="B3427" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3427" t="n">
+        <v>47</v>
+      </c>
+      <c r="D3427" t="n">
+        <v>87</v>
+      </c>
+      <c r="E3427" t="n">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="3428">
+      <c r="A3428" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3428" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3428" t="n">
+        <v>96</v>
+      </c>
+      <c r="D3428" t="n">
+        <v>62</v>
+      </c>
+      <c r="E3428" t="n">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="3429">
+      <c r="A3429" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3429" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3429" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3429" t="n">
+        <v>50</v>
+      </c>
+      <c r="E3429" t="n">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="3430">
+      <c r="A3430" t="n">
+        <v>3</v>
+      </c>
+      <c r="B3430" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3430" t="n">
+        <v>30</v>
+      </c>
+      <c r="D3430" t="n">
+        <v>99</v>
+      </c>
+      <c r="E3430" t="n">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="3431">
+      <c r="A3431" t="n">
+        <v>4</v>
+      </c>
+      <c r="B3431" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3431" t="n">
+        <v>96</v>
+      </c>
+      <c r="D3431" t="n">
+        <v>43</v>
+      </c>
+      <c r="E3431" t="n">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="3432">
+      <c r="A3432" t="n">
+        <v>5</v>
+      </c>
+      <c r="B3432" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3432" t="n">
+        <v>98</v>
+      </c>
+      <c r="D3432" t="n">
+        <v>72</v>
+      </c>
+      <c r="E3432" t="n">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="3433">
+      <c r="A3433" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3433" t="n">
+        <v>7</v>
+      </c>
+      <c r="C3433" t="n">
+        <v>92</v>
+      </c>
+      <c r="D3433" t="n">
+        <v>48</v>
+      </c>
+      <c r="E3433" t="n">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="3434">
+      <c r="A3434" t="n">
+        <v>7</v>
+      </c>
+      <c r="B3434" t="n">
+        <v>8</v>
+      </c>
+      <c r="C3434" t="n">
+        <v>25</v>
+      </c>
+      <c r="D3434" t="n">
+        <v>46</v>
+      </c>
+      <c r="E3434" t="n">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="3435">
+      <c r="A3435" t="n">
+        <v>8</v>
+      </c>
+      <c r="B3435" t="n">
+        <v>9</v>
+      </c>
+      <c r="C3435" t="n">
+        <v>63</v>
+      </c>
+      <c r="D3435" t="n">
+        <v>53</v>
+      </c>
+      <c r="E3435" t="n">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="3436">
+      <c r="A3436" t="n">
+        <v>9</v>
+      </c>
+      <c r="B3436" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3436" t="n">
+        <v>18</v>
+      </c>
+      <c r="D3436" t="n">
+        <v>93</v>
+      </c>
+      <c r="E3436" t="n">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="3437">
+      <c r="A3437" t="n">
+        <v>10</v>
+      </c>
+      <c r="B3437" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3437" t="n">
+        <v>49</v>
+      </c>
+      <c r="D3437" t="n">
+        <v>35</v>
+      </c>
+      <c r="E3437" t="n">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="3438">
+      <c r="A3438" t="n">
+        <v>11</v>
+      </c>
+      <c r="B3438" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3438" t="n">
+        <v>54</v>
+      </c>
+      <c r="D3438" t="n">
+        <v>73</v>
+      </c>
+      <c r="E3438" t="n">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="3439">
+      <c r="A3439" t="n">
+        <v>12</v>
+      </c>
+      <c r="B3439" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3439" t="n">
+        <v>43</v>
+      </c>
+      <c r="D3439" t="n">
+        <v>62</v>
+      </c>
+      <c r="E3439" t="n">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="3440">
+      <c r="A3440" t="n">
+        <v>13</v>
+      </c>
+      <c r="B3440" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3440" t="n">
+        <v>86</v>
+      </c>
+      <c r="D3440" t="n">
+        <v>93</v>
+      </c>
+      <c r="E3440" t="n">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="3441">
+      <c r="A3441" t="n">
+        <v>14</v>
+      </c>
+      <c r="B3441" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3441" t="n">
+        <v>54</v>
+      </c>
+      <c r="D3441" t="n">
+        <v>95</v>
+      </c>
+      <c r="E3441" t="n">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="3442">
+      <c r="A3442" t="n">
+        <v>15</v>
+      </c>
+      <c r="B3442" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3442" t="n">
+        <v>94</v>
+      </c>
+      <c r="D3442" t="n">
+        <v>100</v>
+      </c>
+      <c r="E3442" t="n">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="3443">
+      <c r="A3443" t="n">
+        <v>16</v>
+      </c>
+      <c r="B3443" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3443" t="n">
+        <v>80</v>
+      </c>
+      <c r="D3443" t="n">
+        <v>100</v>
+      </c>
+      <c r="E3443" t="n">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="3444">
+      <c r="A3444" t="n">
+        <v>17</v>
+      </c>
+      <c r="B3444" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3444" t="n">
+        <v>87</v>
+      </c>
+      <c r="D3444" t="n">
+        <v>90</v>
+      </c>
+      <c r="E3444" t="n">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="3445">
+      <c r="A3445" t="n">
+        <v>18</v>
+      </c>
+      <c r="B3445" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3445" t="n">
+        <v>8</v>
+      </c>
+      <c r="D3445" t="n">
+        <v>91</v>
+      </c>
+      <c r="E3445" t="n">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="3446">
+      <c r="A3446" t="n">
+        <v>19</v>
+      </c>
+      <c r="B3446" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3446" t="n">
+        <v>30</v>
+      </c>
+      <c r="D3446" t="n">
+        <v>55</v>
+      </c>
+      <c r="E3446" t="n">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="3447">
+      <c r="A3447" t="n">
+        <v>20</v>
+      </c>
+      <c r="B3447" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3447" t="n">
+        <v>25</v>
+      </c>
+      <c r="D3447" t="n">
+        <v>18</v>
+      </c>
+      <c r="E3447" t="n">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="3448">
+      <c r="A3448" t="n">
+        <v>21</v>
+      </c>
+      <c r="B3448" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3448" t="n">
+        <v>45</v>
+      </c>
+      <c r="D3448" t="n">
+        <v>81</v>
+      </c>
+      <c r="E3448" t="n">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="3449">
+      <c r="A3449" t="n">
+        <v>22</v>
+      </c>
+      <c r="B3449" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3449" t="n">
+        <v>87</v>
+      </c>
+      <c r="D3449" t="n">
+        <v>13</v>
+      </c>
+      <c r="E3449" t="n">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="3450">
+      <c r="A3450" t="n">
+        <v>23</v>
+      </c>
+      <c r="B3450" t="n">
+        <v>7</v>
+      </c>
+      <c r="C3450" t="n">
+        <v>54</v>
+      </c>
+      <c r="D3450" t="n">
+        <v>33</v>
+      </c>
+      <c r="E3450" t="n">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="3451">
+      <c r="A3451" t="n">
+        <v>24</v>
+      </c>
+      <c r="B3451" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3451" t="n">
+        <v>29</v>
+      </c>
+      <c r="D3451" t="n">
+        <v>89</v>
+      </c>
+      <c r="E3451" t="n">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="3452">
+      <c r="A3452" t="n">
+        <v>25</v>
+      </c>
+      <c r="B3452" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3452" t="n">
+        <v>61</v>
+      </c>
+      <c r="D3452" t="n">
+        <v>84</v>
+      </c>
+      <c r="E3452" t="n">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="3453">
+      <c r="A3453" t="n">
+        <v>26</v>
+      </c>
+      <c r="B3453" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3453" t="n">
+        <v>8</v>
+      </c>
+      <c r="D3453" t="n">
+        <v>21</v>
+      </c>
+      <c r="E3453" t="n">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="3454">
+      <c r="A3454" t="n">
+        <v>27</v>
+      </c>
+      <c r="B3454" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3454" t="n">
+        <v>81</v>
+      </c>
+      <c r="D3454" t="n">
+        <v>93</v>
+      </c>
+      <c r="E3454" t="n">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="3455">
+      <c r="A3455" t="n">
+        <v>28</v>
+      </c>
+      <c r="B3455" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3455" t="n">
+        <v>60</v>
+      </c>
+      <c r="D3455" t="n">
+        <v>90</v>
+      </c>
+      <c r="E3455" t="n">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="3456">
+      <c r="A3456" t="n">
+        <v>29</v>
+      </c>
+      <c r="B3456" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3456" t="n">
+        <v>59</v>
+      </c>
+      <c r="D3456" t="n">
+        <v>49</v>
+      </c>
+      <c r="E3456" t="n">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="3457">
+      <c r="A3457" t="n">
+        <v>30</v>
+      </c>
+      <c r="B3457" t="n">
+        <v>7</v>
+      </c>
+      <c r="C3457" t="n">
+        <v>47</v>
+      </c>
+      <c r="D3457" t="n">
+        <v>17</v>
+      </c>
+      <c r="E3457" t="n">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="3458">
+      <c r="A3458" t="n">
+        <v>31</v>
+      </c>
+      <c r="B3458" t="n">
+        <v>8</v>
+      </c>
+      <c r="C3458" t="n">
+        <v>77</v>
+      </c>
+      <c r="D3458" t="n">
+        <v>57</v>
+      </c>
+      <c r="E3458" t="n">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="3459">
+      <c r="A3459" t="n">
+        <v>32</v>
+      </c>
+      <c r="B3459" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3459" t="n">
+        <v>46</v>
+      </c>
+      <c r="D3459" t="n">
+        <v>63</v>
+      </c>
+      <c r="E3459" t="n">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="3460">
+      <c r="A3460" t="n">
+        <v>33</v>
+      </c>
+      <c r="B3460" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3460" t="n">
+        <v>23</v>
+      </c>
+      <c r="D3460" t="n">
+        <v>17</v>
+      </c>
+      <c r="E3460" t="n">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="3461">
+      <c r="A3461" t="n">
+        <v>34</v>
+      </c>
+      <c r="B3461" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3461" t="n">
+        <v>83</v>
+      </c>
+      <c r="D3461" t="n">
+        <v>98</v>
+      </c>
+      <c r="E3461" t="n">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="3462">
+      <c r="A3462" t="n">
+        <v>35</v>
+      </c>
+      <c r="B3462" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3462" t="n">
+        <v>27</v>
+      </c>
+      <c r="D3462" t="n">
+        <v>43</v>
+      </c>
+      <c r="E3462" t="n">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="3463">
+      <c r="A3463" t="n">
+        <v>36</v>
+      </c>
+      <c r="B3463" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3463" t="n">
+        <v>79</v>
+      </c>
+      <c r="D3463" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3463" t="n">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="3464">
+      <c r="A3464" t="n">
+        <v>37</v>
+      </c>
+      <c r="B3464" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3464" t="n">
+        <v>66</v>
+      </c>
+      <c r="D3464" t="n">
+        <v>28</v>
+      </c>
+      <c r="E3464" t="n">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="3465">
+      <c r="A3465" t="n">
+        <v>38</v>
+      </c>
+      <c r="B3465" t="n">
+        <v>7</v>
+      </c>
+      <c r="C3465" t="n">
+        <v>14</v>
+      </c>
+      <c r="D3465" t="n">
+        <v>38</v>
+      </c>
+      <c r="E3465" t="n">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="3466">
+      <c r="A3466" t="n">
+        <v>39</v>
+      </c>
+      <c r="B3466" t="n">
+        <v>8</v>
+      </c>
+      <c r="C3466" t="n">
+        <v>11</v>
+      </c>
+      <c r="D3466" t="n">
+        <v>57</v>
+      </c>
+      <c r="E3466" t="n">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="3467">
+      <c r="A3467" t="n">
+        <v>40</v>
+      </c>
+      <c r="B3467" t="n">
+        <v>9</v>
+      </c>
+      <c r="C3467" t="n">
+        <v>30</v>
+      </c>
+      <c r="D3467" t="n">
+        <v>41</v>
+      </c>
+      <c r="E3467" t="n">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="3468">
+      <c r="A3468" t="n">
+        <v>41</v>
+      </c>
+      <c r="B3468" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3468" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3468" t="n">
+        <v>43</v>
+      </c>
+      <c r="E3468" t="n">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="3469">
+      <c r="A3469" t="n">
+        <v>42</v>
+      </c>
+      <c r="B3469" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3469" t="n">
+        <v>75</v>
+      </c>
+      <c r="D3469" t="n">
+        <v>89</v>
+      </c>
+      <c r="E3469" t="n">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="3470">
+      <c r="A3470" t="n">
+        <v>43</v>
+      </c>
+      <c r="B3470" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3470" t="n">
+        <v>87</v>
+      </c>
+      <c r="D3470" t="n">
+        <v>7</v>
+      </c>
+      <c r="E3470" t="n">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="3471">
+      <c r="A3471" t="n">
+        <v>44</v>
+      </c>
+      <c r="B3471" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3471" t="n">
+        <v>77</v>
+      </c>
+      <c r="D3471" t="n">
+        <v>6</v>
+      </c>
+      <c r="E3471" t="n">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="3472">
+      <c r="A3472" t="n">
+        <v>45</v>
+      </c>
+      <c r="B3472" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3472" t="n">
+        <v>77</v>
+      </c>
+      <c r="D3472" t="n">
+        <v>38</v>
+      </c>
+      <c r="E3472" t="n">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="3473">
+      <c r="A3473" t="n">
+        <v>46</v>
+      </c>
+      <c r="B3473" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3473" t="n">
+        <v>63</v>
+      </c>
+      <c r="D3473" t="n">
+        <v>11</v>
+      </c>
+      <c r="E3473" t="n">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="3474">
+      <c r="A3474" t="n">
+        <v>47</v>
+      </c>
+      <c r="B3474" t="n">
+        <v>7</v>
+      </c>
+      <c r="C3474" t="n">
+        <v>18</v>
+      </c>
+      <c r="D3474" t="n">
+        <v>87</v>
+      </c>
+      <c r="E3474" t="n">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="3475">
+      <c r="A3475" t="n">
+        <v>48</v>
+      </c>
+      <c r="B3475" t="n">
+        <v>8</v>
+      </c>
+      <c r="C3475" t="n">
+        <v>42</v>
+      </c>
+      <c r="D3475" t="n">
+        <v>94</v>
+      </c>
+      <c r="E3475" t="n">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="3476">
+      <c r="A3476" t="n">
+        <v>49</v>
+      </c>
+      <c r="B3476" t="n">
+        <v>9</v>
+      </c>
+      <c r="C3476" t="n">
+        <v>64</v>
+      </c>
+      <c r="D3476" t="n">
+        <v>62</v>
+      </c>
+      <c r="E3476" t="n">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="3477">
+      <c r="A3477" t="n">
+        <v>50</v>
+      </c>
+      <c r="B3477" t="n">
+        <v>10</v>
+      </c>
+      <c r="C3477" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3477" t="n">
+        <v>89</v>
+      </c>
+      <c r="E3477" t="n">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="3478">
+      <c r="A3478" t="n">
+        <v>51</v>
+      </c>
+      <c r="B3478" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3478" t="n">
+        <v>71</v>
+      </c>
+      <c r="D3478" t="n">
+        <v>94</v>
+      </c>
+      <c r="E3478" t="n">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="3479">
+      <c r="A3479" t="n">
+        <v>52</v>
+      </c>
+      <c r="B3479" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3479" t="n">
+        <v>35</v>
+      </c>
+      <c r="D3479" t="n">
+        <v>64</v>
+      </c>
+      <c r="E3479" t="n">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="3480">
+      <c r="A3480" t="n">
+        <v>53</v>
+      </c>
+      <c r="B3480" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3480" t="n">
+        <v>26</v>
+      </c>
+      <c r="D3480" t="n">
+        <v>86</v>
+      </c>
+      <c r="E3480" t="n">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="3481">
+      <c r="A3481" t="n">
+        <v>54</v>
+      </c>
+      <c r="B3481" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3481" t="n">
+        <v>28</v>
+      </c>
+      <c r="D3481" t="n">
+        <v>6</v>
+      </c>
+      <c r="E3481" t="n">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="3482">
+      <c r="A3482" t="n">
+        <v>55</v>
+      </c>
+      <c r="B3482" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3482" t="n">
+        <v>65</v>
+      </c>
+      <c r="D3482" t="n">
+        <v>51</v>
+      </c>
+      <c r="E3482" t="n">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="3483">
+      <c r="A3483" t="n">
+        <v>56</v>
+      </c>
+      <c r="B3483" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3483" t="n">
+        <v>89</v>
+      </c>
+      <c r="D3483" t="n">
+        <v>45</v>
+      </c>
+      <c r="E3483" t="n">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="3484">
+      <c r="A3484" t="n">
+        <v>57</v>
+      </c>
+      <c r="B3484" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3484" t="n">
+        <v>21</v>
+      </c>
+      <c r="D3484" t="n">
+        <v>25</v>
+      </c>
+      <c r="E3484" t="n">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="3485">
+      <c r="A3485" t="n">
+        <v>58</v>
+      </c>
+      <c r="B3485" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3485" t="n">
+        <v>5</v>
+      </c>
+      <c r="D3485" t="n">
+        <v>17</v>
+      </c>
+      <c r="E3485" t="n">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="3486">
+      <c r="A3486" t="n">
+        <v>59</v>
+      </c>
+      <c r="B3486" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3486" t="n">
+        <v>51</v>
+      </c>
+      <c r="D3486" t="n">
+        <v>11</v>
+      </c>
+      <c r="E3486" t="n">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="3487">
+      <c r="A3487" t="n">
+        <v>60</v>
+      </c>
+      <c r="B3487" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3487" t="n">
+        <v>100</v>
+      </c>
+      <c r="D3487" t="n">
+        <v>85</v>
+      </c>
+      <c r="E3487" t="n">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="3488">
+      <c r="A3488" t="n">
+        <v>61</v>
+      </c>
+      <c r="B3488" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3488" t="n">
+        <v>32</v>
+      </c>
+      <c r="D3488" t="n">
+        <v>17</v>
+      </c>
+      <c r="E3488" t="n">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="3489">
+      <c r="A3489" t="n">
+        <v>62</v>
+      </c>
+      <c r="B3489" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3489" t="n">
+        <v>78</v>
+      </c>
+      <c r="D3489" t="n">
+        <v>71</v>
+      </c>
+      <c r="E3489" t="n">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="3490">
+      <c r="A3490" t="n">
+        <v>63</v>
+      </c>
+      <c r="B3490" t="n">
+        <v>7</v>
+      </c>
+      <c r="C3490" t="n">
+        <v>36</v>
+      </c>
+      <c r="D3490" t="n">
+        <v>76</v>
+      </c>
+      <c r="E3490" t="n">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="3491">
+      <c r="A3491" t="n">
+        <v>64</v>
+      </c>
+      <c r="B3491" t="n">
+        <v>8</v>
+      </c>
+      <c r="C3491" t="n">
+        <v>67</v>
+      </c>
+      <c r="D3491" t="n">
+        <v>49</v>
+      </c>
+      <c r="E3491" t="n">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="3492">
+      <c r="A3492" t="n">
+        <v>65</v>
+      </c>
+      <c r="B3492" t="n">
+        <v>9</v>
+      </c>
+      <c r="C3492" t="n">
+        <v>25</v>
+      </c>
+      <c r="D3492" t="n">
+        <v>49</v>
+      </c>
+      <c r="E3492" t="n">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="3493">
+      <c r="A3493" t="n">
+        <v>66</v>
+      </c>
+      <c r="B3493" t="n">
+        <v>10</v>
+      </c>
+      <c r="C3493" t="n">
+        <v>95</v>
+      </c>
+      <c r="D3493" t="n">
+        <v>80</v>
+      </c>
+      <c r="E3493" t="n">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="3494">
+      <c r="A3494" t="n">
+        <v>67</v>
+      </c>
+      <c r="B3494" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3494" t="n">
+        <v>73</v>
+      </c>
+      <c r="D3494" t="n">
+        <v>5</v>
+      </c>
+      <c r="E3494" t="n">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="3495">
+      <c r="A3495" t="n">
+        <v>68</v>
+      </c>
+      <c r="B3495" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3495" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3495" t="n">
+        <v>61</v>
+      </c>
+      <c r="E3495" t="n">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="3496">
+      <c r="A3496" t="n">
+        <v>69</v>
+      </c>
+      <c r="B3496" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3496" t="n">
+        <v>80</v>
+      </c>
+      <c r="D3496" t="n">
+        <v>44</v>
+      </c>
+      <c r="E3496" t="n">
+        <v>570</v>
       </c>
     </row>
   </sheetData>
@@ -67773,7 +69213,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F234"/>
+  <dimension ref="A1:F237"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74306,30 +75746,114 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Vita Max</t>
+          <t>Natural Bio Białystok</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>7440930474</t>
+          <t>9531436215</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>Cieszyn</t>
+          <t>Szczecin</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Sklep internetowy z suplementami</t>
+          <t>Zielarnia</t>
         </is>
       </c>
       <c r="F234" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
+        <v>246</v>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Herbapol Toruń</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>1873824741</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>Warszawa</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>Gabinet dietetyczny</t>
+        </is>
+      </c>
+      <c r="F235" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="n">
+        <v>247</v>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Glow Tychy</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>4474679929</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>Mysłowice</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>Apteka</t>
+        </is>
+      </c>
+      <c r="F236" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="n">
+        <v>248</v>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Herbapol Eco</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>3917565267</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>Katowice</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>Drogeria specjalistyczna</t>
+        </is>
+      </c>
+      <c r="F237" t="n">
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/dane.xlsx
+++ b/dane.xlsx
@@ -3759,7 +3759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G571"/>
+  <dimension ref="A1:G581"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18047,6 +18047,256 @@
       </c>
       <c r="G571" t="n">
         <v>2427</v>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="n">
+        <v>571</v>
+      </c>
+      <c r="B572" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>Nowe</t>
+        </is>
+      </c>
+      <c r="D572" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E572" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F572" t="n">
+        <v>2</v>
+      </c>
+      <c r="G572" t="n">
+        <v>1317</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="n">
+        <v>572</v>
+      </c>
+      <c r="B573" s="2" t="n">
+        <v>46074</v>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>Zwrot</t>
+        </is>
+      </c>
+      <c r="D573" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="E573" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F573" t="n">
+        <v>2</v>
+      </c>
+      <c r="G573" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="n">
+        <v>573</v>
+      </c>
+      <c r="B574" s="2" t="n">
+        <v>46066</v>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>Wysłane</t>
+        </is>
+      </c>
+      <c r="D574" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="E574" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F574" t="n">
+        <v>2</v>
+      </c>
+      <c r="G574" t="n">
+        <v>2672</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="n">
+        <v>574</v>
+      </c>
+      <c r="B575" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>Wysłane</t>
+        </is>
+      </c>
+      <c r="D575" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E575" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F575" t="n">
+        <v>1</v>
+      </c>
+      <c r="G575" t="n">
+        <v>1455</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="n">
+        <v>575</v>
+      </c>
+      <c r="B576" s="2" t="n">
+        <v>46078</v>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>Dostarczone</t>
+        </is>
+      </c>
+      <c r="D576" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="E576" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F576" t="n">
+        <v>2</v>
+      </c>
+      <c r="G576" t="n">
+        <v>3433</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="n">
+        <v>576</v>
+      </c>
+      <c r="B577" s="2" t="n">
+        <v>46075</v>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>Zwrot</t>
+        </is>
+      </c>
+      <c r="D577" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="E577" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F577" t="n">
+        <v>4</v>
+      </c>
+      <c r="G577" t="n">
+        <v>2576</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="n">
+        <v>577</v>
+      </c>
+      <c r="B578" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>Dostarczone</t>
+        </is>
+      </c>
+      <c r="D578" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="E578" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F578" t="n">
+        <v>1</v>
+      </c>
+      <c r="G578" t="n">
+        <v>1578</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="n">
+        <v>578</v>
+      </c>
+      <c r="B579" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>Wysłane</t>
+        </is>
+      </c>
+      <c r="D579" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E579" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F579" t="n">
+        <v>1</v>
+      </c>
+      <c r="G579" t="n">
+        <v>3367</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="n">
+        <v>579</v>
+      </c>
+      <c r="B580" s="2" t="n">
+        <v>46077</v>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>Nowe</t>
+        </is>
+      </c>
+      <c r="D580" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E580" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F580" t="n">
+        <v>1</v>
+      </c>
+      <c r="G580" t="n">
+        <v>2132</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="n">
+        <v>580</v>
+      </c>
+      <c r="B581" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>Nowe</t>
+        </is>
+      </c>
+      <c r="D581" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E581" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F581" t="n">
+        <v>3</v>
+      </c>
+      <c r="G581" t="n">
+        <v>2410</v>
       </c>
     </row>
   </sheetData>
@@ -18060,7 +18310,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3496"/>
+  <dimension ref="A1:E3552"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69200,6 +69450,958 @@
       </c>
       <c r="E3496" t="n">
         <v>570</v>
+      </c>
+    </row>
+    <row r="3497">
+      <c r="A3497" t="n">
+        <v>0</v>
+      </c>
+      <c r="B3497" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3497" t="n">
+        <v>100</v>
+      </c>
+      <c r="D3497" t="n">
+        <v>99</v>
+      </c>
+      <c r="E3497" t="n">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="3498">
+      <c r="A3498" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3498" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3498" t="n">
+        <v>40</v>
+      </c>
+      <c r="D3498" t="n">
+        <v>92</v>
+      </c>
+      <c r="E3498" t="n">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="3499">
+      <c r="A3499" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3499" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3499" t="n">
+        <v>72</v>
+      </c>
+      <c r="D3499" t="n">
+        <v>84</v>
+      </c>
+      <c r="E3499" t="n">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="3500">
+      <c r="A3500" t="n">
+        <v>3</v>
+      </c>
+      <c r="B3500" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3500" t="n">
+        <v>7</v>
+      </c>
+      <c r="D3500" t="n">
+        <v>13</v>
+      </c>
+      <c r="E3500" t="n">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="3501">
+      <c r="A3501" t="n">
+        <v>4</v>
+      </c>
+      <c r="B3501" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3501" t="n">
+        <v>28</v>
+      </c>
+      <c r="D3501" t="n">
+        <v>67</v>
+      </c>
+      <c r="E3501" t="n">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="3502">
+      <c r="A3502" t="n">
+        <v>5</v>
+      </c>
+      <c r="B3502" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3502" t="n">
+        <v>100</v>
+      </c>
+      <c r="D3502" t="n">
+        <v>95</v>
+      </c>
+      <c r="E3502" t="n">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="3503">
+      <c r="A3503" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3503" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3503" t="n">
+        <v>20</v>
+      </c>
+      <c r="D3503" t="n">
+        <v>39</v>
+      </c>
+      <c r="E3503" t="n">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="3504">
+      <c r="A3504" t="n">
+        <v>7</v>
+      </c>
+      <c r="B3504" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3504" t="n">
+        <v>81</v>
+      </c>
+      <c r="D3504" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3504" t="n">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="3505">
+      <c r="A3505" t="n">
+        <v>8</v>
+      </c>
+      <c r="B3505" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3505" t="n">
+        <v>87</v>
+      </c>
+      <c r="D3505" t="n">
+        <v>29</v>
+      </c>
+      <c r="E3505" t="n">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="3506">
+      <c r="A3506" t="n">
+        <v>9</v>
+      </c>
+      <c r="B3506" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3506" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3506" t="n">
+        <v>47</v>
+      </c>
+      <c r="E3506" t="n">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="3507">
+      <c r="A3507" t="n">
+        <v>10</v>
+      </c>
+      <c r="B3507" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3507" t="n">
+        <v>82</v>
+      </c>
+      <c r="D3507" t="n">
+        <v>61</v>
+      </c>
+      <c r="E3507" t="n">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="3508">
+      <c r="A3508" t="n">
+        <v>11</v>
+      </c>
+      <c r="B3508" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3508" t="n">
+        <v>70</v>
+      </c>
+      <c r="D3508" t="n">
+        <v>35</v>
+      </c>
+      <c r="E3508" t="n">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="3509">
+      <c r="A3509" t="n">
+        <v>12</v>
+      </c>
+      <c r="B3509" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3509" t="n">
+        <v>68</v>
+      </c>
+      <c r="D3509" t="n">
+        <v>30</v>
+      </c>
+      <c r="E3509" t="n">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="3510">
+      <c r="A3510" t="n">
+        <v>13</v>
+      </c>
+      <c r="B3510" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3510" t="n">
+        <v>47</v>
+      </c>
+      <c r="D3510" t="n">
+        <v>27</v>
+      </c>
+      <c r="E3510" t="n">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="3511">
+      <c r="A3511" t="n">
+        <v>14</v>
+      </c>
+      <c r="B3511" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3511" t="n">
+        <v>78</v>
+      </c>
+      <c r="D3511" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3511" t="n">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="3512">
+      <c r="A3512" t="n">
+        <v>15</v>
+      </c>
+      <c r="B3512" t="n">
+        <v>7</v>
+      </c>
+      <c r="C3512" t="n">
+        <v>55</v>
+      </c>
+      <c r="D3512" t="n">
+        <v>27</v>
+      </c>
+      <c r="E3512" t="n">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="3513">
+      <c r="A3513" t="n">
+        <v>16</v>
+      </c>
+      <c r="B3513" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3513" t="n">
+        <v>29</v>
+      </c>
+      <c r="D3513" t="n">
+        <v>56</v>
+      </c>
+      <c r="E3513" t="n">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="3514">
+      <c r="A3514" t="n">
+        <v>17</v>
+      </c>
+      <c r="B3514" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3514" t="n">
+        <v>38</v>
+      </c>
+      <c r="D3514" t="n">
+        <v>47</v>
+      </c>
+      <c r="E3514" t="n">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="3515">
+      <c r="A3515" t="n">
+        <v>18</v>
+      </c>
+      <c r="B3515" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3515" t="n">
+        <v>30</v>
+      </c>
+      <c r="D3515" t="n">
+        <v>64</v>
+      </c>
+      <c r="E3515" t="n">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="3516">
+      <c r="A3516" t="n">
+        <v>19</v>
+      </c>
+      <c r="B3516" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3516" t="n">
+        <v>90</v>
+      </c>
+      <c r="D3516" t="n">
+        <v>77</v>
+      </c>
+      <c r="E3516" t="n">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="3517">
+      <c r="A3517" t="n">
+        <v>20</v>
+      </c>
+      <c r="B3517" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3517" t="n">
+        <v>50</v>
+      </c>
+      <c r="D3517" t="n">
+        <v>30</v>
+      </c>
+      <c r="E3517" t="n">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="3518">
+      <c r="A3518" t="n">
+        <v>21</v>
+      </c>
+      <c r="B3518" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3518" t="n">
+        <v>85</v>
+      </c>
+      <c r="D3518" t="n">
+        <v>19</v>
+      </c>
+      <c r="E3518" t="n">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="3519">
+      <c r="A3519" t="n">
+        <v>22</v>
+      </c>
+      <c r="B3519" t="n">
+        <v>7</v>
+      </c>
+      <c r="C3519" t="n">
+        <v>88</v>
+      </c>
+      <c r="D3519" t="n">
+        <v>17</v>
+      </c>
+      <c r="E3519" t="n">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="3520">
+      <c r="A3520" t="n">
+        <v>23</v>
+      </c>
+      <c r="B3520" t="n">
+        <v>8</v>
+      </c>
+      <c r="C3520" t="n">
+        <v>93</v>
+      </c>
+      <c r="D3520" t="n">
+        <v>77</v>
+      </c>
+      <c r="E3520" t="n">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="3521">
+      <c r="A3521" t="n">
+        <v>24</v>
+      </c>
+      <c r="B3521" t="n">
+        <v>9</v>
+      </c>
+      <c r="C3521" t="n">
+        <v>28</v>
+      </c>
+      <c r="D3521" t="n">
+        <v>53</v>
+      </c>
+      <c r="E3521" t="n">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="3522">
+      <c r="A3522" t="n">
+        <v>25</v>
+      </c>
+      <c r="B3522" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3522" t="n">
+        <v>78</v>
+      </c>
+      <c r="D3522" t="n">
+        <v>57</v>
+      </c>
+      <c r="E3522" t="n">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="3523">
+      <c r="A3523" t="n">
+        <v>26</v>
+      </c>
+      <c r="B3523" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3523" t="n">
+        <v>91</v>
+      </c>
+      <c r="D3523" t="n">
+        <v>46</v>
+      </c>
+      <c r="E3523" t="n">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="3524">
+      <c r="A3524" t="n">
+        <v>27</v>
+      </c>
+      <c r="B3524" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3524" t="n">
+        <v>35</v>
+      </c>
+      <c r="D3524" t="n">
+        <v>54</v>
+      </c>
+      <c r="E3524" t="n">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="3525">
+      <c r="A3525" t="n">
+        <v>28</v>
+      </c>
+      <c r="B3525" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3525" t="n">
+        <v>99</v>
+      </c>
+      <c r="D3525" t="n">
+        <v>40</v>
+      </c>
+      <c r="E3525" t="n">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="3526">
+      <c r="A3526" t="n">
+        <v>29</v>
+      </c>
+      <c r="B3526" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3526" t="n">
+        <v>10</v>
+      </c>
+      <c r="D3526" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3526" t="n">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="3527">
+      <c r="A3527" t="n">
+        <v>30</v>
+      </c>
+      <c r="B3527" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3527" t="n">
+        <v>94</v>
+      </c>
+      <c r="D3527" t="n">
+        <v>83</v>
+      </c>
+      <c r="E3527" t="n">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="3528">
+      <c r="A3528" t="n">
+        <v>31</v>
+      </c>
+      <c r="B3528" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3528" t="n">
+        <v>73</v>
+      </c>
+      <c r="D3528" t="n">
+        <v>43</v>
+      </c>
+      <c r="E3528" t="n">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="3529">
+      <c r="A3529" t="n">
+        <v>32</v>
+      </c>
+      <c r="B3529" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3529" t="n">
+        <v>89</v>
+      </c>
+      <c r="D3529" t="n">
+        <v>10</v>
+      </c>
+      <c r="E3529" t="n">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="3530">
+      <c r="A3530" t="n">
+        <v>33</v>
+      </c>
+      <c r="B3530" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3530" t="n">
+        <v>69</v>
+      </c>
+      <c r="D3530" t="n">
+        <v>13</v>
+      </c>
+      <c r="E3530" t="n">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="3531">
+      <c r="A3531" t="n">
+        <v>34</v>
+      </c>
+      <c r="B3531" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3531" t="n">
+        <v>65</v>
+      </c>
+      <c r="D3531" t="n">
+        <v>42</v>
+      </c>
+      <c r="E3531" t="n">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="3532">
+      <c r="A3532" t="n">
+        <v>35</v>
+      </c>
+      <c r="B3532" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3532" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3532" t="n">
+        <v>80</v>
+      </c>
+      <c r="E3532" t="n">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="3533">
+      <c r="A3533" t="n">
+        <v>36</v>
+      </c>
+      <c r="B3533" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3533" t="n">
+        <v>65</v>
+      </c>
+      <c r="D3533" t="n">
+        <v>38</v>
+      </c>
+      <c r="E3533" t="n">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="3534">
+      <c r="A3534" t="n">
+        <v>37</v>
+      </c>
+      <c r="B3534" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3534" t="n">
+        <v>76</v>
+      </c>
+      <c r="D3534" t="n">
+        <v>38</v>
+      </c>
+      <c r="E3534" t="n">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="3535">
+      <c r="A3535" t="n">
+        <v>38</v>
+      </c>
+      <c r="B3535" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3535" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3535" t="n">
+        <v>100</v>
+      </c>
+      <c r="E3535" t="n">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="3536">
+      <c r="A3536" t="n">
+        <v>39</v>
+      </c>
+      <c r="B3536" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3536" t="n">
+        <v>54</v>
+      </c>
+      <c r="D3536" t="n">
+        <v>22</v>
+      </c>
+      <c r="E3536" t="n">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="3537">
+      <c r="A3537" t="n">
+        <v>40</v>
+      </c>
+      <c r="B3537" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3537" t="n">
+        <v>14</v>
+      </c>
+      <c r="D3537" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3537" t="n">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="3538">
+      <c r="A3538" t="n">
+        <v>41</v>
+      </c>
+      <c r="B3538" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3538" t="n">
+        <v>87</v>
+      </c>
+      <c r="D3538" t="n">
+        <v>57</v>
+      </c>
+      <c r="E3538" t="n">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="3539">
+      <c r="A3539" t="n">
+        <v>42</v>
+      </c>
+      <c r="B3539" t="n">
+        <v>7</v>
+      </c>
+      <c r="C3539" t="n">
+        <v>97</v>
+      </c>
+      <c r="D3539" t="n">
+        <v>33</v>
+      </c>
+      <c r="E3539" t="n">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="3540">
+      <c r="A3540" t="n">
+        <v>43</v>
+      </c>
+      <c r="B3540" t="n">
+        <v>8</v>
+      </c>
+      <c r="C3540" t="n">
+        <v>58</v>
+      </c>
+      <c r="D3540" t="n">
+        <v>25</v>
+      </c>
+      <c r="E3540" t="n">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="3541">
+      <c r="A3541" t="n">
+        <v>44</v>
+      </c>
+      <c r="B3541" t="n">
+        <v>9</v>
+      </c>
+      <c r="C3541" t="n">
+        <v>11</v>
+      </c>
+      <c r="D3541" t="n">
+        <v>53</v>
+      </c>
+      <c r="E3541" t="n">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="3542">
+      <c r="A3542" t="n">
+        <v>45</v>
+      </c>
+      <c r="B3542" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3542" t="n">
+        <v>87</v>
+      </c>
+      <c r="D3542" t="n">
+        <v>61</v>
+      </c>
+      <c r="E3542" t="n">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="3543">
+      <c r="A3543" t="n">
+        <v>46</v>
+      </c>
+      <c r="B3543" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3543" t="n">
+        <v>77</v>
+      </c>
+      <c r="D3543" t="n">
+        <v>91</v>
+      </c>
+      <c r="E3543" t="n">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="3544">
+      <c r="A3544" t="n">
+        <v>47</v>
+      </c>
+      <c r="B3544" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3544" t="n">
+        <v>83</v>
+      </c>
+      <c r="D3544" t="n">
+        <v>47</v>
+      </c>
+      <c r="E3544" t="n">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="3545">
+      <c r="A3545" t="n">
+        <v>48</v>
+      </c>
+      <c r="B3545" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3545" t="n">
+        <v>29</v>
+      </c>
+      <c r="D3545" t="n">
+        <v>47</v>
+      </c>
+      <c r="E3545" t="n">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="3546">
+      <c r="A3546" t="n">
+        <v>49</v>
+      </c>
+      <c r="B3546" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3546" t="n">
+        <v>93</v>
+      </c>
+      <c r="D3546" t="n">
+        <v>14</v>
+      </c>
+      <c r="E3546" t="n">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="3547">
+      <c r="A3547" t="n">
+        <v>50</v>
+      </c>
+      <c r="B3547" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3547" t="n">
+        <v>72</v>
+      </c>
+      <c r="D3547" t="n">
+        <v>48</v>
+      </c>
+      <c r="E3547" t="n">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="3548">
+      <c r="A3548" t="n">
+        <v>51</v>
+      </c>
+      <c r="B3548" t="n">
+        <v>7</v>
+      </c>
+      <c r="C3548" t="n">
+        <v>64</v>
+      </c>
+      <c r="D3548" t="n">
+        <v>90</v>
+      </c>
+      <c r="E3548" t="n">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="3549">
+      <c r="A3549" t="n">
+        <v>52</v>
+      </c>
+      <c r="B3549" t="n">
+        <v>8</v>
+      </c>
+      <c r="C3549" t="n">
+        <v>60</v>
+      </c>
+      <c r="D3549" t="n">
+        <v>4</v>
+      </c>
+      <c r="E3549" t="n">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="3550">
+      <c r="A3550" t="n">
+        <v>53</v>
+      </c>
+      <c r="B3550" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3550" t="n">
+        <v>81</v>
+      </c>
+      <c r="D3550" t="n">
+        <v>15</v>
+      </c>
+      <c r="E3550" t="n">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="3551">
+      <c r="A3551" t="n">
+        <v>54</v>
+      </c>
+      <c r="B3551" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3551" t="n">
+        <v>61</v>
+      </c>
+      <c r="D3551" t="n">
+        <v>81</v>
+      </c>
+      <c r="E3551" t="n">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="3552">
+      <c r="A3552" t="n">
+        <v>55</v>
+      </c>
+      <c r="B3552" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3552" t="n">
+        <v>86</v>
+      </c>
+      <c r="D3552" t="n">
+        <v>26</v>
+      </c>
+      <c r="E3552" t="n">
+        <v>580</v>
       </c>
     </row>
   </sheetData>
@@ -69213,7 +70415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F237"/>
+  <dimension ref="A1:F240"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75830,30 +77032,114 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Herbapol Eco</t>
+          <t>Power Eko Łódź</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>3917565267</t>
+          <t>6117049290</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>Katowice</t>
+          <t>Gorzów Wielkopolski</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Drogeria specjalistyczna</t>
+          <t>Gabinet dietetyczny</t>
         </is>
       </c>
       <c r="F237" t="n">
-        <v>25</v>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
+        <v>250</v>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Pro Shine</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>5954862883</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>Kołobrzeg</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>Supermarket / drogeria wielkopowierzchniowa</t>
+        </is>
+      </c>
+      <c r="F238" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="n">
+        <v>251</v>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Naturalna Natural</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>2767869066</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>Zawiercie</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>Medycyna estetyczna / klinika urody</t>
+        </is>
+      </c>
+      <c r="F239" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="n">
+        <v>252</v>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Muscle Gliwice</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>6474385948</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>Gdynia</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>Medycyna estetyczna / klinika urody</t>
+        </is>
+      </c>
+      <c r="F240" t="n">
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/dane.xlsx
+++ b/dane.xlsx
@@ -3759,7 +3759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G581"/>
+  <dimension ref="A1:G591"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18297,6 +18297,256 @@
       </c>
       <c r="G581" t="n">
         <v>2410</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="n">
+        <v>581</v>
+      </c>
+      <c r="B582" s="2" t="n">
+        <v>46064</v>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>Wysłane</t>
+        </is>
+      </c>
+      <c r="D582" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="E582" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F582" t="n">
+        <v>2</v>
+      </c>
+      <c r="G582" t="n">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="n">
+        <v>582</v>
+      </c>
+      <c r="B583" s="2" t="n">
+        <v>46089</v>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>Wysłane</t>
+        </is>
+      </c>
+      <c r="D583" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E583" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F583" t="n">
+        <v>1</v>
+      </c>
+      <c r="G583" t="n">
+        <v>1289</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="n">
+        <v>583</v>
+      </c>
+      <c r="B584" s="2" t="n">
+        <v>46064</v>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>Zwrot</t>
+        </is>
+      </c>
+      <c r="D584" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="E584" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F584" t="n">
+        <v>3</v>
+      </c>
+      <c r="G584" t="n">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="n">
+        <v>584</v>
+      </c>
+      <c r="B585" s="2" t="n">
+        <v>46063</v>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>Nowe</t>
+        </is>
+      </c>
+      <c r="D585" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="E585" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F585" t="n">
+        <v>3</v>
+      </c>
+      <c r="G585" t="n">
+        <v>2271</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="n">
+        <v>585</v>
+      </c>
+      <c r="B586" s="2" t="n">
+        <v>46080</v>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>Dostarczone</t>
+        </is>
+      </c>
+      <c r="D586" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="E586" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F586" t="n">
+        <v>4</v>
+      </c>
+      <c r="G586" t="n">
+        <v>2737</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="n">
+        <v>586</v>
+      </c>
+      <c r="B587" s="2" t="n">
+        <v>46067</v>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>Wysłane</t>
+        </is>
+      </c>
+      <c r="D587" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="E587" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F587" t="n">
+        <v>1</v>
+      </c>
+      <c r="G587" t="n">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="n">
+        <v>587</v>
+      </c>
+      <c r="B588" s="2" t="n">
+        <v>46065</v>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>Zwrot</t>
+        </is>
+      </c>
+      <c r="D588" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E588" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F588" t="n">
+        <v>1</v>
+      </c>
+      <c r="G588" t="n">
+        <v>1350</v>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="n">
+        <v>588</v>
+      </c>
+      <c r="B589" s="2" t="n">
+        <v>46078</v>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>Nowe</t>
+        </is>
+      </c>
+      <c r="D589" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E589" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F589" t="n">
+        <v>4</v>
+      </c>
+      <c r="G589" t="n">
+        <v>1968</v>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="n">
+        <v>589</v>
+      </c>
+      <c r="B590" s="2" t="n">
+        <v>46071</v>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>Wysłane</t>
+        </is>
+      </c>
+      <c r="D590" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="E590" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F590" t="n">
+        <v>1</v>
+      </c>
+      <c r="G590" t="n">
+        <v>2184</v>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="n">
+        <v>590</v>
+      </c>
+      <c r="B591" s="2" t="n">
+        <v>46070</v>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>Wysłane</t>
+        </is>
+      </c>
+      <c r="D591" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="E591" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F591" t="n">
+        <v>1</v>
+      </c>
+      <c r="G591" t="n">
+        <v>433</v>
       </c>
     </row>
   </sheetData>
@@ -18310,7 +18560,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3552"/>
+  <dimension ref="A1:E3623"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70402,6 +70652,1213 @@
       </c>
       <c r="E3552" t="n">
         <v>580</v>
+      </c>
+    </row>
+    <row r="3553">
+      <c r="A3553" t="n">
+        <v>0</v>
+      </c>
+      <c r="B3553" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3553" t="n">
+        <v>60</v>
+      </c>
+      <c r="D3553" t="n">
+        <v>6</v>
+      </c>
+      <c r="E3553" t="n">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="3554">
+      <c r="A3554" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3554" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3554" t="n">
+        <v>58</v>
+      </c>
+      <c r="D3554" t="n">
+        <v>54</v>
+      </c>
+      <c r="E3554" t="n">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="3555">
+      <c r="A3555" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3555" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3555" t="n">
+        <v>11</v>
+      </c>
+      <c r="D3555" t="n">
+        <v>22</v>
+      </c>
+      <c r="E3555" t="n">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="3556">
+      <c r="A3556" t="n">
+        <v>3</v>
+      </c>
+      <c r="B3556" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3556" t="n">
+        <v>25</v>
+      </c>
+      <c r="D3556" t="n">
+        <v>99</v>
+      </c>
+      <c r="E3556" t="n">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="3557">
+      <c r="A3557" t="n">
+        <v>4</v>
+      </c>
+      <c r="B3557" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3557" t="n">
+        <v>67</v>
+      </c>
+      <c r="D3557" t="n">
+        <v>56</v>
+      </c>
+      <c r="E3557" t="n">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="3558">
+      <c r="A3558" t="n">
+        <v>5</v>
+      </c>
+      <c r="B3558" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3558" t="n">
+        <v>66</v>
+      </c>
+      <c r="D3558" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3558" t="n">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="3559">
+      <c r="A3559" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3559" t="n">
+        <v>7</v>
+      </c>
+      <c r="C3559" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3559" t="n">
+        <v>37</v>
+      </c>
+      <c r="E3559" t="n">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="3560">
+      <c r="A3560" t="n">
+        <v>7</v>
+      </c>
+      <c r="B3560" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3560" t="n">
+        <v>53</v>
+      </c>
+      <c r="D3560" t="n">
+        <v>90</v>
+      </c>
+      <c r="E3560" t="n">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="3561">
+      <c r="A3561" t="n">
+        <v>8</v>
+      </c>
+      <c r="B3561" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3561" t="n">
+        <v>37</v>
+      </c>
+      <c r="D3561" t="n">
+        <v>50</v>
+      </c>
+      <c r="E3561" t="n">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="3562">
+      <c r="A3562" t="n">
+        <v>9</v>
+      </c>
+      <c r="B3562" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3562" t="n">
+        <v>92</v>
+      </c>
+      <c r="D3562" t="n">
+        <v>13</v>
+      </c>
+      <c r="E3562" t="n">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="3563">
+      <c r="A3563" t="n">
+        <v>10</v>
+      </c>
+      <c r="B3563" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3563" t="n">
+        <v>37</v>
+      </c>
+      <c r="D3563" t="n">
+        <v>16</v>
+      </c>
+      <c r="E3563" t="n">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="3564">
+      <c r="A3564" t="n">
+        <v>11</v>
+      </c>
+      <c r="B3564" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3564" t="n">
+        <v>28</v>
+      </c>
+      <c r="D3564" t="n">
+        <v>58</v>
+      </c>
+      <c r="E3564" t="n">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="3565">
+      <c r="A3565" t="n">
+        <v>12</v>
+      </c>
+      <c r="B3565" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3565" t="n">
+        <v>27</v>
+      </c>
+      <c r="D3565" t="n">
+        <v>72</v>
+      </c>
+      <c r="E3565" t="n">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="3566">
+      <c r="A3566" t="n">
+        <v>13</v>
+      </c>
+      <c r="B3566" t="n">
+        <v>7</v>
+      </c>
+      <c r="C3566" t="n">
+        <v>17</v>
+      </c>
+      <c r="D3566" t="n">
+        <v>80</v>
+      </c>
+      <c r="E3566" t="n">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="3567">
+      <c r="A3567" t="n">
+        <v>14</v>
+      </c>
+      <c r="B3567" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3567" t="n">
+        <v>98</v>
+      </c>
+      <c r="D3567" t="n">
+        <v>24</v>
+      </c>
+      <c r="E3567" t="n">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="3568">
+      <c r="A3568" t="n">
+        <v>15</v>
+      </c>
+      <c r="B3568" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3568" t="n">
+        <v>68</v>
+      </c>
+      <c r="D3568" t="n">
+        <v>25</v>
+      </c>
+      <c r="E3568" t="n">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="3569">
+      <c r="A3569" t="n">
+        <v>16</v>
+      </c>
+      <c r="B3569" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3569" t="n">
+        <v>60</v>
+      </c>
+      <c r="D3569" t="n">
+        <v>46</v>
+      </c>
+      <c r="E3569" t="n">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="3570">
+      <c r="A3570" t="n">
+        <v>17</v>
+      </c>
+      <c r="B3570" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3570" t="n">
+        <v>84</v>
+      </c>
+      <c r="D3570" t="n">
+        <v>31</v>
+      </c>
+      <c r="E3570" t="n">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="3571">
+      <c r="A3571" t="n">
+        <v>18</v>
+      </c>
+      <c r="B3571" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3571" t="n">
+        <v>98</v>
+      </c>
+      <c r="D3571" t="n">
+        <v>45</v>
+      </c>
+      <c r="E3571" t="n">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="3572">
+      <c r="A3572" t="n">
+        <v>19</v>
+      </c>
+      <c r="B3572" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3572" t="n">
+        <v>73</v>
+      </c>
+      <c r="D3572" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3572" t="n">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="3573">
+      <c r="A3573" t="n">
+        <v>20</v>
+      </c>
+      <c r="B3573" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3573" t="n">
+        <v>21</v>
+      </c>
+      <c r="D3573" t="n">
+        <v>92</v>
+      </c>
+      <c r="E3573" t="n">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="3574">
+      <c r="A3574" t="n">
+        <v>21</v>
+      </c>
+      <c r="B3574" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3574" t="n">
+        <v>37</v>
+      </c>
+      <c r="D3574" t="n">
+        <v>71</v>
+      </c>
+      <c r="E3574" t="n">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="3575">
+      <c r="A3575" t="n">
+        <v>22</v>
+      </c>
+      <c r="B3575" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3575" t="n">
+        <v>68</v>
+      </c>
+      <c r="D3575" t="n">
+        <v>65</v>
+      </c>
+      <c r="E3575" t="n">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="3576">
+      <c r="A3576" t="n">
+        <v>23</v>
+      </c>
+      <c r="B3576" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3576" t="n">
+        <v>93</v>
+      </c>
+      <c r="D3576" t="n">
+        <v>86</v>
+      </c>
+      <c r="E3576" t="n">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="3577">
+      <c r="A3577" t="n">
+        <v>24</v>
+      </c>
+      <c r="B3577" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3577" t="n">
+        <v>68</v>
+      </c>
+      <c r="D3577" t="n">
+        <v>63</v>
+      </c>
+      <c r="E3577" t="n">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="3578">
+      <c r="A3578" t="n">
+        <v>25</v>
+      </c>
+      <c r="B3578" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3578" t="n">
+        <v>65</v>
+      </c>
+      <c r="D3578" t="n">
+        <v>78</v>
+      </c>
+      <c r="E3578" t="n">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="3579">
+      <c r="A3579" t="n">
+        <v>26</v>
+      </c>
+      <c r="B3579" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3579" t="n">
+        <v>75</v>
+      </c>
+      <c r="D3579" t="n">
+        <v>78</v>
+      </c>
+      <c r="E3579" t="n">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="3580">
+      <c r="A3580" t="n">
+        <v>27</v>
+      </c>
+      <c r="B3580" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3580" t="n">
+        <v>57</v>
+      </c>
+      <c r="D3580" t="n">
+        <v>37</v>
+      </c>
+      <c r="E3580" t="n">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="3581">
+      <c r="A3581" t="n">
+        <v>28</v>
+      </c>
+      <c r="B3581" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3581" t="n">
+        <v>11</v>
+      </c>
+      <c r="D3581" t="n">
+        <v>7</v>
+      </c>
+      <c r="E3581" t="n">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="3582">
+      <c r="A3582" t="n">
+        <v>29</v>
+      </c>
+      <c r="B3582" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3582" t="n">
+        <v>27</v>
+      </c>
+      <c r="D3582" t="n">
+        <v>62</v>
+      </c>
+      <c r="E3582" t="n">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="3583">
+      <c r="A3583" t="n">
+        <v>30</v>
+      </c>
+      <c r="B3583" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3583" t="n">
+        <v>13</v>
+      </c>
+      <c r="D3583" t="n">
+        <v>4</v>
+      </c>
+      <c r="E3583" t="n">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="3584">
+      <c r="A3584" t="n">
+        <v>31</v>
+      </c>
+      <c r="B3584" t="n">
+        <v>7</v>
+      </c>
+      <c r="C3584" t="n">
+        <v>18</v>
+      </c>
+      <c r="D3584" t="n">
+        <v>65</v>
+      </c>
+      <c r="E3584" t="n">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="3585">
+      <c r="A3585" t="n">
+        <v>32</v>
+      </c>
+      <c r="B3585" t="n">
+        <v>8</v>
+      </c>
+      <c r="C3585" t="n">
+        <v>17</v>
+      </c>
+      <c r="D3585" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3585" t="n">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="3586">
+      <c r="A3586" t="n">
+        <v>33</v>
+      </c>
+      <c r="B3586" t="n">
+        <v>9</v>
+      </c>
+      <c r="C3586" t="n">
+        <v>7</v>
+      </c>
+      <c r="D3586" t="n">
+        <v>54</v>
+      </c>
+      <c r="E3586" t="n">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="3587">
+      <c r="A3587" t="n">
+        <v>34</v>
+      </c>
+      <c r="B3587" t="n">
+        <v>10</v>
+      </c>
+      <c r="C3587" t="n">
+        <v>12</v>
+      </c>
+      <c r="D3587" t="n">
+        <v>84</v>
+      </c>
+      <c r="E3587" t="n">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="3588">
+      <c r="A3588" t="n">
+        <v>35</v>
+      </c>
+      <c r="B3588" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3588" t="n">
+        <v>75</v>
+      </c>
+      <c r="D3588" t="n">
+        <v>26</v>
+      </c>
+      <c r="E3588" t="n">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="3589">
+      <c r="A3589" t="n">
+        <v>36</v>
+      </c>
+      <c r="B3589" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3589" t="n">
+        <v>86</v>
+      </c>
+      <c r="D3589" t="n">
+        <v>88</v>
+      </c>
+      <c r="E3589" t="n">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="3590">
+      <c r="A3590" t="n">
+        <v>37</v>
+      </c>
+      <c r="B3590" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3590" t="n">
+        <v>43</v>
+      </c>
+      <c r="D3590" t="n">
+        <v>30</v>
+      </c>
+      <c r="E3590" t="n">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="3591">
+      <c r="A3591" t="n">
+        <v>38</v>
+      </c>
+      <c r="B3591" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3591" t="n">
+        <v>18</v>
+      </c>
+      <c r="D3591" t="n">
+        <v>83</v>
+      </c>
+      <c r="E3591" t="n">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="3592">
+      <c r="A3592" t="n">
+        <v>39</v>
+      </c>
+      <c r="B3592" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3592" t="n">
+        <v>72</v>
+      </c>
+      <c r="D3592" t="n">
+        <v>49</v>
+      </c>
+      <c r="E3592" t="n">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="3593">
+      <c r="A3593" t="n">
+        <v>40</v>
+      </c>
+      <c r="B3593" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3593" t="n">
+        <v>34</v>
+      </c>
+      <c r="D3593" t="n">
+        <v>87</v>
+      </c>
+      <c r="E3593" t="n">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="3594">
+      <c r="A3594" t="n">
+        <v>41</v>
+      </c>
+      <c r="B3594" t="n">
+        <v>7</v>
+      </c>
+      <c r="C3594" t="n">
+        <v>16</v>
+      </c>
+      <c r="D3594" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3594" t="n">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="3595">
+      <c r="A3595" t="n">
+        <v>42</v>
+      </c>
+      <c r="B3595" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3595" t="n">
+        <v>73</v>
+      </c>
+      <c r="D3595" t="n">
+        <v>86</v>
+      </c>
+      <c r="E3595" t="n">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="3596">
+      <c r="A3596" t="n">
+        <v>43</v>
+      </c>
+      <c r="B3596" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3596" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3596" t="n">
+        <v>85</v>
+      </c>
+      <c r="E3596" t="n">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="3597">
+      <c r="A3597" t="n">
+        <v>44</v>
+      </c>
+      <c r="B3597" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3597" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3597" t="n">
+        <v>95</v>
+      </c>
+      <c r="E3597" t="n">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="3598">
+      <c r="A3598" t="n">
+        <v>45</v>
+      </c>
+      <c r="B3598" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3598" t="n">
+        <v>99</v>
+      </c>
+      <c r="D3598" t="n">
+        <v>32</v>
+      </c>
+      <c r="E3598" t="n">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="3599">
+      <c r="A3599" t="n">
+        <v>46</v>
+      </c>
+      <c r="B3599" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3599" t="n">
+        <v>60</v>
+      </c>
+      <c r="D3599" t="n">
+        <v>71</v>
+      </c>
+      <c r="E3599" t="n">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="3600">
+      <c r="A3600" t="n">
+        <v>47</v>
+      </c>
+      <c r="B3600" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3600" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3600" t="n">
+        <v>70</v>
+      </c>
+      <c r="E3600" t="n">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="3601">
+      <c r="A3601" t="n">
+        <v>48</v>
+      </c>
+      <c r="B3601" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3601" t="n">
+        <v>76</v>
+      </c>
+      <c r="D3601" t="n">
+        <v>86</v>
+      </c>
+      <c r="E3601" t="n">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="3602">
+      <c r="A3602" t="n">
+        <v>49</v>
+      </c>
+      <c r="B3602" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3602" t="n">
+        <v>26</v>
+      </c>
+      <c r="D3602" t="n">
+        <v>18</v>
+      </c>
+      <c r="E3602" t="n">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="3603">
+      <c r="A3603" t="n">
+        <v>50</v>
+      </c>
+      <c r="B3603" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3603" t="n">
+        <v>53</v>
+      </c>
+      <c r="D3603" t="n">
+        <v>67</v>
+      </c>
+      <c r="E3603" t="n">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="3604">
+      <c r="A3604" t="n">
+        <v>51</v>
+      </c>
+      <c r="B3604" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3604" t="n">
+        <v>27</v>
+      </c>
+      <c r="D3604" t="n">
+        <v>90</v>
+      </c>
+      <c r="E3604" t="n">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="3605">
+      <c r="A3605" t="n">
+        <v>52</v>
+      </c>
+      <c r="B3605" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3605" t="n">
+        <v>80</v>
+      </c>
+      <c r="D3605" t="n">
+        <v>33</v>
+      </c>
+      <c r="E3605" t="n">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="3606">
+      <c r="A3606" t="n">
+        <v>53</v>
+      </c>
+      <c r="B3606" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3606" t="n">
+        <v>63</v>
+      </c>
+      <c r="D3606" t="n">
+        <v>28</v>
+      </c>
+      <c r="E3606" t="n">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="3607">
+      <c r="A3607" t="n">
+        <v>54</v>
+      </c>
+      <c r="B3607" t="n">
+        <v>7</v>
+      </c>
+      <c r="C3607" t="n">
+        <v>18</v>
+      </c>
+      <c r="D3607" t="n">
+        <v>62</v>
+      </c>
+      <c r="E3607" t="n">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="3608">
+      <c r="A3608" t="n">
+        <v>55</v>
+      </c>
+      <c r="B3608" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3608" t="n">
+        <v>82</v>
+      </c>
+      <c r="D3608" t="n">
+        <v>25</v>
+      </c>
+      <c r="E3608" t="n">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="3609">
+      <c r="A3609" t="n">
+        <v>56</v>
+      </c>
+      <c r="B3609" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3609" t="n">
+        <v>100</v>
+      </c>
+      <c r="D3609" t="n">
+        <v>45</v>
+      </c>
+      <c r="E3609" t="n">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="3610">
+      <c r="A3610" t="n">
+        <v>57</v>
+      </c>
+      <c r="B3610" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3610" t="n">
+        <v>53</v>
+      </c>
+      <c r="D3610" t="n">
+        <v>8</v>
+      </c>
+      <c r="E3610" t="n">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="3611">
+      <c r="A3611" t="n">
+        <v>58</v>
+      </c>
+      <c r="B3611" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3611" t="n">
+        <v>78</v>
+      </c>
+      <c r="D3611" t="n">
+        <v>59</v>
+      </c>
+      <c r="E3611" t="n">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="3612">
+      <c r="A3612" t="n">
+        <v>59</v>
+      </c>
+      <c r="B3612" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3612" t="n">
+        <v>61</v>
+      </c>
+      <c r="D3612" t="n">
+        <v>71</v>
+      </c>
+      <c r="E3612" t="n">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="3613">
+      <c r="A3613" t="n">
+        <v>60</v>
+      </c>
+      <c r="B3613" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3613" t="n">
+        <v>53</v>
+      </c>
+      <c r="D3613" t="n">
+        <v>52</v>
+      </c>
+      <c r="E3613" t="n">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="3614">
+      <c r="A3614" t="n">
+        <v>61</v>
+      </c>
+      <c r="B3614" t="n">
+        <v>7</v>
+      </c>
+      <c r="C3614" t="n">
+        <v>73</v>
+      </c>
+      <c r="D3614" t="n">
+        <v>12</v>
+      </c>
+      <c r="E3614" t="n">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="3615">
+      <c r="A3615" t="n">
+        <v>62</v>
+      </c>
+      <c r="B3615" t="n">
+        <v>8</v>
+      </c>
+      <c r="C3615" t="n">
+        <v>77</v>
+      </c>
+      <c r="D3615" t="n">
+        <v>91</v>
+      </c>
+      <c r="E3615" t="n">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="3616">
+      <c r="A3616" t="n">
+        <v>63</v>
+      </c>
+      <c r="B3616" t="n">
+        <v>9</v>
+      </c>
+      <c r="C3616" t="n">
+        <v>93</v>
+      </c>
+      <c r="D3616" t="n">
+        <v>46</v>
+      </c>
+      <c r="E3616" t="n">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="3617">
+      <c r="A3617" t="n">
+        <v>64</v>
+      </c>
+      <c r="B3617" t="n">
+        <v>10</v>
+      </c>
+      <c r="C3617" t="n">
+        <v>33</v>
+      </c>
+      <c r="D3617" t="n">
+        <v>67</v>
+      </c>
+      <c r="E3617" t="n">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="3618">
+      <c r="A3618" t="n">
+        <v>65</v>
+      </c>
+      <c r="B3618" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3618" t="n">
+        <v>91</v>
+      </c>
+      <c r="D3618" t="n">
+        <v>30</v>
+      </c>
+      <c r="E3618" t="n">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="3619">
+      <c r="A3619" t="n">
+        <v>66</v>
+      </c>
+      <c r="B3619" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3619" t="n">
+        <v>39</v>
+      </c>
+      <c r="D3619" t="n">
+        <v>20</v>
+      </c>
+      <c r="E3619" t="n">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="3620">
+      <c r="A3620" t="n">
+        <v>67</v>
+      </c>
+      <c r="B3620" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3620" t="n">
+        <v>44</v>
+      </c>
+      <c r="D3620" t="n">
+        <v>67</v>
+      </c>
+      <c r="E3620" t="n">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="3621">
+      <c r="A3621" t="n">
+        <v>68</v>
+      </c>
+      <c r="B3621" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3621" t="n">
+        <v>55</v>
+      </c>
+      <c r="D3621" t="n">
+        <v>36</v>
+      </c>
+      <c r="E3621" t="n">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="3622">
+      <c r="A3622" t="n">
+        <v>69</v>
+      </c>
+      <c r="B3622" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3622" t="n">
+        <v>94</v>
+      </c>
+      <c r="D3622" t="n">
+        <v>83</v>
+      </c>
+      <c r="E3622" t="n">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="3623">
+      <c r="A3623" t="n">
+        <v>70</v>
+      </c>
+      <c r="B3623" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3623" t="n">
+        <v>51</v>
+      </c>
+      <c r="D3623" t="n">
+        <v>26</v>
+      </c>
+      <c r="E3623" t="n">
+        <v>590</v>
       </c>
     </row>
   </sheetData>
@@ -70415,7 +71872,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F240"/>
+  <dimension ref="A1:F243"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -77116,30 +78573,114 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Muscle Gliwice</t>
+          <t>Apteka Chorzów</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>6474385948</t>
+          <t>5165257821</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>Gdynia</t>
+          <t>Zambrów</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Medycyna estetyczna / klinika urody</t>
+          <t>Zielarnia</t>
         </is>
       </c>
       <c r="F240" t="n">
-        <v>22</v>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="n">
+        <v>254</v>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Care Active</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>5880356590</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>Zawiercie</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>Apteka</t>
+        </is>
+      </c>
+      <c r="F241" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="n">
+        <v>255</v>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Health Natura Wrocław</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>8820039406</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>Rumia</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>Apteka</t>
+        </is>
+      </c>
+      <c r="F242" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
+        <v>256</v>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Pro Active s.c</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>3279301836</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>Toruń</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>Sklep internetowy z suplementami</t>
+        </is>
+      </c>
+      <c r="F243" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/dane.xlsx
+++ b/dane.xlsx
@@ -3759,7 +3759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G591"/>
+  <dimension ref="A1:G601"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18547,6 +18547,256 @@
       </c>
       <c r="G591" t="n">
         <v>433</v>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="n">
+        <v>591</v>
+      </c>
+      <c r="B592" s="2" t="n">
+        <v>46064</v>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>Dostarczone</t>
+        </is>
+      </c>
+      <c r="D592" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="E592" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F592" t="n">
+        <v>3</v>
+      </c>
+      <c r="G592" t="n">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="n">
+        <v>592</v>
+      </c>
+      <c r="B593" s="2" t="n">
+        <v>46081</v>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>Dostarczone</t>
+        </is>
+      </c>
+      <c r="D593" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="E593" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F593" t="n">
+        <v>2</v>
+      </c>
+      <c r="G593" t="n">
+        <v>1973</v>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="n">
+        <v>593</v>
+      </c>
+      <c r="B594" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>Dostarczone</t>
+        </is>
+      </c>
+      <c r="D594" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="E594" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F594" t="n">
+        <v>2</v>
+      </c>
+      <c r="G594" t="n">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="n">
+        <v>594</v>
+      </c>
+      <c r="B595" s="2" t="n">
+        <v>46074</v>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>Dostarczone</t>
+        </is>
+      </c>
+      <c r="D595" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="E595" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F595" t="n">
+        <v>1</v>
+      </c>
+      <c r="G595" t="n">
+        <v>1781</v>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="n">
+        <v>595</v>
+      </c>
+      <c r="B596" s="2" t="n">
+        <v>46081</v>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>Zwrot</t>
+        </is>
+      </c>
+      <c r="D596" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E596" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F596" t="n">
+        <v>2</v>
+      </c>
+      <c r="G596" t="n">
+        <v>1929</v>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="n">
+        <v>596</v>
+      </c>
+      <c r="B597" s="2" t="n">
+        <v>46076</v>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>Zwrot</t>
+        </is>
+      </c>
+      <c r="D597" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E597" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F597" t="n">
+        <v>3</v>
+      </c>
+      <c r="G597" t="n">
+        <v>2187</v>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="n">
+        <v>597</v>
+      </c>
+      <c r="B598" s="2" t="n">
+        <v>46088</v>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>Wysłane</t>
+        </is>
+      </c>
+      <c r="D598" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E598" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F598" t="n">
+        <v>4</v>
+      </c>
+      <c r="G598" t="n">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="n">
+        <v>598</v>
+      </c>
+      <c r="B599" s="2" t="n">
+        <v>46068</v>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>Zwrot</t>
+        </is>
+      </c>
+      <c r="D599" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="E599" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F599" t="n">
+        <v>2</v>
+      </c>
+      <c r="G599" t="n">
+        <v>2807</v>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="n">
+        <v>599</v>
+      </c>
+      <c r="B600" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>Wysłane</t>
+        </is>
+      </c>
+      <c r="D600" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="E600" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F600" t="n">
+        <v>3</v>
+      </c>
+      <c r="G600" t="n">
+        <v>2151</v>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="n">
+        <v>600</v>
+      </c>
+      <c r="B601" s="2" t="n">
+        <v>46070</v>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>Wysłane</t>
+        </is>
+      </c>
+      <c r="D601" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="E601" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F601" t="n">
+        <v>1</v>
+      </c>
+      <c r="G601" t="n">
+        <v>724</v>
       </c>
     </row>
   </sheetData>
@@ -18560,7 +18810,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3623"/>
+  <dimension ref="A1:E3675"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -71859,6 +72109,890 @@
       </c>
       <c r="E3623" t="n">
         <v>590</v>
+      </c>
+    </row>
+    <row r="3624">
+      <c r="A3624" t="n">
+        <v>0</v>
+      </c>
+      <c r="B3624" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3624" t="n">
+        <v>14</v>
+      </c>
+      <c r="D3624" t="n">
+        <v>100</v>
+      </c>
+      <c r="E3624" t="n">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="3625">
+      <c r="A3625" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3625" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3625" t="n">
+        <v>59</v>
+      </c>
+      <c r="D3625" t="n">
+        <v>57</v>
+      </c>
+      <c r="E3625" t="n">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="3626">
+      <c r="A3626" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3626" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3626" t="n">
+        <v>69</v>
+      </c>
+      <c r="D3626" t="n">
+        <v>34</v>
+      </c>
+      <c r="E3626" t="n">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="3627">
+      <c r="A3627" t="n">
+        <v>3</v>
+      </c>
+      <c r="B3627" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3627" t="n">
+        <v>19</v>
+      </c>
+      <c r="D3627" t="n">
+        <v>39</v>
+      </c>
+      <c r="E3627" t="n">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="3628">
+      <c r="A3628" t="n">
+        <v>4</v>
+      </c>
+      <c r="B3628" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3628" t="n">
+        <v>86</v>
+      </c>
+      <c r="D3628" t="n">
+        <v>27</v>
+      </c>
+      <c r="E3628" t="n">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="3629">
+      <c r="A3629" t="n">
+        <v>5</v>
+      </c>
+      <c r="B3629" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3629" t="n">
+        <v>69</v>
+      </c>
+      <c r="D3629" t="n">
+        <v>43</v>
+      </c>
+      <c r="E3629" t="n">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="3630">
+      <c r="A3630" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3630" t="n">
+        <v>7</v>
+      </c>
+      <c r="C3630" t="n">
+        <v>88</v>
+      </c>
+      <c r="D3630" t="n">
+        <v>13</v>
+      </c>
+      <c r="E3630" t="n">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="3631">
+      <c r="A3631" t="n">
+        <v>7</v>
+      </c>
+      <c r="B3631" t="n">
+        <v>8</v>
+      </c>
+      <c r="C3631" t="n">
+        <v>14</v>
+      </c>
+      <c r="D3631" t="n">
+        <v>16</v>
+      </c>
+      <c r="E3631" t="n">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="3632">
+      <c r="A3632" t="n">
+        <v>8</v>
+      </c>
+      <c r="B3632" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3632" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3632" t="n">
+        <v>32</v>
+      </c>
+      <c r="E3632" t="n">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="3633">
+      <c r="A3633" t="n">
+        <v>9</v>
+      </c>
+      <c r="B3633" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3633" t="n">
+        <v>40</v>
+      </c>
+      <c r="D3633" t="n">
+        <v>30</v>
+      </c>
+      <c r="E3633" t="n">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="3634">
+      <c r="A3634" t="n">
+        <v>10</v>
+      </c>
+      <c r="B3634" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3634" t="n">
+        <v>63</v>
+      </c>
+      <c r="D3634" t="n">
+        <v>82</v>
+      </c>
+      <c r="E3634" t="n">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="3635">
+      <c r="A3635" t="n">
+        <v>11</v>
+      </c>
+      <c r="B3635" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3635" t="n">
+        <v>42</v>
+      </c>
+      <c r="D3635" t="n">
+        <v>35</v>
+      </c>
+      <c r="E3635" t="n">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="3636">
+      <c r="A3636" t="n">
+        <v>12</v>
+      </c>
+      <c r="B3636" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3636" t="n">
+        <v>5</v>
+      </c>
+      <c r="D3636" t="n">
+        <v>11</v>
+      </c>
+      <c r="E3636" t="n">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="3637">
+      <c r="A3637" t="n">
+        <v>13</v>
+      </c>
+      <c r="B3637" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3637" t="n">
+        <v>90</v>
+      </c>
+      <c r="D3637" t="n">
+        <v>90</v>
+      </c>
+      <c r="E3637" t="n">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="3638">
+      <c r="A3638" t="n">
+        <v>14</v>
+      </c>
+      <c r="B3638" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3638" t="n">
+        <v>97</v>
+      </c>
+      <c r="D3638" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3638" t="n">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="3639">
+      <c r="A3639" t="n">
+        <v>15</v>
+      </c>
+      <c r="B3639" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3639" t="n">
+        <v>11</v>
+      </c>
+      <c r="D3639" t="n">
+        <v>67</v>
+      </c>
+      <c r="E3639" t="n">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="3640">
+      <c r="A3640" t="n">
+        <v>16</v>
+      </c>
+      <c r="B3640" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3640" t="n">
+        <v>73</v>
+      </c>
+      <c r="D3640" t="n">
+        <v>81</v>
+      </c>
+      <c r="E3640" t="n">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="3641">
+      <c r="A3641" t="n">
+        <v>17</v>
+      </c>
+      <c r="B3641" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3641" t="n">
+        <v>56</v>
+      </c>
+      <c r="D3641" t="n">
+        <v>92</v>
+      </c>
+      <c r="E3641" t="n">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="3642">
+      <c r="A3642" t="n">
+        <v>18</v>
+      </c>
+      <c r="B3642" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3642" t="n">
+        <v>26</v>
+      </c>
+      <c r="D3642" t="n">
+        <v>63</v>
+      </c>
+      <c r="E3642" t="n">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="3643">
+      <c r="A3643" t="n">
+        <v>19</v>
+      </c>
+      <c r="B3643" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3643" t="n">
+        <v>25</v>
+      </c>
+      <c r="D3643" t="n">
+        <v>59</v>
+      </c>
+      <c r="E3643" t="n">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="3644">
+      <c r="A3644" t="n">
+        <v>20</v>
+      </c>
+      <c r="B3644" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3644" t="n">
+        <v>44</v>
+      </c>
+      <c r="D3644" t="n">
+        <v>76</v>
+      </c>
+      <c r="E3644" t="n">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="3645">
+      <c r="A3645" t="n">
+        <v>21</v>
+      </c>
+      <c r="B3645" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3645" t="n">
+        <v>65</v>
+      </c>
+      <c r="D3645" t="n">
+        <v>52</v>
+      </c>
+      <c r="E3645" t="n">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="3646">
+      <c r="A3646" t="n">
+        <v>22</v>
+      </c>
+      <c r="B3646" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3646" t="n">
+        <v>59</v>
+      </c>
+      <c r="D3646" t="n">
+        <v>30</v>
+      </c>
+      <c r="E3646" t="n">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="3647">
+      <c r="A3647" t="n">
+        <v>23</v>
+      </c>
+      <c r="B3647" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3647" t="n">
+        <v>56</v>
+      </c>
+      <c r="D3647" t="n">
+        <v>96</v>
+      </c>
+      <c r="E3647" t="n">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="3648">
+      <c r="A3648" t="n">
+        <v>24</v>
+      </c>
+      <c r="B3648" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3648" t="n">
+        <v>19</v>
+      </c>
+      <c r="D3648" t="n">
+        <v>58</v>
+      </c>
+      <c r="E3648" t="n">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="3649">
+      <c r="A3649" t="n">
+        <v>25</v>
+      </c>
+      <c r="B3649" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3649" t="n">
+        <v>43</v>
+      </c>
+      <c r="D3649" t="n">
+        <v>64</v>
+      </c>
+      <c r="E3649" t="n">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="3650">
+      <c r="A3650" t="n">
+        <v>26</v>
+      </c>
+      <c r="B3650" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3650" t="n">
+        <v>35</v>
+      </c>
+      <c r="D3650" t="n">
+        <v>26</v>
+      </c>
+      <c r="E3650" t="n">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="3651">
+      <c r="A3651" t="n">
+        <v>27</v>
+      </c>
+      <c r="B3651" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3651" t="n">
+        <v>86</v>
+      </c>
+      <c r="D3651" t="n">
+        <v>7</v>
+      </c>
+      <c r="E3651" t="n">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="3652">
+      <c r="A3652" t="n">
+        <v>28</v>
+      </c>
+      <c r="B3652" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3652" t="n">
+        <v>78</v>
+      </c>
+      <c r="D3652" t="n">
+        <v>63</v>
+      </c>
+      <c r="E3652" t="n">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="3653">
+      <c r="A3653" t="n">
+        <v>29</v>
+      </c>
+      <c r="B3653" t="n">
+        <v>7</v>
+      </c>
+      <c r="C3653" t="n">
+        <v>58</v>
+      </c>
+      <c r="D3653" t="n">
+        <v>48</v>
+      </c>
+      <c r="E3653" t="n">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="3654">
+      <c r="A3654" t="n">
+        <v>30</v>
+      </c>
+      <c r="B3654" t="n">
+        <v>8</v>
+      </c>
+      <c r="C3654" t="n">
+        <v>35</v>
+      </c>
+      <c r="D3654" t="n">
+        <v>67</v>
+      </c>
+      <c r="E3654" t="n">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="3655">
+      <c r="A3655" t="n">
+        <v>31</v>
+      </c>
+      <c r="B3655" t="n">
+        <v>9</v>
+      </c>
+      <c r="C3655" t="n">
+        <v>44</v>
+      </c>
+      <c r="D3655" t="n">
+        <v>76</v>
+      </c>
+      <c r="E3655" t="n">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="3656">
+      <c r="A3656" t="n">
+        <v>32</v>
+      </c>
+      <c r="B3656" t="n">
+        <v>10</v>
+      </c>
+      <c r="C3656" t="n">
+        <v>37</v>
+      </c>
+      <c r="D3656" t="n">
+        <v>46</v>
+      </c>
+      <c r="E3656" t="n">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="3657">
+      <c r="A3657" t="n">
+        <v>33</v>
+      </c>
+      <c r="B3657" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3657" t="n">
+        <v>96</v>
+      </c>
+      <c r="D3657" t="n">
+        <v>20</v>
+      </c>
+      <c r="E3657" t="n">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="3658">
+      <c r="A3658" t="n">
+        <v>34</v>
+      </c>
+      <c r="B3658" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3658" t="n">
+        <v>35</v>
+      </c>
+      <c r="D3658" t="n">
+        <v>19</v>
+      </c>
+      <c r="E3658" t="n">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="3659">
+      <c r="A3659" t="n">
+        <v>35</v>
+      </c>
+      <c r="B3659" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3659" t="n">
+        <v>98</v>
+      </c>
+      <c r="D3659" t="n">
+        <v>82</v>
+      </c>
+      <c r="E3659" t="n">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="3660">
+      <c r="A3660" t="n">
+        <v>36</v>
+      </c>
+      <c r="B3660" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3660" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3660" t="n">
+        <v>24</v>
+      </c>
+      <c r="E3660" t="n">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="3661">
+      <c r="A3661" t="n">
+        <v>37</v>
+      </c>
+      <c r="B3661" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3661" t="n">
+        <v>70</v>
+      </c>
+      <c r="D3661" t="n">
+        <v>25</v>
+      </c>
+      <c r="E3661" t="n">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="3662">
+      <c r="A3662" t="n">
+        <v>38</v>
+      </c>
+      <c r="B3662" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3662" t="n">
+        <v>80</v>
+      </c>
+      <c r="D3662" t="n">
+        <v>23</v>
+      </c>
+      <c r="E3662" t="n">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="3663">
+      <c r="A3663" t="n">
+        <v>39</v>
+      </c>
+      <c r="B3663" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3663" t="n">
+        <v>25</v>
+      </c>
+      <c r="D3663" t="n">
+        <v>91</v>
+      </c>
+      <c r="E3663" t="n">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="3664">
+      <c r="A3664" t="n">
+        <v>40</v>
+      </c>
+      <c r="B3664" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3664" t="n">
+        <v>60</v>
+      </c>
+      <c r="D3664" t="n">
+        <v>54</v>
+      </c>
+      <c r="E3664" t="n">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="3665">
+      <c r="A3665" t="n">
+        <v>41</v>
+      </c>
+      <c r="B3665" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3665" t="n">
+        <v>54</v>
+      </c>
+      <c r="D3665" t="n">
+        <v>55</v>
+      </c>
+      <c r="E3665" t="n">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="3666">
+      <c r="A3666" t="n">
+        <v>42</v>
+      </c>
+      <c r="B3666" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3666" t="n">
+        <v>78</v>
+      </c>
+      <c r="D3666" t="n">
+        <v>61</v>
+      </c>
+      <c r="E3666" t="n">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="3667">
+      <c r="A3667" t="n">
+        <v>43</v>
+      </c>
+      <c r="B3667" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3667" t="n">
+        <v>57</v>
+      </c>
+      <c r="D3667" t="n">
+        <v>15</v>
+      </c>
+      <c r="E3667" t="n">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="3668">
+      <c r="A3668" t="n">
+        <v>44</v>
+      </c>
+      <c r="B3668" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3668" t="n">
+        <v>99</v>
+      </c>
+      <c r="D3668" t="n">
+        <v>71</v>
+      </c>
+      <c r="E3668" t="n">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="3669">
+      <c r="A3669" t="n">
+        <v>45</v>
+      </c>
+      <c r="B3669" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3669" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3669" t="n">
+        <v>12</v>
+      </c>
+      <c r="E3669" t="n">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="3670">
+      <c r="A3670" t="n">
+        <v>46</v>
+      </c>
+      <c r="B3670" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3670" t="n">
+        <v>17</v>
+      </c>
+      <c r="D3670" t="n">
+        <v>33</v>
+      </c>
+      <c r="E3670" t="n">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="3671">
+      <c r="A3671" t="n">
+        <v>47</v>
+      </c>
+      <c r="B3671" t="n">
+        <v>7</v>
+      </c>
+      <c r="C3671" t="n">
+        <v>41</v>
+      </c>
+      <c r="D3671" t="n">
+        <v>72</v>
+      </c>
+      <c r="E3671" t="n">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="3672">
+      <c r="A3672" t="n">
+        <v>48</v>
+      </c>
+      <c r="B3672" t="n">
+        <v>8</v>
+      </c>
+      <c r="C3672" t="n">
+        <v>56</v>
+      </c>
+      <c r="D3672" t="n">
+        <v>81</v>
+      </c>
+      <c r="E3672" t="n">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="3673">
+      <c r="A3673" t="n">
+        <v>49</v>
+      </c>
+      <c r="B3673" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3673" t="n">
+        <v>54</v>
+      </c>
+      <c r="D3673" t="n">
+        <v>65</v>
+      </c>
+      <c r="E3673" t="n">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="3674">
+      <c r="A3674" t="n">
+        <v>50</v>
+      </c>
+      <c r="B3674" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3674" t="n">
+        <v>51</v>
+      </c>
+      <c r="D3674" t="n">
+        <v>32</v>
+      </c>
+      <c r="E3674" t="n">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="3675">
+      <c r="A3675" t="n">
+        <v>51</v>
+      </c>
+      <c r="B3675" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3675" t="n">
+        <v>70</v>
+      </c>
+      <c r="D3675" t="n">
+        <v>8</v>
+      </c>
+      <c r="E3675" t="n">
+        <v>600</v>
       </c>
     </row>
   </sheetData>
@@ -71872,7 +73006,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F243"/>
+  <dimension ref="A1:F246"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78657,30 +79791,114 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Pro Active s.c</t>
+          <t>Sport Fit Team</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>3279301836</t>
+          <t>5715758035</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>Toruń</t>
+          <t>Warszawa</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
+          <t>Medycyna estetyczna / klinika urody</t>
+        </is>
+      </c>
+      <c r="F243" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="n">
+        <v>258</v>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Eko Bio</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>6839173790</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>Jastrzębie-Zdrój</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>Medycyna estetyczna / klinika urody</t>
+        </is>
+      </c>
+      <c r="F244" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="n">
+        <v>259</v>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Bio Max Sp. z o.o.</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>0609941487</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>Kościan</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
           <t>Sklep internetowy z suplementami</t>
         </is>
       </c>
-      <c r="F243" t="n">
-        <v>3</v>
+      <c r="F245" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="n">
+        <v>260</v>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Suplementy Opole</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>2304315973</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>Zduńska Wola</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>Zielarnia</t>
+        </is>
+      </c>
+      <c r="F246" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/dane.xlsx
+++ b/dane.xlsx
@@ -3759,7 +3759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G601"/>
+  <dimension ref="A1:G611"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18797,6 +18797,256 @@
       </c>
       <c r="G601" t="n">
         <v>724</v>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="n">
+        <v>601</v>
+      </c>
+      <c r="B602" s="2" t="n">
+        <v>46069</v>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>Zwrot</t>
+        </is>
+      </c>
+      <c r="D602" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E602" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F602" t="n">
+        <v>4</v>
+      </c>
+      <c r="G602" t="n">
+        <v>2399</v>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="n">
+        <v>602</v>
+      </c>
+      <c r="B603" s="2" t="n">
+        <v>46069</v>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>Zwrot</t>
+        </is>
+      </c>
+      <c r="D603" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="E603" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F603" t="n">
+        <v>2</v>
+      </c>
+      <c r="G603" t="n">
+        <v>2219</v>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="n">
+        <v>603</v>
+      </c>
+      <c r="B604" s="2" t="n">
+        <v>46090</v>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>Wysłane</t>
+        </is>
+      </c>
+      <c r="D604" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="E604" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F604" t="n">
+        <v>1</v>
+      </c>
+      <c r="G604" t="n">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="n">
+        <v>604</v>
+      </c>
+      <c r="B605" s="2" t="n">
+        <v>46089</v>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>Nowe</t>
+        </is>
+      </c>
+      <c r="D605" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E605" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F605" t="n">
+        <v>4</v>
+      </c>
+      <c r="G605" t="n">
+        <v>2326</v>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="n">
+        <v>605</v>
+      </c>
+      <c r="B606" s="2" t="n">
+        <v>46072</v>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>Zwrot</t>
+        </is>
+      </c>
+      <c r="D606" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="E606" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F606" t="n">
+        <v>3</v>
+      </c>
+      <c r="G606" t="n">
+        <v>3439</v>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="n">
+        <v>606</v>
+      </c>
+      <c r="B607" s="2" t="n">
+        <v>46095</v>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>Dostarczone</t>
+        </is>
+      </c>
+      <c r="D607" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="E607" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F607" t="n">
+        <v>2</v>
+      </c>
+      <c r="G607" t="n">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="n">
+        <v>607</v>
+      </c>
+      <c r="B608" s="2" t="n">
+        <v>46088</v>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>Wysłane</t>
+        </is>
+      </c>
+      <c r="D608" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="E608" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F608" t="n">
+        <v>3</v>
+      </c>
+      <c r="G608" t="n">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="n">
+        <v>608</v>
+      </c>
+      <c r="B609" s="2" t="n">
+        <v>46068</v>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>Nowe</t>
+        </is>
+      </c>
+      <c r="D609" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E609" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F609" t="n">
+        <v>4</v>
+      </c>
+      <c r="G609" t="n">
+        <v>2756</v>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="n">
+        <v>609</v>
+      </c>
+      <c r="B610" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>Wysłane</t>
+        </is>
+      </c>
+      <c r="D610" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="E610" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F610" t="n">
+        <v>4</v>
+      </c>
+      <c r="G610" t="n">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="n">
+        <v>610</v>
+      </c>
+      <c r="B611" s="2" t="n">
+        <v>46083</v>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>Nowe</t>
+        </is>
+      </c>
+      <c r="D611" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="E611" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F611" t="n">
+        <v>1</v>
+      </c>
+      <c r="G611" t="n">
+        <v>2775</v>
       </c>
     </row>
   </sheetData>
@@ -18810,7 +19060,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3675"/>
+  <dimension ref="A1:E3719"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -72993,6 +73243,754 @@
       </c>
       <c r="E3675" t="n">
         <v>600</v>
+      </c>
+    </row>
+    <row r="3676">
+      <c r="A3676" t="n">
+        <v>0</v>
+      </c>
+      <c r="B3676" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3676" t="n">
+        <v>16</v>
+      </c>
+      <c r="D3676" t="n">
+        <v>34</v>
+      </c>
+      <c r="E3676" t="n">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="3677">
+      <c r="A3677" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3677" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3677" t="n">
+        <v>42</v>
+      </c>
+      <c r="D3677" t="n">
+        <v>61</v>
+      </c>
+      <c r="E3677" t="n">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="3678">
+      <c r="A3678" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3678" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3678" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3678" t="n">
+        <v>28</v>
+      </c>
+      <c r="E3678" t="n">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="3679">
+      <c r="A3679" t="n">
+        <v>3</v>
+      </c>
+      <c r="B3679" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3679" t="n">
+        <v>8</v>
+      </c>
+      <c r="D3679" t="n">
+        <v>99</v>
+      </c>
+      <c r="E3679" t="n">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="3680">
+      <c r="A3680" t="n">
+        <v>4</v>
+      </c>
+      <c r="B3680" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3680" t="n">
+        <v>83</v>
+      </c>
+      <c r="D3680" t="n">
+        <v>97</v>
+      </c>
+      <c r="E3680" t="n">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="3681">
+      <c r="A3681" t="n">
+        <v>5</v>
+      </c>
+      <c r="B3681" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3681" t="n">
+        <v>63</v>
+      </c>
+      <c r="D3681" t="n">
+        <v>87</v>
+      </c>
+      <c r="E3681" t="n">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="3682">
+      <c r="A3682" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3682" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3682" t="n">
+        <v>69</v>
+      </c>
+      <c r="D3682" t="n">
+        <v>65</v>
+      </c>
+      <c r="E3682" t="n">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="3683">
+      <c r="A3683" t="n">
+        <v>7</v>
+      </c>
+      <c r="B3683" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3683" t="n">
+        <v>91</v>
+      </c>
+      <c r="D3683" t="n">
+        <v>5</v>
+      </c>
+      <c r="E3683" t="n">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="3684">
+      <c r="A3684" t="n">
+        <v>8</v>
+      </c>
+      <c r="B3684" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3684" t="n">
+        <v>47</v>
+      </c>
+      <c r="D3684" t="n">
+        <v>26</v>
+      </c>
+      <c r="E3684" t="n">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="3685">
+      <c r="A3685" t="n">
+        <v>9</v>
+      </c>
+      <c r="B3685" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3685" t="n">
+        <v>7</v>
+      </c>
+      <c r="D3685" t="n">
+        <v>88</v>
+      </c>
+      <c r="E3685" t="n">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="3686">
+      <c r="A3686" t="n">
+        <v>10</v>
+      </c>
+      <c r="B3686" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3686" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3686" t="n">
+        <v>91</v>
+      </c>
+      <c r="E3686" t="n">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="3687">
+      <c r="A3687" t="n">
+        <v>11</v>
+      </c>
+      <c r="B3687" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3687" t="n">
+        <v>24</v>
+      </c>
+      <c r="D3687" t="n">
+        <v>39</v>
+      </c>
+      <c r="E3687" t="n">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="3688">
+      <c r="A3688" t="n">
+        <v>12</v>
+      </c>
+      <c r="B3688" t="n">
+        <v>7</v>
+      </c>
+      <c r="C3688" t="n">
+        <v>70</v>
+      </c>
+      <c r="D3688" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3688" t="n">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="3689">
+      <c r="A3689" t="n">
+        <v>13</v>
+      </c>
+      <c r="B3689" t="n">
+        <v>8</v>
+      </c>
+      <c r="C3689" t="n">
+        <v>39</v>
+      </c>
+      <c r="D3689" t="n">
+        <v>91</v>
+      </c>
+      <c r="E3689" t="n">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="3690">
+      <c r="A3690" t="n">
+        <v>14</v>
+      </c>
+      <c r="B3690" t="n">
+        <v>9</v>
+      </c>
+      <c r="C3690" t="n">
+        <v>65</v>
+      </c>
+      <c r="D3690" t="n">
+        <v>67</v>
+      </c>
+      <c r="E3690" t="n">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="3691">
+      <c r="A3691" t="n">
+        <v>15</v>
+      </c>
+      <c r="B3691" t="n">
+        <v>10</v>
+      </c>
+      <c r="C3691" t="n">
+        <v>72</v>
+      </c>
+      <c r="D3691" t="n">
+        <v>91</v>
+      </c>
+      <c r="E3691" t="n">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="3692">
+      <c r="A3692" t="n">
+        <v>16</v>
+      </c>
+      <c r="B3692" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3692" t="n">
+        <v>91</v>
+      </c>
+      <c r="D3692" t="n">
+        <v>37</v>
+      </c>
+      <c r="E3692" t="n">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="3693">
+      <c r="A3693" t="n">
+        <v>17</v>
+      </c>
+      <c r="B3693" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3693" t="n">
+        <v>15</v>
+      </c>
+      <c r="D3693" t="n">
+        <v>14</v>
+      </c>
+      <c r="E3693" t="n">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="3694">
+      <c r="A3694" t="n">
+        <v>18</v>
+      </c>
+      <c r="B3694" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3694" t="n">
+        <v>59</v>
+      </c>
+      <c r="D3694" t="n">
+        <v>98</v>
+      </c>
+      <c r="E3694" t="n">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="3695">
+      <c r="A3695" t="n">
+        <v>19</v>
+      </c>
+      <c r="B3695" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3695" t="n">
+        <v>80</v>
+      </c>
+      <c r="D3695" t="n">
+        <v>20</v>
+      </c>
+      <c r="E3695" t="n">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="3696">
+      <c r="A3696" t="n">
+        <v>20</v>
+      </c>
+      <c r="B3696" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3696" t="n">
+        <v>34</v>
+      </c>
+      <c r="D3696" t="n">
+        <v>78</v>
+      </c>
+      <c r="E3696" t="n">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="3697">
+      <c r="A3697" t="n">
+        <v>21</v>
+      </c>
+      <c r="B3697" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3697" t="n">
+        <v>9</v>
+      </c>
+      <c r="D3697" t="n">
+        <v>29</v>
+      </c>
+      <c r="E3697" t="n">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="3698">
+      <c r="A3698" t="n">
+        <v>22</v>
+      </c>
+      <c r="B3698" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3698" t="n">
+        <v>57</v>
+      </c>
+      <c r="D3698" t="n">
+        <v>90</v>
+      </c>
+      <c r="E3698" t="n">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="3699">
+      <c r="A3699" t="n">
+        <v>23</v>
+      </c>
+      <c r="B3699" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3699" t="n">
+        <v>24</v>
+      </c>
+      <c r="D3699" t="n">
+        <v>48</v>
+      </c>
+      <c r="E3699" t="n">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="3700">
+      <c r="A3700" t="n">
+        <v>24</v>
+      </c>
+      <c r="B3700" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3700" t="n">
+        <v>20</v>
+      </c>
+      <c r="D3700" t="n">
+        <v>73</v>
+      </c>
+      <c r="E3700" t="n">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="3701">
+      <c r="A3701" t="n">
+        <v>25</v>
+      </c>
+      <c r="B3701" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3701" t="n">
+        <v>97</v>
+      </c>
+      <c r="D3701" t="n">
+        <v>60</v>
+      </c>
+      <c r="E3701" t="n">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="3702">
+      <c r="A3702" t="n">
+        <v>26</v>
+      </c>
+      <c r="B3702" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3702" t="n">
+        <v>93</v>
+      </c>
+      <c r="D3702" t="n">
+        <v>41</v>
+      </c>
+      <c r="E3702" t="n">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="3703">
+      <c r="A3703" t="n">
+        <v>27</v>
+      </c>
+      <c r="B3703" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3703" t="n">
+        <v>35</v>
+      </c>
+      <c r="D3703" t="n">
+        <v>51</v>
+      </c>
+      <c r="E3703" t="n">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="3704">
+      <c r="A3704" t="n">
+        <v>28</v>
+      </c>
+      <c r="B3704" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3704" t="n">
+        <v>83</v>
+      </c>
+      <c r="D3704" t="n">
+        <v>22</v>
+      </c>
+      <c r="E3704" t="n">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="3705">
+      <c r="A3705" t="n">
+        <v>29</v>
+      </c>
+      <c r="B3705" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3705" t="n">
+        <v>91</v>
+      </c>
+      <c r="D3705" t="n">
+        <v>38</v>
+      </c>
+      <c r="E3705" t="n">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="3706">
+      <c r="A3706" t="n">
+        <v>30</v>
+      </c>
+      <c r="B3706" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3706" t="n">
+        <v>46</v>
+      </c>
+      <c r="D3706" t="n">
+        <v>24</v>
+      </c>
+      <c r="E3706" t="n">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="3707">
+      <c r="A3707" t="n">
+        <v>31</v>
+      </c>
+      <c r="B3707" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3707" t="n">
+        <v>6</v>
+      </c>
+      <c r="D3707" t="n">
+        <v>8</v>
+      </c>
+      <c r="E3707" t="n">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="3708">
+      <c r="A3708" t="n">
+        <v>32</v>
+      </c>
+      <c r="B3708" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3708" t="n">
+        <v>32</v>
+      </c>
+      <c r="D3708" t="n">
+        <v>10</v>
+      </c>
+      <c r="E3708" t="n">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="3709">
+      <c r="A3709" t="n">
+        <v>33</v>
+      </c>
+      <c r="B3709" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3709" t="n">
+        <v>67</v>
+      </c>
+      <c r="D3709" t="n">
+        <v>13</v>
+      </c>
+      <c r="E3709" t="n">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="3710">
+      <c r="A3710" t="n">
+        <v>34</v>
+      </c>
+      <c r="B3710" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3710" t="n">
+        <v>51</v>
+      </c>
+      <c r="D3710" t="n">
+        <v>47</v>
+      </c>
+      <c r="E3710" t="n">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="3711">
+      <c r="A3711" t="n">
+        <v>35</v>
+      </c>
+      <c r="B3711" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3711" t="n">
+        <v>91</v>
+      </c>
+      <c r="D3711" t="n">
+        <v>94</v>
+      </c>
+      <c r="E3711" t="n">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="3712">
+      <c r="A3712" t="n">
+        <v>36</v>
+      </c>
+      <c r="B3712" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3712" t="n">
+        <v>58</v>
+      </c>
+      <c r="D3712" t="n">
+        <v>43</v>
+      </c>
+      <c r="E3712" t="n">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="3713">
+      <c r="A3713" t="n">
+        <v>37</v>
+      </c>
+      <c r="B3713" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3713" t="n">
+        <v>22</v>
+      </c>
+      <c r="D3713" t="n">
+        <v>70</v>
+      </c>
+      <c r="E3713" t="n">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="3714">
+      <c r="A3714" t="n">
+        <v>38</v>
+      </c>
+      <c r="B3714" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3714" t="n">
+        <v>18</v>
+      </c>
+      <c r="D3714" t="n">
+        <v>56</v>
+      </c>
+      <c r="E3714" t="n">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="3715">
+      <c r="A3715" t="n">
+        <v>39</v>
+      </c>
+      <c r="B3715" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3715" t="n">
+        <v>19</v>
+      </c>
+      <c r="D3715" t="n">
+        <v>10</v>
+      </c>
+      <c r="E3715" t="n">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="3716">
+      <c r="A3716" t="n">
+        <v>40</v>
+      </c>
+      <c r="B3716" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3716" t="n">
+        <v>68</v>
+      </c>
+      <c r="D3716" t="n">
+        <v>93</v>
+      </c>
+      <c r="E3716" t="n">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="3717">
+      <c r="A3717" t="n">
+        <v>41</v>
+      </c>
+      <c r="B3717" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3717" t="n">
+        <v>50</v>
+      </c>
+      <c r="D3717" t="n">
+        <v>17</v>
+      </c>
+      <c r="E3717" t="n">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="3718">
+      <c r="A3718" t="n">
+        <v>42</v>
+      </c>
+      <c r="B3718" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3718" t="n">
+        <v>82</v>
+      </c>
+      <c r="D3718" t="n">
+        <v>75</v>
+      </c>
+      <c r="E3718" t="n">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="3719">
+      <c r="A3719" t="n">
+        <v>43</v>
+      </c>
+      <c r="B3719" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3719" t="n">
+        <v>94</v>
+      </c>
+      <c r="D3719" t="n">
+        <v>76</v>
+      </c>
+      <c r="E3719" t="n">
+        <v>610</v>
       </c>
     </row>
   </sheetData>
@@ -73006,7 +74004,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F246"/>
+  <dimension ref="A1:F249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -79875,21 +80873,21 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Suplementy Opole</t>
+          <t>Apteka Sosnowiec</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>2304315973</t>
+          <t>3489128030</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>Zduńska Wola</t>
+          <t>Szczecin</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -79898,7 +80896,91 @@
         </is>
       </c>
       <c r="F246" t="n">
-        <v>4</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="n">
+        <v>262</v>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Pro Pharma Chorzów</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>7261860096</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>Piekary Śląskie</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>Siłownia / klub sportowy</t>
+        </is>
+      </c>
+      <c r="F247" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="n">
+        <v>263</v>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Elite Dbam o Zdrowie Jaworzno</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>2058363375</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>Wodzisław Śląski</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>Gabinet dietetyczny</t>
+        </is>
+      </c>
+      <c r="F248" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="n">
+        <v>264</v>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Muscle Health s.c</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>4555070472</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>Wałcz</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>Zielarnia</t>
+        </is>
+      </c>
+      <c r="F249" t="n">
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/dane.xlsx
+++ b/dane.xlsx
@@ -3759,7 +3759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G611"/>
+  <dimension ref="A1:G621"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19047,6 +19047,256 @@
       </c>
       <c r="G611" t="n">
         <v>2775</v>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="n">
+        <v>611</v>
+      </c>
+      <c r="B612" s="2" t="n">
+        <v>46081</v>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>Wysłane</t>
+        </is>
+      </c>
+      <c r="D612" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E612" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F612" t="n">
+        <v>3</v>
+      </c>
+      <c r="G612" t="n">
+        <v>1475</v>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="n">
+        <v>612</v>
+      </c>
+      <c r="B613" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>Wysłane</t>
+        </is>
+      </c>
+      <c r="D613" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="E613" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F613" t="n">
+        <v>4</v>
+      </c>
+      <c r="G613" t="n">
+        <v>1726</v>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="n">
+        <v>613</v>
+      </c>
+      <c r="B614" s="2" t="n">
+        <v>46090</v>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>Wysłane</t>
+        </is>
+      </c>
+      <c r="D614" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="E614" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F614" t="n">
+        <v>2</v>
+      </c>
+      <c r="G614" t="n">
+        <v>1696</v>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="n">
+        <v>614</v>
+      </c>
+      <c r="B615" s="2" t="n">
+        <v>46070</v>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>Wysłane</t>
+        </is>
+      </c>
+      <c r="D615" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E615" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F615" t="n">
+        <v>3</v>
+      </c>
+      <c r="G615" t="n">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="n">
+        <v>615</v>
+      </c>
+      <c r="B616" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>Zwrot</t>
+        </is>
+      </c>
+      <c r="D616" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="E616" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F616" t="n">
+        <v>2</v>
+      </c>
+      <c r="G616" t="n">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="n">
+        <v>616</v>
+      </c>
+      <c r="B617" s="2" t="n">
+        <v>46078</v>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>Zwrot</t>
+        </is>
+      </c>
+      <c r="D617" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="E617" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F617" t="n">
+        <v>3</v>
+      </c>
+      <c r="G617" t="n">
+        <v>1857</v>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="n">
+        <v>617</v>
+      </c>
+      <c r="B618" s="2" t="n">
+        <v>46067</v>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>Nowe</t>
+        </is>
+      </c>
+      <c r="D618" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="E618" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F618" t="n">
+        <v>2</v>
+      </c>
+      <c r="G618" t="n">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="n">
+        <v>618</v>
+      </c>
+      <c r="B619" s="2" t="n">
+        <v>46095</v>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>Wysłane</t>
+        </is>
+      </c>
+      <c r="D619" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E619" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F619" t="n">
+        <v>2</v>
+      </c>
+      <c r="G619" t="n">
+        <v>3122</v>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="n">
+        <v>619</v>
+      </c>
+      <c r="B620" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>Zwrot</t>
+        </is>
+      </c>
+      <c r="D620" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="E620" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F620" t="n">
+        <v>4</v>
+      </c>
+      <c r="G620" t="n">
+        <v>1507</v>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="n">
+        <v>620</v>
+      </c>
+      <c r="B621" s="2" t="n">
+        <v>46095</v>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>Nowe</t>
+        </is>
+      </c>
+      <c r="D621" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="E621" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F621" t="n">
+        <v>2</v>
+      </c>
+      <c r="G621" t="n">
+        <v>1296</v>
       </c>
     </row>
   </sheetData>
@@ -19060,7 +19310,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3719"/>
+  <dimension ref="A1:E3775"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73991,6 +74241,958 @@
       </c>
       <c r="E3719" t="n">
         <v>610</v>
+      </c>
+    </row>
+    <row r="3720">
+      <c r="A3720" t="n">
+        <v>0</v>
+      </c>
+      <c r="B3720" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3720" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3720" t="n">
+        <v>4</v>
+      </c>
+      <c r="E3720" t="n">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="3721">
+      <c r="A3721" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3721" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3721" t="n">
+        <v>66</v>
+      </c>
+      <c r="D3721" t="n">
+        <v>80</v>
+      </c>
+      <c r="E3721" t="n">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="3722">
+      <c r="A3722" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3722" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3722" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3722" t="n">
+        <v>35</v>
+      </c>
+      <c r="E3722" t="n">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="3723">
+      <c r="A3723" t="n">
+        <v>3</v>
+      </c>
+      <c r="B3723" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3723" t="n">
+        <v>45</v>
+      </c>
+      <c r="D3723" t="n">
+        <v>5</v>
+      </c>
+      <c r="E3723" t="n">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="3724">
+      <c r="A3724" t="n">
+        <v>4</v>
+      </c>
+      <c r="B3724" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3724" t="n">
+        <v>78</v>
+      </c>
+      <c r="D3724" t="n">
+        <v>66</v>
+      </c>
+      <c r="E3724" t="n">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="3725">
+      <c r="A3725" t="n">
+        <v>5</v>
+      </c>
+      <c r="B3725" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3725" t="n">
+        <v>29</v>
+      </c>
+      <c r="D3725" t="n">
+        <v>56</v>
+      </c>
+      <c r="E3725" t="n">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="3726">
+      <c r="A3726" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3726" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3726" t="n">
+        <v>48</v>
+      </c>
+      <c r="D3726" t="n">
+        <v>6</v>
+      </c>
+      <c r="E3726" t="n">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="3727">
+      <c r="A3727" t="n">
+        <v>7</v>
+      </c>
+      <c r="B3727" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3727" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3727" t="n">
+        <v>60</v>
+      </c>
+      <c r="E3727" t="n">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="3728">
+      <c r="A3728" t="n">
+        <v>8</v>
+      </c>
+      <c r="B3728" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3728" t="n">
+        <v>48</v>
+      </c>
+      <c r="D3728" t="n">
+        <v>86</v>
+      </c>
+      <c r="E3728" t="n">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="3729">
+      <c r="A3729" t="n">
+        <v>9</v>
+      </c>
+      <c r="B3729" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3729" t="n">
+        <v>78</v>
+      </c>
+      <c r="D3729" t="n">
+        <v>52</v>
+      </c>
+      <c r="E3729" t="n">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="3730">
+      <c r="A3730" t="n">
+        <v>10</v>
+      </c>
+      <c r="B3730" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3730" t="n">
+        <v>46</v>
+      </c>
+      <c r="D3730" t="n">
+        <v>61</v>
+      </c>
+      <c r="E3730" t="n">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="3731">
+      <c r="A3731" t="n">
+        <v>11</v>
+      </c>
+      <c r="B3731" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3731" t="n">
+        <v>57</v>
+      </c>
+      <c r="D3731" t="n">
+        <v>23</v>
+      </c>
+      <c r="E3731" t="n">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="3732">
+      <c r="A3732" t="n">
+        <v>12</v>
+      </c>
+      <c r="B3732" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3732" t="n">
+        <v>45</v>
+      </c>
+      <c r="D3732" t="n">
+        <v>87</v>
+      </c>
+      <c r="E3732" t="n">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="3733">
+      <c r="A3733" t="n">
+        <v>13</v>
+      </c>
+      <c r="B3733" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3733" t="n">
+        <v>32</v>
+      </c>
+      <c r="D3733" t="n">
+        <v>29</v>
+      </c>
+      <c r="E3733" t="n">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="3734">
+      <c r="A3734" t="n">
+        <v>14</v>
+      </c>
+      <c r="B3734" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3734" t="n">
+        <v>13</v>
+      </c>
+      <c r="D3734" t="n">
+        <v>88</v>
+      </c>
+      <c r="E3734" t="n">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="3735">
+      <c r="A3735" t="n">
+        <v>15</v>
+      </c>
+      <c r="B3735" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3735" t="n">
+        <v>58</v>
+      </c>
+      <c r="D3735" t="n">
+        <v>98</v>
+      </c>
+      <c r="E3735" t="n">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="3736">
+      <c r="A3736" t="n">
+        <v>16</v>
+      </c>
+      <c r="B3736" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3736" t="n">
+        <v>16</v>
+      </c>
+      <c r="D3736" t="n">
+        <v>96</v>
+      </c>
+      <c r="E3736" t="n">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="3737">
+      <c r="A3737" t="n">
+        <v>17</v>
+      </c>
+      <c r="B3737" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3737" t="n">
+        <v>23</v>
+      </c>
+      <c r="D3737" t="n">
+        <v>34</v>
+      </c>
+      <c r="E3737" t="n">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="3738">
+      <c r="A3738" t="n">
+        <v>18</v>
+      </c>
+      <c r="B3738" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3738" t="n">
+        <v>13</v>
+      </c>
+      <c r="D3738" t="n">
+        <v>71</v>
+      </c>
+      <c r="E3738" t="n">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="3739">
+      <c r="A3739" t="n">
+        <v>19</v>
+      </c>
+      <c r="B3739" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3739" t="n">
+        <v>6</v>
+      </c>
+      <c r="D3739" t="n">
+        <v>12</v>
+      </c>
+      <c r="E3739" t="n">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="3740">
+      <c r="A3740" t="n">
+        <v>20</v>
+      </c>
+      <c r="B3740" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3740" t="n">
+        <v>14</v>
+      </c>
+      <c r="D3740" t="n">
+        <v>35</v>
+      </c>
+      <c r="E3740" t="n">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="3741">
+      <c r="A3741" t="n">
+        <v>21</v>
+      </c>
+      <c r="B3741" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3741" t="n">
+        <v>51</v>
+      </c>
+      <c r="D3741" t="n">
+        <v>5</v>
+      </c>
+      <c r="E3741" t="n">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="3742">
+      <c r="A3742" t="n">
+        <v>22</v>
+      </c>
+      <c r="B3742" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3742" t="n">
+        <v>64</v>
+      </c>
+      <c r="D3742" t="n">
+        <v>10</v>
+      </c>
+      <c r="E3742" t="n">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="3743">
+      <c r="A3743" t="n">
+        <v>23</v>
+      </c>
+      <c r="B3743" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3743" t="n">
+        <v>94</v>
+      </c>
+      <c r="D3743" t="n">
+        <v>79</v>
+      </c>
+      <c r="E3743" t="n">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="3744">
+      <c r="A3744" t="n">
+        <v>24</v>
+      </c>
+      <c r="B3744" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3744" t="n">
+        <v>46</v>
+      </c>
+      <c r="D3744" t="n">
+        <v>69</v>
+      </c>
+      <c r="E3744" t="n">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="3745">
+      <c r="A3745" t="n">
+        <v>25</v>
+      </c>
+      <c r="B3745" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3745" t="n">
+        <v>66</v>
+      </c>
+      <c r="D3745" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3745" t="n">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="3746">
+      <c r="A3746" t="n">
+        <v>26</v>
+      </c>
+      <c r="B3746" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3746" t="n">
+        <v>31</v>
+      </c>
+      <c r="D3746" t="n">
+        <v>20</v>
+      </c>
+      <c r="E3746" t="n">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="3747">
+      <c r="A3747" t="n">
+        <v>27</v>
+      </c>
+      <c r="B3747" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3747" t="n">
+        <v>8</v>
+      </c>
+      <c r="D3747" t="n">
+        <v>36</v>
+      </c>
+      <c r="E3747" t="n">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="3748">
+      <c r="A3748" t="n">
+        <v>28</v>
+      </c>
+      <c r="B3748" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3748" t="n">
+        <v>37</v>
+      </c>
+      <c r="D3748" t="n">
+        <v>31</v>
+      </c>
+      <c r="E3748" t="n">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="3749">
+      <c r="A3749" t="n">
+        <v>29</v>
+      </c>
+      <c r="B3749" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3749" t="n">
+        <v>70</v>
+      </c>
+      <c r="D3749" t="n">
+        <v>53</v>
+      </c>
+      <c r="E3749" t="n">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="3750">
+      <c r="A3750" t="n">
+        <v>30</v>
+      </c>
+      <c r="B3750" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3750" t="n">
+        <v>31</v>
+      </c>
+      <c r="D3750" t="n">
+        <v>44</v>
+      </c>
+      <c r="E3750" t="n">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="3751">
+      <c r="A3751" t="n">
+        <v>31</v>
+      </c>
+      <c r="B3751" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3751" t="n">
+        <v>35</v>
+      </c>
+      <c r="D3751" t="n">
+        <v>66</v>
+      </c>
+      <c r="E3751" t="n">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="3752">
+      <c r="A3752" t="n">
+        <v>32</v>
+      </c>
+      <c r="B3752" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3752" t="n">
+        <v>46</v>
+      </c>
+      <c r="D3752" t="n">
+        <v>86</v>
+      </c>
+      <c r="E3752" t="n">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="3753">
+      <c r="A3753" t="n">
+        <v>33</v>
+      </c>
+      <c r="B3753" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3753" t="n">
+        <v>61</v>
+      </c>
+      <c r="D3753" t="n">
+        <v>23</v>
+      </c>
+      <c r="E3753" t="n">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="3754">
+      <c r="A3754" t="n">
+        <v>34</v>
+      </c>
+      <c r="B3754" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3754" t="n">
+        <v>63</v>
+      </c>
+      <c r="D3754" t="n">
+        <v>56</v>
+      </c>
+      <c r="E3754" t="n">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="3755">
+      <c r="A3755" t="n">
+        <v>35</v>
+      </c>
+      <c r="B3755" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3755" t="n">
+        <v>95</v>
+      </c>
+      <c r="D3755" t="n">
+        <v>89</v>
+      </c>
+      <c r="E3755" t="n">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="3756">
+      <c r="A3756" t="n">
+        <v>36</v>
+      </c>
+      <c r="B3756" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3756" t="n">
+        <v>69</v>
+      </c>
+      <c r="D3756" t="n">
+        <v>30</v>
+      </c>
+      <c r="E3756" t="n">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="3757">
+      <c r="A3757" t="n">
+        <v>37</v>
+      </c>
+      <c r="B3757" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3757" t="n">
+        <v>12</v>
+      </c>
+      <c r="D3757" t="n">
+        <v>50</v>
+      </c>
+      <c r="E3757" t="n">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="3758">
+      <c r="A3758" t="n">
+        <v>38</v>
+      </c>
+      <c r="B3758" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3758" t="n">
+        <v>82</v>
+      </c>
+      <c r="D3758" t="n">
+        <v>87</v>
+      </c>
+      <c r="E3758" t="n">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="3759">
+      <c r="A3759" t="n">
+        <v>39</v>
+      </c>
+      <c r="B3759" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3759" t="n">
+        <v>34</v>
+      </c>
+      <c r="D3759" t="n">
+        <v>76</v>
+      </c>
+      <c r="E3759" t="n">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="3760">
+      <c r="A3760" t="n">
+        <v>40</v>
+      </c>
+      <c r="B3760" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3760" t="n">
+        <v>48</v>
+      </c>
+      <c r="D3760" t="n">
+        <v>88</v>
+      </c>
+      <c r="E3760" t="n">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="3761">
+      <c r="A3761" t="n">
+        <v>41</v>
+      </c>
+      <c r="B3761" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3761" t="n">
+        <v>22</v>
+      </c>
+      <c r="D3761" t="n">
+        <v>69</v>
+      </c>
+      <c r="E3761" t="n">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="3762">
+      <c r="A3762" t="n">
+        <v>42</v>
+      </c>
+      <c r="B3762" t="n">
+        <v>7</v>
+      </c>
+      <c r="C3762" t="n">
+        <v>57</v>
+      </c>
+      <c r="D3762" t="n">
+        <v>36</v>
+      </c>
+      <c r="E3762" t="n">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="3763">
+      <c r="A3763" t="n">
+        <v>43</v>
+      </c>
+      <c r="B3763" t="n">
+        <v>8</v>
+      </c>
+      <c r="C3763" t="n">
+        <v>13</v>
+      </c>
+      <c r="D3763" t="n">
+        <v>97</v>
+      </c>
+      <c r="E3763" t="n">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="3764">
+      <c r="A3764" t="n">
+        <v>44</v>
+      </c>
+      <c r="B3764" t="n">
+        <v>9</v>
+      </c>
+      <c r="C3764" t="n">
+        <v>12</v>
+      </c>
+      <c r="D3764" t="n">
+        <v>72</v>
+      </c>
+      <c r="E3764" t="n">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="3765">
+      <c r="A3765" t="n">
+        <v>45</v>
+      </c>
+      <c r="B3765" t="n">
+        <v>10</v>
+      </c>
+      <c r="C3765" t="n">
+        <v>38</v>
+      </c>
+      <c r="D3765" t="n">
+        <v>84</v>
+      </c>
+      <c r="E3765" t="n">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="3766">
+      <c r="A3766" t="n">
+        <v>46</v>
+      </c>
+      <c r="B3766" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3766" t="n">
+        <v>75</v>
+      </c>
+      <c r="D3766" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3766" t="n">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="3767">
+      <c r="A3767" t="n">
+        <v>47</v>
+      </c>
+      <c r="B3767" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3767" t="n">
+        <v>55</v>
+      </c>
+      <c r="D3767" t="n">
+        <v>13</v>
+      </c>
+      <c r="E3767" t="n">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="3768">
+      <c r="A3768" t="n">
+        <v>48</v>
+      </c>
+      <c r="B3768" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3768" t="n">
+        <v>96</v>
+      </c>
+      <c r="D3768" t="n">
+        <v>38</v>
+      </c>
+      <c r="E3768" t="n">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="3769">
+      <c r="A3769" t="n">
+        <v>49</v>
+      </c>
+      <c r="B3769" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3769" t="n">
+        <v>34</v>
+      </c>
+      <c r="D3769" t="n">
+        <v>74</v>
+      </c>
+      <c r="E3769" t="n">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="3770">
+      <c r="A3770" t="n">
+        <v>50</v>
+      </c>
+      <c r="B3770" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3770" t="n">
+        <v>57</v>
+      </c>
+      <c r="D3770" t="n">
+        <v>79</v>
+      </c>
+      <c r="E3770" t="n">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="3771">
+      <c r="A3771" t="n">
+        <v>51</v>
+      </c>
+      <c r="B3771" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3771" t="n">
+        <v>28</v>
+      </c>
+      <c r="D3771" t="n">
+        <v>73</v>
+      </c>
+      <c r="E3771" t="n">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="3772">
+      <c r="A3772" t="n">
+        <v>52</v>
+      </c>
+      <c r="B3772" t="n">
+        <v>7</v>
+      </c>
+      <c r="C3772" t="n">
+        <v>44</v>
+      </c>
+      <c r="D3772" t="n">
+        <v>86</v>
+      </c>
+      <c r="E3772" t="n">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="3773">
+      <c r="A3773" t="n">
+        <v>53</v>
+      </c>
+      <c r="B3773" t="n">
+        <v>8</v>
+      </c>
+      <c r="C3773" t="n">
+        <v>76</v>
+      </c>
+      <c r="D3773" t="n">
+        <v>57</v>
+      </c>
+      <c r="E3773" t="n">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="3774">
+      <c r="A3774" t="n">
+        <v>54</v>
+      </c>
+      <c r="B3774" t="n">
+        <v>9</v>
+      </c>
+      <c r="C3774" t="n">
+        <v>73</v>
+      </c>
+      <c r="D3774" t="n">
+        <v>22</v>
+      </c>
+      <c r="E3774" t="n">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="3775">
+      <c r="A3775" t="n">
+        <v>55</v>
+      </c>
+      <c r="B3775" t="n">
+        <v>10</v>
+      </c>
+      <c r="C3775" t="n">
+        <v>74</v>
+      </c>
+      <c r="D3775" t="n">
+        <v>44</v>
+      </c>
+      <c r="E3775" t="n">
+        <v>620</v>
       </c>
     </row>
   </sheetData>
@@ -74004,7 +75206,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F249"/>
+  <dimension ref="A1:F252"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -80957,29 +82159,113 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Muscle Health s.c</t>
+          <t>Apteki Expert</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>4555070472</t>
+          <t>9787698337</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>Wałcz</t>
+          <t>Grudziądz</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Zielarnia</t>
+          <t>Sklep internetowy z suplementami</t>
         </is>
       </c>
       <c r="F249" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="n">
+        <v>266</v>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Vita Elbląg</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>1685334876</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>Białystok</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>Siłownia / klub sportowy</t>
+        </is>
+      </c>
+      <c r="F250" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="n">
+        <v>267</v>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Eco Naturalna Kielce</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>5250320566</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>Mysłowice</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>Siłownia / klub sportowy</t>
+        </is>
+      </c>
+      <c r="F251" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="n">
+        <v>268</v>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Naturalna Poznań</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>1645388926</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>Augustów</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>Siłownia / klub sportowy</t>
+        </is>
+      </c>
+      <c r="F252" t="n">
         <v>13</v>
       </c>
     </row>

--- a/dane.xlsx
+++ b/dane.xlsx
@@ -3759,7 +3759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G621"/>
+  <dimension ref="A1:G631"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19297,6 +19297,256 @@
       </c>
       <c r="G621" t="n">
         <v>1296</v>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="n">
+        <v>621</v>
+      </c>
+      <c r="B622" s="2" t="n">
+        <v>46073</v>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>Wysłane</t>
+        </is>
+      </c>
+      <c r="D622" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="E622" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F622" t="n">
+        <v>4</v>
+      </c>
+      <c r="G622" t="n">
+        <v>2291</v>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="n">
+        <v>622</v>
+      </c>
+      <c r="B623" s="2" t="n">
+        <v>46083</v>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>Nowe</t>
+        </is>
+      </c>
+      <c r="D623" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E623" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F623" t="n">
+        <v>2</v>
+      </c>
+      <c r="G623" t="n">
+        <v>1398</v>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="n">
+        <v>623</v>
+      </c>
+      <c r="B624" s="2" t="n">
+        <v>46083</v>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>Nowe</t>
+        </is>
+      </c>
+      <c r="D624" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="E624" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F624" t="n">
+        <v>2</v>
+      </c>
+      <c r="G624" t="n">
+        <v>3363</v>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="n">
+        <v>624</v>
+      </c>
+      <c r="B625" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>Nowe</t>
+        </is>
+      </c>
+      <c r="D625" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="E625" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F625" t="n">
+        <v>3</v>
+      </c>
+      <c r="G625" t="n">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="n">
+        <v>625</v>
+      </c>
+      <c r="B626" s="2" t="n">
+        <v>46075</v>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>Zwrot</t>
+        </is>
+      </c>
+      <c r="D626" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="E626" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F626" t="n">
+        <v>1</v>
+      </c>
+      <c r="G626" t="n">
+        <v>2111</v>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="n">
+        <v>626</v>
+      </c>
+      <c r="B627" s="2" t="n">
+        <v>46070</v>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>Nowe</t>
+        </is>
+      </c>
+      <c r="D627" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="E627" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F627" t="n">
+        <v>1</v>
+      </c>
+      <c r="G627" t="n">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="n">
+        <v>627</v>
+      </c>
+      <c r="B628" s="2" t="n">
+        <v>46074</v>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>Zwrot</t>
+        </is>
+      </c>
+      <c r="D628" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E628" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F628" t="n">
+        <v>3</v>
+      </c>
+      <c r="G628" t="n">
+        <v>1935</v>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="n">
+        <v>628</v>
+      </c>
+      <c r="B629" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>Wysłane</t>
+        </is>
+      </c>
+      <c r="D629" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E629" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F629" t="n">
+        <v>4</v>
+      </c>
+      <c r="G629" t="n">
+        <v>2361</v>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="n">
+        <v>629</v>
+      </c>
+      <c r="B630" s="2" t="n">
+        <v>46088</v>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>Nowe</t>
+        </is>
+      </c>
+      <c r="D630" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E630" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F630" t="n">
+        <v>3</v>
+      </c>
+      <c r="G630" t="n">
+        <v>2457</v>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="n">
+        <v>630</v>
+      </c>
+      <c r="B631" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>Nowe</t>
+        </is>
+      </c>
+      <c r="D631" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E631" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F631" t="n">
+        <v>3</v>
+      </c>
+      <c r="G631" t="n">
+        <v>2671</v>
       </c>
     </row>
   </sheetData>
@@ -19310,7 +19560,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3775"/>
+  <dimension ref="A1:E3825"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75193,6 +75443,856 @@
       </c>
       <c r="E3775" t="n">
         <v>620</v>
+      </c>
+    </row>
+    <row r="3776">
+      <c r="A3776" t="n">
+        <v>0</v>
+      </c>
+      <c r="B3776" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3776" t="n">
+        <v>18</v>
+      </c>
+      <c r="D3776" t="n">
+        <v>37</v>
+      </c>
+      <c r="E3776" t="n">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="3777">
+      <c r="A3777" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3777" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3777" t="n">
+        <v>61</v>
+      </c>
+      <c r="D3777" t="n">
+        <v>64</v>
+      </c>
+      <c r="E3777" t="n">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="3778">
+      <c r="A3778" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3778" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3778" t="n">
+        <v>92</v>
+      </c>
+      <c r="D3778" t="n">
+        <v>94</v>
+      </c>
+      <c r="E3778" t="n">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="3779">
+      <c r="A3779" t="n">
+        <v>3</v>
+      </c>
+      <c r="B3779" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3779" t="n">
+        <v>51</v>
+      </c>
+      <c r="D3779" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3779" t="n">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="3780">
+      <c r="A3780" t="n">
+        <v>4</v>
+      </c>
+      <c r="B3780" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3780" t="n">
+        <v>77</v>
+      </c>
+      <c r="D3780" t="n">
+        <v>52</v>
+      </c>
+      <c r="E3780" t="n">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="3781">
+      <c r="A3781" t="n">
+        <v>5</v>
+      </c>
+      <c r="B3781" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3781" t="n">
+        <v>16</v>
+      </c>
+      <c r="D3781" t="n">
+        <v>6</v>
+      </c>
+      <c r="E3781" t="n">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="3782">
+      <c r="A3782" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3782" t="n">
+        <v>7</v>
+      </c>
+      <c r="C3782" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3782" t="n">
+        <v>38</v>
+      </c>
+      <c r="E3782" t="n">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="3783">
+      <c r="A3783" t="n">
+        <v>7</v>
+      </c>
+      <c r="B3783" t="n">
+        <v>8</v>
+      </c>
+      <c r="C3783" t="n">
+        <v>29</v>
+      </c>
+      <c r="D3783" t="n">
+        <v>44</v>
+      </c>
+      <c r="E3783" t="n">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="3784">
+      <c r="A3784" t="n">
+        <v>8</v>
+      </c>
+      <c r="B3784" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3784" t="n">
+        <v>96</v>
+      </c>
+      <c r="D3784" t="n">
+        <v>95</v>
+      </c>
+      <c r="E3784" t="n">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="3785">
+      <c r="A3785" t="n">
+        <v>9</v>
+      </c>
+      <c r="B3785" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3785" t="n">
+        <v>25</v>
+      </c>
+      <c r="D3785" t="n">
+        <v>47</v>
+      </c>
+      <c r="E3785" t="n">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="3786">
+      <c r="A3786" t="n">
+        <v>10</v>
+      </c>
+      <c r="B3786" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3786" t="n">
+        <v>98</v>
+      </c>
+      <c r="D3786" t="n">
+        <v>18</v>
+      </c>
+      <c r="E3786" t="n">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="3787">
+      <c r="A3787" t="n">
+        <v>11</v>
+      </c>
+      <c r="B3787" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3787" t="n">
+        <v>92</v>
+      </c>
+      <c r="D3787" t="n">
+        <v>14</v>
+      </c>
+      <c r="E3787" t="n">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="3788">
+      <c r="A3788" t="n">
+        <v>12</v>
+      </c>
+      <c r="B3788" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3788" t="n">
+        <v>13</v>
+      </c>
+      <c r="D3788" t="n">
+        <v>33</v>
+      </c>
+      <c r="E3788" t="n">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="3789">
+      <c r="A3789" t="n">
+        <v>13</v>
+      </c>
+      <c r="B3789" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3789" t="n">
+        <v>72</v>
+      </c>
+      <c r="D3789" t="n">
+        <v>14</v>
+      </c>
+      <c r="E3789" t="n">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="3790">
+      <c r="A3790" t="n">
+        <v>14</v>
+      </c>
+      <c r="B3790" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3790" t="n">
+        <v>54</v>
+      </c>
+      <c r="D3790" t="n">
+        <v>26</v>
+      </c>
+      <c r="E3790" t="n">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="3791">
+      <c r="A3791" t="n">
+        <v>15</v>
+      </c>
+      <c r="B3791" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3791" t="n">
+        <v>15</v>
+      </c>
+      <c r="D3791" t="n">
+        <v>96</v>
+      </c>
+      <c r="E3791" t="n">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="3792">
+      <c r="A3792" t="n">
+        <v>16</v>
+      </c>
+      <c r="B3792" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3792" t="n">
+        <v>78</v>
+      </c>
+      <c r="D3792" t="n">
+        <v>33</v>
+      </c>
+      <c r="E3792" t="n">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="3793">
+      <c r="A3793" t="n">
+        <v>17</v>
+      </c>
+      <c r="B3793" t="n">
+        <v>7</v>
+      </c>
+      <c r="C3793" t="n">
+        <v>46</v>
+      </c>
+      <c r="D3793" t="n">
+        <v>44</v>
+      </c>
+      <c r="E3793" t="n">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="3794">
+      <c r="A3794" t="n">
+        <v>18</v>
+      </c>
+      <c r="B3794" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3794" t="n">
+        <v>97</v>
+      </c>
+      <c r="D3794" t="n">
+        <v>50</v>
+      </c>
+      <c r="E3794" t="n">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="3795">
+      <c r="A3795" t="n">
+        <v>19</v>
+      </c>
+      <c r="B3795" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3795" t="n">
+        <v>63</v>
+      </c>
+      <c r="D3795" t="n">
+        <v>73</v>
+      </c>
+      <c r="E3795" t="n">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="3796">
+      <c r="A3796" t="n">
+        <v>20</v>
+      </c>
+      <c r="B3796" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3796" t="n">
+        <v>99</v>
+      </c>
+      <c r="D3796" t="n">
+        <v>75</v>
+      </c>
+      <c r="E3796" t="n">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="3797">
+      <c r="A3797" t="n">
+        <v>21</v>
+      </c>
+      <c r="B3797" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3797" t="n">
+        <v>78</v>
+      </c>
+      <c r="D3797" t="n">
+        <v>82</v>
+      </c>
+      <c r="E3797" t="n">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="3798">
+      <c r="A3798" t="n">
+        <v>22</v>
+      </c>
+      <c r="B3798" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3798" t="n">
+        <v>5</v>
+      </c>
+      <c r="D3798" t="n">
+        <v>32</v>
+      </c>
+      <c r="E3798" t="n">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="3799">
+      <c r="A3799" t="n">
+        <v>23</v>
+      </c>
+      <c r="B3799" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3799" t="n">
+        <v>71</v>
+      </c>
+      <c r="D3799" t="n">
+        <v>5</v>
+      </c>
+      <c r="E3799" t="n">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="3800">
+      <c r="A3800" t="n">
+        <v>24</v>
+      </c>
+      <c r="B3800" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3800" t="n">
+        <v>48</v>
+      </c>
+      <c r="D3800" t="n">
+        <v>17</v>
+      </c>
+      <c r="E3800" t="n">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="3801">
+      <c r="A3801" t="n">
+        <v>25</v>
+      </c>
+      <c r="B3801" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3801" t="n">
+        <v>36</v>
+      </c>
+      <c r="D3801" t="n">
+        <v>72</v>
+      </c>
+      <c r="E3801" t="n">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="3802">
+      <c r="A3802" t="n">
+        <v>26</v>
+      </c>
+      <c r="B3802" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3802" t="n">
+        <v>53</v>
+      </c>
+      <c r="D3802" t="n">
+        <v>18</v>
+      </c>
+      <c r="E3802" t="n">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="3803">
+      <c r="A3803" t="n">
+        <v>27</v>
+      </c>
+      <c r="B3803" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3803" t="n">
+        <v>80</v>
+      </c>
+      <c r="D3803" t="n">
+        <v>22</v>
+      </c>
+      <c r="E3803" t="n">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="3804">
+      <c r="A3804" t="n">
+        <v>28</v>
+      </c>
+      <c r="B3804" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3804" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3804" t="n">
+        <v>15</v>
+      </c>
+      <c r="E3804" t="n">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="3805">
+      <c r="A3805" t="n">
+        <v>29</v>
+      </c>
+      <c r="B3805" t="n">
+        <v>7</v>
+      </c>
+      <c r="C3805" t="n">
+        <v>9</v>
+      </c>
+      <c r="D3805" t="n">
+        <v>45</v>
+      </c>
+      <c r="E3805" t="n">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="3806">
+      <c r="A3806" t="n">
+        <v>30</v>
+      </c>
+      <c r="B3806" t="n">
+        <v>8</v>
+      </c>
+      <c r="C3806" t="n">
+        <v>82</v>
+      </c>
+      <c r="D3806" t="n">
+        <v>92</v>
+      </c>
+      <c r="E3806" t="n">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="3807">
+      <c r="A3807" t="n">
+        <v>31</v>
+      </c>
+      <c r="B3807" t="n">
+        <v>9</v>
+      </c>
+      <c r="C3807" t="n">
+        <v>25</v>
+      </c>
+      <c r="D3807" t="n">
+        <v>15</v>
+      </c>
+      <c r="E3807" t="n">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="3808">
+      <c r="A3808" t="n">
+        <v>32</v>
+      </c>
+      <c r="B3808" t="n">
+        <v>10</v>
+      </c>
+      <c r="C3808" t="n">
+        <v>76</v>
+      </c>
+      <c r="D3808" t="n">
+        <v>30</v>
+      </c>
+      <c r="E3808" t="n">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="3809">
+      <c r="A3809" t="n">
+        <v>33</v>
+      </c>
+      <c r="B3809" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3809" t="n">
+        <v>69</v>
+      </c>
+      <c r="D3809" t="n">
+        <v>91</v>
+      </c>
+      <c r="E3809" t="n">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="3810">
+      <c r="A3810" t="n">
+        <v>34</v>
+      </c>
+      <c r="B3810" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3810" t="n">
+        <v>42</v>
+      </c>
+      <c r="D3810" t="n">
+        <v>90</v>
+      </c>
+      <c r="E3810" t="n">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="3811">
+      <c r="A3811" t="n">
+        <v>35</v>
+      </c>
+      <c r="B3811" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3811" t="n">
+        <v>30</v>
+      </c>
+      <c r="D3811" t="n">
+        <v>65</v>
+      </c>
+      <c r="E3811" t="n">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="3812">
+      <c r="A3812" t="n">
+        <v>36</v>
+      </c>
+      <c r="B3812" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3812" t="n">
+        <v>10</v>
+      </c>
+      <c r="D3812" t="n">
+        <v>11</v>
+      </c>
+      <c r="E3812" t="n">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="3813">
+      <c r="A3813" t="n">
+        <v>37</v>
+      </c>
+      <c r="B3813" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3813" t="n">
+        <v>82</v>
+      </c>
+      <c r="D3813" t="n">
+        <v>54</v>
+      </c>
+      <c r="E3813" t="n">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="3814">
+      <c r="A3814" t="n">
+        <v>38</v>
+      </c>
+      <c r="B3814" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3814" t="n">
+        <v>63</v>
+      </c>
+      <c r="D3814" t="n">
+        <v>50</v>
+      </c>
+      <c r="E3814" t="n">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="3815">
+      <c r="A3815" t="n">
+        <v>39</v>
+      </c>
+      <c r="B3815" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3815" t="n">
+        <v>43</v>
+      </c>
+      <c r="D3815" t="n">
+        <v>5</v>
+      </c>
+      <c r="E3815" t="n">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="3816">
+      <c r="A3816" t="n">
+        <v>40</v>
+      </c>
+      <c r="B3816" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3816" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3816" t="n">
+        <v>80</v>
+      </c>
+      <c r="E3816" t="n">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="3817">
+      <c r="A3817" t="n">
+        <v>41</v>
+      </c>
+      <c r="B3817" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3817" t="n">
+        <v>66</v>
+      </c>
+      <c r="D3817" t="n">
+        <v>44</v>
+      </c>
+      <c r="E3817" t="n">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="3818">
+      <c r="A3818" t="n">
+        <v>42</v>
+      </c>
+      <c r="B3818" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3818" t="n">
+        <v>50</v>
+      </c>
+      <c r="D3818" t="n">
+        <v>43</v>
+      </c>
+      <c r="E3818" t="n">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="3819">
+      <c r="A3819" t="n">
+        <v>43</v>
+      </c>
+      <c r="B3819" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3819" t="n">
+        <v>32</v>
+      </c>
+      <c r="D3819" t="n">
+        <v>30</v>
+      </c>
+      <c r="E3819" t="n">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="3820">
+      <c r="A3820" t="n">
+        <v>44</v>
+      </c>
+      <c r="B3820" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3820" t="n">
+        <v>86</v>
+      </c>
+      <c r="D3820" t="n">
+        <v>35</v>
+      </c>
+      <c r="E3820" t="n">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="3821">
+      <c r="A3821" t="n">
+        <v>45</v>
+      </c>
+      <c r="B3821" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3821" t="n">
+        <v>91</v>
+      </c>
+      <c r="D3821" t="n">
+        <v>58</v>
+      </c>
+      <c r="E3821" t="n">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="3822">
+      <c r="A3822" t="n">
+        <v>46</v>
+      </c>
+      <c r="B3822" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3822" t="n">
+        <v>61</v>
+      </c>
+      <c r="D3822" t="n">
+        <v>78</v>
+      </c>
+      <c r="E3822" t="n">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="3823">
+      <c r="A3823" t="n">
+        <v>47</v>
+      </c>
+      <c r="B3823" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3823" t="n">
+        <v>71</v>
+      </c>
+      <c r="D3823" t="n">
+        <v>97</v>
+      </c>
+      <c r="E3823" t="n">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="3824">
+      <c r="A3824" t="n">
+        <v>48</v>
+      </c>
+      <c r="B3824" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3824" t="n">
+        <v>64</v>
+      </c>
+      <c r="D3824" t="n">
+        <v>42</v>
+      </c>
+      <c r="E3824" t="n">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="3825">
+      <c r="A3825" t="n">
+        <v>49</v>
+      </c>
+      <c r="B3825" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3825" t="n">
+        <v>62</v>
+      </c>
+      <c r="D3825" t="n">
+        <v>61</v>
+      </c>
+      <c r="E3825" t="n">
+        <v>630</v>
       </c>
     </row>
   </sheetData>
@@ -75206,7 +76306,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F252"/>
+  <dimension ref="A1:F255"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -82243,30 +83343,114 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Naturalna Poznań</t>
+          <t>Care Olsztyn</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>1645388926</t>
+          <t>9579862754</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>Augustów</t>
+          <t>Radom</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Siłownia / klub sportowy</t>
+          <t>Gabinet dietetyczny</t>
         </is>
       </c>
       <c r="F252" t="n">
         <v>13</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="n">
+        <v>270</v>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Shine Nutri Lublin</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>1959791174</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>Knurów</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>Sklep internetowy z suplementami</t>
+        </is>
+      </c>
+      <c r="F253" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="n">
+        <v>271</v>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Vital Wellness</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>9267868558</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Płock</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>Supermarket / drogeria wielkopowierzchniowa</t>
+        </is>
+      </c>
+      <c r="F254" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="n">
+        <v>272</v>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Apteka Szczecin</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>1014092081</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>Bełchatów</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>Drogeria specjalistyczna</t>
+        </is>
+      </c>
+      <c r="F255" t="n">
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/dane.xlsx
+++ b/dane.xlsx
@@ -3759,7 +3759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G631"/>
+  <dimension ref="A1:G641"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19547,6 +19547,256 @@
       </c>
       <c r="G631" t="n">
         <v>2671</v>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="n">
+        <v>631</v>
+      </c>
+      <c r="B632" s="2" t="n">
+        <v>46096</v>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>Zwrot</t>
+        </is>
+      </c>
+      <c r="D632" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="E632" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F632" t="n">
+        <v>4</v>
+      </c>
+      <c r="G632" t="n">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="n">
+        <v>632</v>
+      </c>
+      <c r="B633" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>Dostarczone</t>
+        </is>
+      </c>
+      <c r="D633" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E633" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F633" t="n">
+        <v>4</v>
+      </c>
+      <c r="G633" t="n">
+        <v>1733</v>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="n">
+        <v>633</v>
+      </c>
+      <c r="B634" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>Zwrot</t>
+        </is>
+      </c>
+      <c r="D634" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="E634" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F634" t="n">
+        <v>4</v>
+      </c>
+      <c r="G634" t="n">
+        <v>2894</v>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="n">
+        <v>634</v>
+      </c>
+      <c r="B635" s="2" t="n">
+        <v>46075</v>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>Dostarczone</t>
+        </is>
+      </c>
+      <c r="D635" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="E635" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F635" t="n">
+        <v>4</v>
+      </c>
+      <c r="G635" t="n">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="n">
+        <v>635</v>
+      </c>
+      <c r="B636" s="2" t="n">
+        <v>46069</v>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>Wysłane</t>
+        </is>
+      </c>
+      <c r="D636" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E636" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F636" t="n">
+        <v>2</v>
+      </c>
+      <c r="G636" t="n">
+        <v>3821</v>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="n">
+        <v>636</v>
+      </c>
+      <c r="B637" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>Zwrot</t>
+        </is>
+      </c>
+      <c r="D637" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E637" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F637" t="n">
+        <v>4</v>
+      </c>
+      <c r="G637" t="n">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="n">
+        <v>637</v>
+      </c>
+      <c r="B638" s="2" t="n">
+        <v>46072</v>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>Wysłane</t>
+        </is>
+      </c>
+      <c r="D638" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="E638" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F638" t="n">
+        <v>4</v>
+      </c>
+      <c r="G638" t="n">
+        <v>1927</v>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="n">
+        <v>638</v>
+      </c>
+      <c r="B639" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>Dostarczone</t>
+        </is>
+      </c>
+      <c r="D639" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="E639" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F639" t="n">
+        <v>4</v>
+      </c>
+      <c r="G639" t="n">
+        <v>2527</v>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="n">
+        <v>639</v>
+      </c>
+      <c r="B640" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>Nowe</t>
+        </is>
+      </c>
+      <c r="D640" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="E640" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F640" t="n">
+        <v>1</v>
+      </c>
+      <c r="G640" t="n">
+        <v>3353</v>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="n">
+        <v>640</v>
+      </c>
+      <c r="B641" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>Wysłane</t>
+        </is>
+      </c>
+      <c r="D641" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E641" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F641" t="n">
+        <v>1</v>
+      </c>
+      <c r="G641" t="n">
+        <v>257</v>
       </c>
     </row>
   </sheetData>
@@ -19560,7 +19810,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3825"/>
+  <dimension ref="A1:E3883"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -76293,6 +76543,992 @@
       </c>
       <c r="E3825" t="n">
         <v>630</v>
+      </c>
+    </row>
+    <row r="3826">
+      <c r="A3826" t="n">
+        <v>0</v>
+      </c>
+      <c r="B3826" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3826" t="n">
+        <v>34</v>
+      </c>
+      <c r="D3826" t="n">
+        <v>15</v>
+      </c>
+      <c r="E3826" t="n">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="3827">
+      <c r="A3827" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3827" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3827" t="n">
+        <v>96</v>
+      </c>
+      <c r="D3827" t="n">
+        <v>17</v>
+      </c>
+      <c r="E3827" t="n">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="3828">
+      <c r="A3828" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3828" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3828" t="n">
+        <v>68</v>
+      </c>
+      <c r="D3828" t="n">
+        <v>29</v>
+      </c>
+      <c r="E3828" t="n">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="3829">
+      <c r="A3829" t="n">
+        <v>3</v>
+      </c>
+      <c r="B3829" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3829" t="n">
+        <v>24</v>
+      </c>
+      <c r="D3829" t="n">
+        <v>68</v>
+      </c>
+      <c r="E3829" t="n">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="3830">
+      <c r="A3830" t="n">
+        <v>4</v>
+      </c>
+      <c r="B3830" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3830" t="n">
+        <v>56</v>
+      </c>
+      <c r="D3830" t="n">
+        <v>90</v>
+      </c>
+      <c r="E3830" t="n">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="3831">
+      <c r="A3831" t="n">
+        <v>5</v>
+      </c>
+      <c r="B3831" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3831" t="n">
+        <v>77</v>
+      </c>
+      <c r="D3831" t="n">
+        <v>54</v>
+      </c>
+      <c r="E3831" t="n">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="3832">
+      <c r="A3832" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3832" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3832" t="n">
+        <v>26</v>
+      </c>
+      <c r="D3832" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3832" t="n">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="3833">
+      <c r="A3833" t="n">
+        <v>7</v>
+      </c>
+      <c r="B3833" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3833" t="n">
+        <v>30</v>
+      </c>
+      <c r="D3833" t="n">
+        <v>28</v>
+      </c>
+      <c r="E3833" t="n">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="3834">
+      <c r="A3834" t="n">
+        <v>8</v>
+      </c>
+      <c r="B3834" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3834" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3834" t="n">
+        <v>14</v>
+      </c>
+      <c r="E3834" t="n">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="3835">
+      <c r="A3835" t="n">
+        <v>9</v>
+      </c>
+      <c r="B3835" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3835" t="n">
+        <v>24</v>
+      </c>
+      <c r="D3835" t="n">
+        <v>49</v>
+      </c>
+      <c r="E3835" t="n">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="3836">
+      <c r="A3836" t="n">
+        <v>10</v>
+      </c>
+      <c r="B3836" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3836" t="n">
+        <v>12</v>
+      </c>
+      <c r="D3836" t="n">
+        <v>75</v>
+      </c>
+      <c r="E3836" t="n">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="3837">
+      <c r="A3837" t="n">
+        <v>11</v>
+      </c>
+      <c r="B3837" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3837" t="n">
+        <v>90</v>
+      </c>
+      <c r="D3837" t="n">
+        <v>85</v>
+      </c>
+      <c r="E3837" t="n">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="3838">
+      <c r="A3838" t="n">
+        <v>12</v>
+      </c>
+      <c r="B3838" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3838" t="n">
+        <v>52</v>
+      </c>
+      <c r="D3838" t="n">
+        <v>38</v>
+      </c>
+      <c r="E3838" t="n">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="3839">
+      <c r="A3839" t="n">
+        <v>13</v>
+      </c>
+      <c r="B3839" t="n">
+        <v>7</v>
+      </c>
+      <c r="C3839" t="n">
+        <v>100</v>
+      </c>
+      <c r="D3839" t="n">
+        <v>77</v>
+      </c>
+      <c r="E3839" t="n">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="3840">
+      <c r="A3840" t="n">
+        <v>14</v>
+      </c>
+      <c r="B3840" t="n">
+        <v>8</v>
+      </c>
+      <c r="C3840" t="n">
+        <v>24</v>
+      </c>
+      <c r="D3840" t="n">
+        <v>45</v>
+      </c>
+      <c r="E3840" t="n">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="3841">
+      <c r="A3841" t="n">
+        <v>15</v>
+      </c>
+      <c r="B3841" t="n">
+        <v>9</v>
+      </c>
+      <c r="C3841" t="n">
+        <v>62</v>
+      </c>
+      <c r="D3841" t="n">
+        <v>30</v>
+      </c>
+      <c r="E3841" t="n">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="3842">
+      <c r="A3842" t="n">
+        <v>16</v>
+      </c>
+      <c r="B3842" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3842" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3842" t="n">
+        <v>76</v>
+      </c>
+      <c r="E3842" t="n">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="3843">
+      <c r="A3843" t="n">
+        <v>17</v>
+      </c>
+      <c r="B3843" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3843" t="n">
+        <v>5</v>
+      </c>
+      <c r="D3843" t="n">
+        <v>26</v>
+      </c>
+      <c r="E3843" t="n">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="3844">
+      <c r="A3844" t="n">
+        <v>18</v>
+      </c>
+      <c r="B3844" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3844" t="n">
+        <v>84</v>
+      </c>
+      <c r="D3844" t="n">
+        <v>98</v>
+      </c>
+      <c r="E3844" t="n">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="3845">
+      <c r="A3845" t="n">
+        <v>19</v>
+      </c>
+      <c r="B3845" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3845" t="n">
+        <v>72</v>
+      </c>
+      <c r="D3845" t="n">
+        <v>39</v>
+      </c>
+      <c r="E3845" t="n">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="3846">
+      <c r="A3846" t="n">
+        <v>20</v>
+      </c>
+      <c r="B3846" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3846" t="n">
+        <v>45</v>
+      </c>
+      <c r="D3846" t="n">
+        <v>41</v>
+      </c>
+      <c r="E3846" t="n">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="3847">
+      <c r="A3847" t="n">
+        <v>21</v>
+      </c>
+      <c r="B3847" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3847" t="n">
+        <v>16</v>
+      </c>
+      <c r="D3847" t="n">
+        <v>53</v>
+      </c>
+      <c r="E3847" t="n">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="3848">
+      <c r="A3848" t="n">
+        <v>22</v>
+      </c>
+      <c r="B3848" t="n">
+        <v>7</v>
+      </c>
+      <c r="C3848" t="n">
+        <v>44</v>
+      </c>
+      <c r="D3848" t="n">
+        <v>78</v>
+      </c>
+      <c r="E3848" t="n">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="3849">
+      <c r="A3849" t="n">
+        <v>23</v>
+      </c>
+      <c r="B3849" t="n">
+        <v>8</v>
+      </c>
+      <c r="C3849" t="n">
+        <v>52</v>
+      </c>
+      <c r="D3849" t="n">
+        <v>55</v>
+      </c>
+      <c r="E3849" t="n">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="3850">
+      <c r="A3850" t="n">
+        <v>24</v>
+      </c>
+      <c r="B3850" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3850" t="n">
+        <v>84</v>
+      </c>
+      <c r="D3850" t="n">
+        <v>46</v>
+      </c>
+      <c r="E3850" t="n">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="3851">
+      <c r="A3851" t="n">
+        <v>25</v>
+      </c>
+      <c r="B3851" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3851" t="n">
+        <v>63</v>
+      </c>
+      <c r="D3851" t="n">
+        <v>55</v>
+      </c>
+      <c r="E3851" t="n">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="3852">
+      <c r="A3852" t="n">
+        <v>26</v>
+      </c>
+      <c r="B3852" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3852" t="n">
+        <v>84</v>
+      </c>
+      <c r="D3852" t="n">
+        <v>64</v>
+      </c>
+      <c r="E3852" t="n">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="3853">
+      <c r="A3853" t="n">
+        <v>27</v>
+      </c>
+      <c r="B3853" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3853" t="n">
+        <v>95</v>
+      </c>
+      <c r="D3853" t="n">
+        <v>72</v>
+      </c>
+      <c r="E3853" t="n">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="3854">
+      <c r="A3854" t="n">
+        <v>28</v>
+      </c>
+      <c r="B3854" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3854" t="n">
+        <v>42</v>
+      </c>
+      <c r="D3854" t="n">
+        <v>27</v>
+      </c>
+      <c r="E3854" t="n">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="3855">
+      <c r="A3855" t="n">
+        <v>29</v>
+      </c>
+      <c r="B3855" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3855" t="n">
+        <v>36</v>
+      </c>
+      <c r="D3855" t="n">
+        <v>34</v>
+      </c>
+      <c r="E3855" t="n">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="3856">
+      <c r="A3856" t="n">
+        <v>30</v>
+      </c>
+      <c r="B3856" t="n">
+        <v>7</v>
+      </c>
+      <c r="C3856" t="n">
+        <v>96</v>
+      </c>
+      <c r="D3856" t="n">
+        <v>81</v>
+      </c>
+      <c r="E3856" t="n">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="3857">
+      <c r="A3857" t="n">
+        <v>31</v>
+      </c>
+      <c r="B3857" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3857" t="n">
+        <v>6</v>
+      </c>
+      <c r="D3857" t="n">
+        <v>10</v>
+      </c>
+      <c r="E3857" t="n">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="3858">
+      <c r="A3858" t="n">
+        <v>32</v>
+      </c>
+      <c r="B3858" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3858" t="n">
+        <v>69</v>
+      </c>
+      <c r="D3858" t="n">
+        <v>78</v>
+      </c>
+      <c r="E3858" t="n">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="3859">
+      <c r="A3859" t="n">
+        <v>33</v>
+      </c>
+      <c r="B3859" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3859" t="n">
+        <v>36</v>
+      </c>
+      <c r="D3859" t="n">
+        <v>89</v>
+      </c>
+      <c r="E3859" t="n">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="3860">
+      <c r="A3860" t="n">
+        <v>34</v>
+      </c>
+      <c r="B3860" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3860" t="n">
+        <v>36</v>
+      </c>
+      <c r="D3860" t="n">
+        <v>20</v>
+      </c>
+      <c r="E3860" t="n">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="3861">
+      <c r="A3861" t="n">
+        <v>35</v>
+      </c>
+      <c r="B3861" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3861" t="n">
+        <v>48</v>
+      </c>
+      <c r="D3861" t="n">
+        <v>38</v>
+      </c>
+      <c r="E3861" t="n">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="3862">
+      <c r="A3862" t="n">
+        <v>36</v>
+      </c>
+      <c r="B3862" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3862" t="n">
+        <v>21</v>
+      </c>
+      <c r="D3862" t="n">
+        <v>77</v>
+      </c>
+      <c r="E3862" t="n">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="3863">
+      <c r="A3863" t="n">
+        <v>37</v>
+      </c>
+      <c r="B3863" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3863" t="n">
+        <v>23</v>
+      </c>
+      <c r="D3863" t="n">
+        <v>43</v>
+      </c>
+      <c r="E3863" t="n">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="3864">
+      <c r="A3864" t="n">
+        <v>38</v>
+      </c>
+      <c r="B3864" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3864" t="n">
+        <v>5</v>
+      </c>
+      <c r="D3864" t="n">
+        <v>55</v>
+      </c>
+      <c r="E3864" t="n">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="3865">
+      <c r="A3865" t="n">
+        <v>39</v>
+      </c>
+      <c r="B3865" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3865" t="n">
+        <v>12</v>
+      </c>
+      <c r="D3865" t="n">
+        <v>41</v>
+      </c>
+      <c r="E3865" t="n">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="3866">
+      <c r="A3866" t="n">
+        <v>40</v>
+      </c>
+      <c r="B3866" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3866" t="n">
+        <v>10</v>
+      </c>
+      <c r="D3866" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3866" t="n">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="3867">
+      <c r="A3867" t="n">
+        <v>41</v>
+      </c>
+      <c r="B3867" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3867" t="n">
+        <v>23</v>
+      </c>
+      <c r="D3867" t="n">
+        <v>14</v>
+      </c>
+      <c r="E3867" t="n">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="3868">
+      <c r="A3868" t="n">
+        <v>42</v>
+      </c>
+      <c r="B3868" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3868" t="n">
+        <v>55</v>
+      </c>
+      <c r="D3868" t="n">
+        <v>57</v>
+      </c>
+      <c r="E3868" t="n">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="3869">
+      <c r="A3869" t="n">
+        <v>43</v>
+      </c>
+      <c r="B3869" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3869" t="n">
+        <v>94</v>
+      </c>
+      <c r="D3869" t="n">
+        <v>52</v>
+      </c>
+      <c r="E3869" t="n">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="3870">
+      <c r="A3870" t="n">
+        <v>44</v>
+      </c>
+      <c r="B3870" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3870" t="n">
+        <v>69</v>
+      </c>
+      <c r="D3870" t="n">
+        <v>76</v>
+      </c>
+      <c r="E3870" t="n">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="3871">
+      <c r="A3871" t="n">
+        <v>45</v>
+      </c>
+      <c r="B3871" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3871" t="n">
+        <v>64</v>
+      </c>
+      <c r="D3871" t="n">
+        <v>94</v>
+      </c>
+      <c r="E3871" t="n">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="3872">
+      <c r="A3872" t="n">
+        <v>46</v>
+      </c>
+      <c r="B3872" t="n">
+        <v>7</v>
+      </c>
+      <c r="C3872" t="n">
+        <v>55</v>
+      </c>
+      <c r="D3872" t="n">
+        <v>82</v>
+      </c>
+      <c r="E3872" t="n">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="3873">
+      <c r="A3873" t="n">
+        <v>47</v>
+      </c>
+      <c r="B3873" t="n">
+        <v>8</v>
+      </c>
+      <c r="C3873" t="n">
+        <v>35</v>
+      </c>
+      <c r="D3873" t="n">
+        <v>85</v>
+      </c>
+      <c r="E3873" t="n">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="3874">
+      <c r="A3874" t="n">
+        <v>48</v>
+      </c>
+      <c r="B3874" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3874" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3874" t="n">
+        <v>27</v>
+      </c>
+      <c r="E3874" t="n">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="3875">
+      <c r="A3875" t="n">
+        <v>49</v>
+      </c>
+      <c r="B3875" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3875" t="n">
+        <v>98</v>
+      </c>
+      <c r="D3875" t="n">
+        <v>95</v>
+      </c>
+      <c r="E3875" t="n">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="3876">
+      <c r="A3876" t="n">
+        <v>50</v>
+      </c>
+      <c r="B3876" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3876" t="n">
+        <v>38</v>
+      </c>
+      <c r="D3876" t="n">
+        <v>60</v>
+      </c>
+      <c r="E3876" t="n">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="3877">
+      <c r="A3877" t="n">
+        <v>51</v>
+      </c>
+      <c r="B3877" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3877" t="n">
+        <v>11</v>
+      </c>
+      <c r="D3877" t="n">
+        <v>54</v>
+      </c>
+      <c r="E3877" t="n">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="3878">
+      <c r="A3878" t="n">
+        <v>52</v>
+      </c>
+      <c r="B3878" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3878" t="n">
+        <v>62</v>
+      </c>
+      <c r="D3878" t="n">
+        <v>48</v>
+      </c>
+      <c r="E3878" t="n">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="3879">
+      <c r="A3879" t="n">
+        <v>53</v>
+      </c>
+      <c r="B3879" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3879" t="n">
+        <v>34</v>
+      </c>
+      <c r="D3879" t="n">
+        <v>54</v>
+      </c>
+      <c r="E3879" t="n">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="3880">
+      <c r="A3880" t="n">
+        <v>54</v>
+      </c>
+      <c r="B3880" t="n">
+        <v>7</v>
+      </c>
+      <c r="C3880" t="n">
+        <v>52</v>
+      </c>
+      <c r="D3880" t="n">
+        <v>18</v>
+      </c>
+      <c r="E3880" t="n">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="3881">
+      <c r="A3881" t="n">
+        <v>55</v>
+      </c>
+      <c r="B3881" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3881" t="n">
+        <v>17</v>
+      </c>
+      <c r="D3881" t="n">
+        <v>58</v>
+      </c>
+      <c r="E3881" t="n">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="3882">
+      <c r="A3882" t="n">
+        <v>56</v>
+      </c>
+      <c r="B3882" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3882" t="n">
+        <v>54</v>
+      </c>
+      <c r="D3882" t="n">
+        <v>73</v>
+      </c>
+      <c r="E3882" t="n">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="3883">
+      <c r="A3883" t="n">
+        <v>57</v>
+      </c>
+      <c r="B3883" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3883" t="n">
+        <v>42</v>
+      </c>
+      <c r="D3883" t="n">
+        <v>84</v>
+      </c>
+      <c r="E3883" t="n">
+        <v>640</v>
       </c>
     </row>
   </sheetData>
@@ -76306,7 +77542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F255"/>
+  <dimension ref="A1:F258"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83427,30 +84663,114 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Apteka Szczecin</t>
+          <t>Nutri Well Team</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>1014092081</t>
+          <t>9113746833</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>Bełchatów</t>
+          <t>Kraków</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
+          <t>Zielarnia</t>
+        </is>
+      </c>
+      <c r="F255" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="n">
+        <v>274</v>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Natural Glow Wałbrzych</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>4609543160</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>Szczecin</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>Supermarket / drogeria wielkopowierzchniowa</t>
+        </is>
+      </c>
+      <c r="F256" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="n">
+        <v>275</v>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Dbam o Zdrowie Beauty</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>3386970209</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>Łaziska Górne</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
           <t>Drogeria specjalistyczna</t>
         </is>
       </c>
-      <c r="F255" t="n">
-        <v>17</v>
+      <c r="F257" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="n">
+        <v>276</v>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Natura Active </t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>7305880552</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>Kluczbork</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>Medycyna estetyczna / klinika urody</t>
+        </is>
+      </c>
+      <c r="F258" t="n">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
